--- a/docs/cost-analysis/Secure_Send_Cost_Model.xlsx
+++ b/docs/cost-analysis/Secure_Send_Cost_Model.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="判断サマリー" sheetId="1" r:id="R061b4fd8eaaa4c98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定と出典" sheetId="2" r:id="R35217e688fad476f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="収益試算" sheetId="3" r:id="R576429ae03364fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実績取得状況" sheetId="4" r:id="R961255a2efdd444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="判断サマリー" sheetId="1" r:id="Rc633babfa78848e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定と出典" sheetId="2" r:id="R2b84874bb62a4df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="収益試算" sheetId="3" r:id="Rc16274ddc78b4649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実績取得状況" sheetId="4" r:id="R24b6c12d482a4863"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <x:numFmt numFmtId="201" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -48,7 +49,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -65,6 +66,11 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F3556"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -78,7 +84,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -92,6 +98,12 @@
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -102,7 +114,7 @@
         <x:color rgb="FFB71C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -112,7 +124,7 @@
         <x:color rgb="FFB71C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -485,7 +497,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>実測未取得。以下は仮定による条件付き試算。正式価格・配分率の決定ではない。</x:v>
+        <x:v>共有請求取得済。Run単価を校正した将来試算。Secure Send実原価の確定値ではない。</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -691,7 +703,7 @@
       </x:c>
       <x:c r="E6" s="7" t="n">
         <x:f>'収益試算'!AF6</x:f>
-        <x:v>14665.436998596193</x:v>
+        <x:v>14294.933397311817</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
         <x:f>SUM('収益試算'!AH6:AI6)</x:f>
@@ -699,23 +711,23 @@
       </x:c>
       <x:c r="G6" s="7" t="n">
         <x:f>'収益試算'!AJ6</x:f>
-        <x:v>3921.229668070475</x:v>
+        <x:v>4291.733269354849</x:v>
       </x:c>
       <x:c r="H6" s="7" t="n">
         <x:f>'収益試算'!AK6</x:f>
-        <x:v>-11078.770331929525</x:v>
+        <x:v>-10708.266730645151</x:v>
       </x:c>
       <x:c r="I6" s="7" t="n">
         <x:f>'収益試算'!AL6</x:f>
-        <x:v>-1078.7703319295251</x:v>
+        <x:v>-708.2667306451513</x:v>
       </x:c>
       <x:c r="J6" s="8" t="n">
         <x:f>'収益試算'!AO6</x:f>
-        <x:v>0.13070765560234915</x:v>
+        <x:v>0.14305777564516162</x:v>
       </x:c>
       <x:c r="K6" s="8" t="n">
         <x:f>'収益試算'!AP6</x:f>
-        <x:v>-0.06929234439765086</x:v>
+        <x:v>-0.056942224354838394</x:v>
       </x:c>
       <x:c r="L6" s="1"/>
       <x:c r="M6" s="1"/>
@@ -779,7 +791,7 @@
       </x:c>
       <x:c r="E7" s="7" t="n">
         <x:f>'収益試算'!AF7</x:f>
-        <x:v>15514.548431884767</x:v>
+        <x:v>15140.595112834477</x:v>
       </x:c>
       <x:c r="F7" s="7" t="n">
         <x:f>SUM('収益試算'!AH7:AI7)</x:f>
@@ -787,23 +799,23 @@
       </x:c>
       <x:c r="G7" s="7" t="n">
         <x:f>'収益試算'!AJ7</x:f>
-        <x:v>-261.2150985514345</x:v>
+        <x:v>112.73822049885712</x:v>
       </x:c>
       <x:c r="H7" s="7" t="n">
         <x:f>'収益試算'!AK7</x:f>
-        <x:v>-15261.215098551434</x:v>
+        <x:v>-14887.261779501143</x:v>
       </x:c>
       <x:c r="I7" s="7" t="n">
         <x:f>'収益試算'!AL7</x:f>
-        <x:v>-5261.2150985514345</x:v>
+        <x:v>-4887.261779501143</x:v>
       </x:c>
       <x:c r="J7" s="8" t="n">
         <x:f>'収益試算'!AO7</x:f>
-        <x:v>-0.008707169951714484</x:v>
+        <x:v>0.003757940683295237</x:v>
       </x:c>
       <x:c r="K7" s="8" t="n">
         <x:f>'収益試算'!AP7</x:f>
-        <x:v>-0.20870716995171448</x:v>
+        <x:v>-0.19624205931670477</x:v>
       </x:c>
       <x:c r="L7" s="1"/>
       <x:c r="M7" s="1"/>
@@ -867,7 +879,7 @@
       </x:c>
       <x:c r="E8" s="7" t="n">
         <x:f>'収益試算'!AF8</x:f>
-        <x:v>39678.590477539066</x:v>
+        <x:v>39255.37782163064</x:v>
       </x:c>
       <x:c r="F8" s="7" t="n">
         <x:f>SUM('収益試算'!AH8:AI8)</x:f>
@@ -875,23 +887,23 @@
       </x:c>
       <x:c r="G8" s="7" t="n">
         <x:f>'収益試算'!AJ8</x:f>
-        <x:v>-32425.25714420573</x:v>
+        <x:v>-32002.044488297302</x:v>
       </x:c>
       <x:c r="H8" s="7" t="n">
         <x:f>'収益試算'!AK8</x:f>
-        <x:v>-47425.25714420573</x:v>
+        <x:v>-47002.0444882973</x:v>
       </x:c>
       <x:c r="I8" s="7" t="n">
         <x:f>'収益試算'!AL8</x:f>
-        <x:v>-37425.25714420573</x:v>
+        <x:v>-37002.0444882973</x:v>
       </x:c>
       <x:c r="J8" s="8" t="n">
         <x:f>'収益試算'!AO8</x:f>
-        <x:v>-1.0808419048068576</x:v>
+        <x:v>-1.0667348162765768</x:v>
       </x:c>
       <x:c r="K8" s="8" t="n">
         <x:f>'収益試算'!AP8</x:f>
-        <x:v>-1.2808419048068576</x:v>
+        <x:v>-1.2667348162765768</x:v>
       </x:c>
       <x:c r="L8" s="1"/>
       <x:c r="M8" s="1"/>
@@ -955,7 +967,7 @@
       </x:c>
       <x:c r="E9" s="7" t="n">
         <x:f>'収益試算'!AF9</x:f>
-        <x:v>15164.147994384766</x:v>
+        <x:v>14792.825333968543</x:v>
       </x:c>
       <x:c r="F9" s="7" t="n">
         <x:f>SUM('収益試算'!AH9:AI9)</x:f>
@@ -963,23 +975,23 @@
       </x:c>
       <x:c r="G9" s="7" t="n">
         <x:f>'収益試算'!AJ9</x:f>
-        <x:v>21702.5186722819</x:v>
+        <x:v>22073.841332698124</x:v>
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f>'収益試算'!AK9</x:f>
-        <x:v>-3297.4813277180983</x:v>
+        <x:v>-2926.1586673018755</x:v>
       </x:c>
       <x:c r="I9" s="7" t="n">
         <x:f>'収益試算'!AL9</x:f>
-        <x:v>16702.5186722819</x:v>
+        <x:v>17073.841332698124</x:v>
       </x:c>
       <x:c r="J9" s="8" t="n">
         <x:f>'収益試算'!AO9</x:f>
-        <x:v>0.434050373445638</x:v>
+        <x:v>0.4414768266539625</x:v>
       </x:c>
       <x:c r="K9" s="8" t="n">
         <x:f>'収益試算'!AP9</x:f>
-        <x:v>0.234050373445638</x:v>
+        <x:v>0.24147682665396247</x:v>
       </x:c>
       <x:c r="L9" s="1"/>
       <x:c r="M9" s="1"/>
@@ -1043,7 +1055,7 @@
       </x:c>
       <x:c r="E10" s="7" t="n">
         <x:f>'収益試算'!AF10</x:f>
-        <x:v>18560.593727539064</x:v>
+        <x:v>18175.47219605918</x:v>
       </x:c>
       <x:c r="F10" s="7" t="n">
         <x:f>SUM('収益試算'!AH10:AI10)</x:f>
@@ -1051,23 +1063,23 @@
       </x:c>
       <x:c r="G10" s="7" t="n">
         <x:f>'収益試算'!AJ10</x:f>
-        <x:v>14972.739605794268</x:v>
+        <x:v>15357.86113727415</x:v>
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f>'収益試算'!AK10</x:f>
-        <x:v>-10027.260394205732</x:v>
+        <x:v>-9642.13886272585</x:v>
       </x:c>
       <x:c r="I10" s="7" t="n">
         <x:f>'収益試算'!AL10</x:f>
-        <x:v>9972.739605794268</x:v>
+        <x:v>10357.86113727415</x:v>
       </x:c>
       <x:c r="J10" s="8" t="n">
         <x:f>'収益試算'!AO10</x:f>
-        <x:v>0.2994547921158854</x:v>
+        <x:v>0.307157222745483</x:v>
       </x:c>
       <x:c r="K10" s="8" t="n">
         <x:f>'収益試算'!AP10</x:f>
-        <x:v>0.09945479211588537</x:v>
+        <x:v>0.107157222745483</x:v>
       </x:c>
       <x:c r="L10" s="1"/>
       <x:c r="M10" s="1"/>
@@ -1131,7 +1143,7 @@
       </x:c>
       <x:c r="E11" s="7" t="n">
         <x:f>'収益試算'!AF11</x:f>
-        <x:v>115216.76191015624</x:v>
+        <x:v>114634.60303124384</x:v>
       </x:c>
       <x:c r="F11" s="7" t="n">
         <x:f>SUM('収益試算'!AH11:AI11)</x:f>
@@ -1139,23 +1151,23 @@
       </x:c>
       <x:c r="G11" s="7" t="n">
         <x:f>'収益試算'!AJ11</x:f>
-        <x:v>-89683.42857682292</x:v>
+        <x:v>-89101.2696979105</x:v>
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f>'収益試算'!AK11</x:f>
-        <x:v>-114683.42857682292</x:v>
+        <x:v>-114101.2696979105</x:v>
       </x:c>
       <x:c r="I11" s="7" t="n">
         <x:f>'収益試算'!AL11</x:f>
-        <x:v>-94683.42857682292</x:v>
+        <x:v>-94101.2696979105</x:v>
       </x:c>
       <x:c r="J11" s="8" t="n">
         <x:f>'収益試算'!AO11</x:f>
-        <x:v>-1.7936685715364584</x:v>
+        <x:v>-1.7820253939582098</x:v>
       </x:c>
       <x:c r="K11" s="8" t="n">
         <x:f>'収益試算'!AP11</x:f>
-        <x:v>-1.9936685715364584</x:v>
+        <x:v>-1.9820253939582098</x:v>
       </x:c>
       <x:c r="L11" s="1"/>
       <x:c r="M11" s="1"/>
@@ -1219,7 +1231,7 @@
       </x:c>
       <x:c r="E12" s="7" t="n">
         <x:f>'収益試算'!AF12</x:f>
-        <x:v>16161.569985961914</x:v>
+        <x:v>15788.609207281996</x:v>
       </x:c>
       <x:c r="F12" s="7" t="n">
         <x:f>SUM('収益試算'!AH12:AI12)</x:f>
@@ -1227,23 +1239,23 @@
       </x:c>
       <x:c r="G12" s="7" t="n">
         <x:f>'収益試算'!AJ12</x:f>
-        <x:v>47625.09668070475</x:v>
+        <x:v>47998.05745938467</x:v>
       </x:c>
       <x:c r="H12" s="7" t="n">
         <x:f>'収益試算'!AK12</x:f>
-        <x:v>7625.096680704752</x:v>
+        <x:v>7998.057459384669</x:v>
       </x:c>
       <x:c r="I12" s="7" t="n">
         <x:f>'収益試算'!AL12</x:f>
-        <x:v>42625.09668070475</x:v>
+        <x:v>42998.05745938467</x:v>
       </x:c>
       <x:c r="J12" s="8" t="n">
         <x:f>'収益試算'!AO12</x:f>
-        <x:v>0.5953137085088094</x:v>
+        <x:v>0.5999757182423083</x:v>
       </x:c>
       <x:c r="K12" s="8" t="n">
         <x:f>'収益試算'!AP12</x:f>
-        <x:v>0.39531370850880937</x:v>
+        <x:v>0.3999757182423083</x:v>
       </x:c>
       <x:c r="L12" s="1"/>
       <x:c r="M12" s="1"/>
@@ -1307,7 +1319,7 @@
       </x:c>
       <x:c r="E13" s="7" t="n">
         <x:f>'収益試算'!AF13</x:f>
-        <x:v>24652.684318847656</x:v>
+        <x:v>24245.22636250859</x:v>
       </x:c>
       <x:c r="F13" s="7" t="n">
         <x:f>SUM('収益試算'!AH13:AI13)</x:f>
@@ -1315,23 +1327,23 @@
       </x:c>
       <x:c r="G13" s="7" t="n">
         <x:f>'収益試算'!AJ13</x:f>
-        <x:v>35800.64901448568</x:v>
+        <x:v>36208.106970824745</x:v>
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f>'収益試算'!AK13</x:f>
-        <x:v>-4199.35098551432</x:v>
+        <x:v>-3791.893029175255</x:v>
       </x:c>
       <x:c r="I13" s="7" t="n">
         <x:f>'収益試算'!AL13</x:f>
-        <x:v>30800.64901448568</x:v>
+        <x:v>31208.106970824745</x:v>
       </x:c>
       <x:c r="J13" s="8" t="n">
         <x:f>'収益試算'!AO13</x:f>
-        <x:v>0.447508112681071</x:v>
+        <x:v>0.4526013371353093</x:v>
       </x:c>
       <x:c r="K13" s="8" t="n">
         <x:f>'収益試算'!AP13</x:f>
-        <x:v>0.24750811268107098</x:v>
+        <x:v>0.2526013371353093</x:v>
       </x:c>
       <x:c r="L13" s="1"/>
       <x:c r="M13" s="1"/>
@@ -1395,7 +1407,7 @@
       </x:c>
       <x:c r="E14" s="7" t="n">
         <x:f>'収益試算'!AF14</x:f>
-        <x:v>266293.10477539065</x:v>
+        <x:v>265393.0534504702</x:v>
       </x:c>
       <x:c r="F14" s="7" t="n">
         <x:f>SUM('収益試算'!AH14:AI14)</x:f>
@@ -1403,23 +1415,23 @@
       </x:c>
       <x:c r="G14" s="7" t="n">
         <x:f>'収益試算'!AJ14</x:f>
-        <x:v>-213839.77144205733</x:v>
+        <x:v>-212939.7201171369</x:v>
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f>'収益試算'!AK14</x:f>
-        <x:v>-253839.77144205733</x:v>
+        <x:v>-252939.7201171369</x:v>
       </x:c>
       <x:c r="I14" s="7" t="n">
         <x:f>'収益試算'!AL14</x:f>
-        <x:v>-218839.77144205733</x:v>
+        <x:v>-217939.7201171369</x:v>
       </x:c>
       <x:c r="J14" s="8" t="n">
         <x:f>'収益試算'!AO14</x:f>
-        <x:v>-2.6729971430257167</x:v>
+        <x:v>-2.661746501464211</x:v>
       </x:c>
       <x:c r="K14" s="8" t="n">
         <x:f>'収益試算'!AP14</x:f>
-        <x:v>-2.872997143025717</x:v>
+        <x:v>-2.861746501464211</x:v>
       </x:c>
       <x:c r="L14" s="1"/>
       <x:c r="M14" s="1"/>
@@ -1483,7 +1495,7 @@
       </x:c>
       <x:c r="E15" s="7" t="n">
         <x:f>'収益試算'!AF15</x:f>
-        <x:v>20661.569985961913</x:v>
+        <x:v>20288.609207281996</x:v>
       </x:c>
       <x:c r="F15" s="7" t="n">
         <x:f>SUM('収益試算'!AH15:AI15)</x:f>
@@ -1491,23 +1503,23 @@
       </x:c>
       <x:c r="G15" s="7" t="n">
         <x:f>'収益試算'!AJ15</x:f>
-        <x:v>237205.09668070474</x:v>
+        <x:v>237578.05745938467</x:v>
       </x:c>
       <x:c r="H15" s="7" t="n">
         <x:f>'収益試算'!AK15</x:f>
-        <x:v>87205.09668070474</x:v>
+        <x:v>87578.05745938467</x:v>
       </x:c>
       <x:c r="I15" s="7" t="n">
         <x:f>'収益試算'!AL15</x:f>
-        <x:v>187205.09668070474</x:v>
+        <x:v>187578.05745938467</x:v>
       </x:c>
       <x:c r="J15" s="8" t="n">
         <x:f>'収益試算'!AO15</x:f>
-        <x:v>0.7906836556023491</x:v>
+        <x:v>0.791926858197949</x:v>
       </x:c>
       <x:c r="K15" s="8" t="n">
         <x:f>'収益試算'!AP15</x:f>
-        <x:v>0.5906836556023491</x:v>
+        <x:v>0.5919268581979489</x:v>
       </x:c>
       <x:c r="L15" s="1"/>
       <x:c r="M15" s="1"/>
@@ -1571,7 +1583,7 @@
       </x:c>
       <x:c r="E16" s="7" t="n">
         <x:f>'収益試算'!AF16</x:f>
-        <x:v>29152.684318847656</x:v>
+        <x:v>28745.226362508587</x:v>
       </x:c>
       <x:c r="F16" s="7" t="n">
         <x:f>SUM('収益試算'!AH16:AI16)</x:f>
@@ -1579,23 +1591,23 @@
       </x:c>
       <x:c r="G16" s="7" t="n">
         <x:f>'収益試算'!AJ16</x:f>
-        <x:v>195380.64901448568</x:v>
+        <x:v>195788.10697082474</x:v>
       </x:c>
       <x:c r="H16" s="7" t="n">
         <x:f>'収益試算'!AK16</x:f>
-        <x:v>45380.64901448568</x:v>
+        <x:v>45788.10697082474</x:v>
       </x:c>
       <x:c r="I16" s="7" t="n">
         <x:f>'収益試算'!AL16</x:f>
-        <x:v>145380.64901448568</x:v>
+        <x:v>145788.10697082474</x:v>
       </x:c>
       <x:c r="J16" s="8" t="n">
         <x:f>'収益試算'!AO16</x:f>
-        <x:v>0.6512688300482856</x:v>
+        <x:v>0.6526270232360825</x:v>
       </x:c>
       <x:c r="K16" s="8" t="n">
         <x:f>'収益試算'!AP16</x:f>
-        <x:v>0.4512688300482856</x:v>
+        <x:v>0.45262702323608245</x:v>
       </x:c>
       <x:c r="L16" s="1"/>
       <x:c r="M16" s="1"/>
@@ -1659,7 +1671,7 @@
       </x:c>
       <x:c r="E17" s="7" t="n">
         <x:f>'収益試算'!AF17</x:f>
-        <x:v>270793.10477539065</x:v>
+        <x:v>269893.0534504702</x:v>
       </x:c>
       <x:c r="F17" s="7" t="n">
         <x:f>SUM('収益試算'!AH17:AI17)</x:f>
@@ -1667,23 +1679,23 @@
       </x:c>
       <x:c r="G17" s="7" t="n">
         <x:f>'収益試算'!AJ17</x:f>
-        <x:v>-126259.77144205733</x:v>
+        <x:v>-125359.72011713684</x:v>
       </x:c>
       <x:c r="H17" s="7" t="n">
         <x:f>'収益試算'!AK17</x:f>
-        <x:v>-276259.77144205733</x:v>
+        <x:v>-275359.72011713684</x:v>
       </x:c>
       <x:c r="I17" s="7" t="n">
         <x:f>'収益試算'!AL17</x:f>
-        <x:v>-176259.77144205733</x:v>
+        <x:v>-175359.72011713684</x:v>
       </x:c>
       <x:c r="J17" s="8" t="n">
         <x:f>'収益試算'!AO17</x:f>
-        <x:v>-0.42086590480685776</x:v>
+        <x:v>-0.41786573372378943</x:v>
       </x:c>
       <x:c r="K17" s="8" t="n">
         <x:f>'収益試算'!AP17</x:f>
-        <x:v>-0.6208659048068578</x:v>
+        <x:v>-0.6178657337237894</x:v>
       </x:c>
       <x:c r="L17" s="1"/>
       <x:c r="M17" s="1"/>
@@ -1747,7 +1759,7 @@
       </x:c>
       <x:c r="E18" s="7" t="n">
         <x:f>'収益試算'!AF18</x:f>
-        <x:v>25648.679943847656</x:v>
+        <x:v>25267.528573849253</x:v>
       </x:c>
       <x:c r="F18" s="7" t="n">
         <x:f>SUM('収益試算'!AH18:AI18)</x:f>
@@ -1755,23 +1767,23 @@
       </x:c>
       <x:c r="G18" s="7" t="n">
         <x:f>'収益試算'!AJ18</x:f>
-        <x:v>415017.98672281904</x:v>
+        <x:v>415399.1380928174</x:v>
       </x:c>
       <x:c r="H18" s="7" t="n">
         <x:f>'収益試算'!AK18</x:f>
-        <x:v>165017.98672281904</x:v>
+        <x:v>165399.1380928174</x:v>
       </x:c>
       <x:c r="I18" s="7" t="n">
         <x:f>'収益試算'!AL18</x:f>
-        <x:v>365017.98672281904</x:v>
+        <x:v>365399.1380928174</x:v>
       </x:c>
       <x:c r="J18" s="8" t="n">
         <x:f>'収益試算'!AO18</x:f>
-        <x:v>0.8300359734456381</x:v>
+        <x:v>0.8307982761856347</x:v>
       </x:c>
       <x:c r="K18" s="8" t="n">
         <x:f>'収益試算'!AP18</x:f>
-        <x:v>0.630035973445638</x:v>
+        <x:v>0.6307982761856348</x:v>
       </x:c>
       <x:c r="L18" s="1"/>
       <x:c r="M18" s="1"/>
@@ -1835,7 +1847,7 @@
       </x:c>
       <x:c r="E19" s="7" t="n">
         <x:f>'収益試算'!AF19</x:f>
-        <x:v>59613.13727539062</x:v>
+        <x:v>59093.997194755626</x:v>
       </x:c>
       <x:c r="F19" s="7" t="n">
         <x:f>SUM('収益試算'!AH19:AI19)</x:f>
@@ -1843,23 +1855,23 @@
       </x:c>
       <x:c r="G19" s="7" t="n">
         <x:f>'収益試算'!AJ19</x:f>
-        <x:v>347720.1960579427</x:v>
+        <x:v>348239.3361385777</x:v>
       </x:c>
       <x:c r="H19" s="7" t="n">
         <x:f>'収益試算'!AK19</x:f>
-        <x:v>97720.1960579427</x:v>
+        <x:v>98239.33613857772</x:v>
       </x:c>
       <x:c r="I19" s="7" t="n">
         <x:f>'収益試算'!AL19</x:f>
-        <x:v>297720.1960579427</x:v>
+        <x:v>298239.3361385777</x:v>
       </x:c>
       <x:c r="J19" s="8" t="n">
         <x:f>'収益試算'!AO19</x:f>
-        <x:v>0.6954403921158854</x:v>
+        <x:v>0.6964786722771554</x:v>
       </x:c>
       <x:c r="K19" s="8" t="n">
         <x:f>'収益試算'!AP19</x:f>
-        <x:v>0.49544039211588536</x:v>
+        <x:v>0.4964786722771554</x:v>
       </x:c>
       <x:c r="L19" s="1"/>
       <x:c r="M19" s="1"/>
@@ -1923,7 +1935,7 @@
       </x:c>
       <x:c r="E20" s="7" t="n">
         <x:f>'収益試算'!AF20</x:f>
-        <x:v>1026174.8191015625</x:v>
+        <x:v>1023685.3055466022</x:v>
       </x:c>
       <x:c r="F20" s="7" t="n">
         <x:f>SUM('収益試算'!AH20:AI20)</x:f>
@@ -1931,23 +1943,23 @@
       </x:c>
       <x:c r="G20" s="7" t="n">
         <x:f>'収益試算'!AJ20</x:f>
-        <x:v>-698841.4857682292</x:v>
+        <x:v>-696351.972213269</x:v>
       </x:c>
       <x:c r="H20" s="7" t="n">
         <x:f>'収益試算'!AK20</x:f>
-        <x:v>-948841.4857682292</x:v>
+        <x:v>-946351.972213269</x:v>
       </x:c>
       <x:c r="I20" s="7" t="n">
         <x:f>'収益試算'!AL20</x:f>
-        <x:v>-748841.4857682292</x:v>
+        <x:v>-746351.972213269</x:v>
       </x:c>
       <x:c r="J20" s="8" t="n">
         <x:f>'収益試算'!AO20</x:f>
-        <x:v>-1.3976829715364585</x:v>
+        <x:v>-1.3927039444265379</x:v>
       </x:c>
       <x:c r="K20" s="8" t="n">
         <x:f>'収益試算'!AP20</x:f>
-        <x:v>-1.5976829715364584</x:v>
+        <x:v>-1.5927039444265378</x:v>
       </x:c>
       <x:c r="L20" s="1"/>
       <x:c r="M20" s="1"/>
@@ -2011,7 +2023,7 @@
       </x:c>
       <x:c r="E21" s="7" t="n">
         <x:f>'収益試算'!AF21</x:f>
-        <x:v>35622.89985961914</x:v>
+        <x:v>35225.367306983775</x:v>
       </x:c>
       <x:c r="F21" s="7" t="n">
         <x:f>SUM('収益試算'!AH21:AI21)</x:f>
@@ -2019,23 +2031,23 @@
       </x:c>
       <x:c r="G21" s="7" t="n">
         <x:f>'収益試算'!AJ21</x:f>
-        <x:v>674243.7668070475</x:v>
+        <x:v>674641.299359683</x:v>
       </x:c>
       <x:c r="H21" s="7" t="n">
         <x:f>'収益試算'!AK21</x:f>
-        <x:v>274243.76680704753</x:v>
+        <x:v>274641.29935968295</x:v>
       </x:c>
       <x:c r="I21" s="7" t="n">
         <x:f>'収益試算'!AL21</x:f>
-        <x:v>624243.7668070475</x:v>
+        <x:v>624641.299359683</x:v>
       </x:c>
       <x:c r="J21" s="8" t="n">
         <x:f>'収益試算'!AO21</x:f>
-        <x:v>0.8428047085088094</x:v>
+        <x:v>0.8433016241996036</x:v>
       </x:c>
       <x:c r="K21" s="8" t="n">
         <x:f>'収益試算'!AP21</x:f>
-        <x:v>0.6428047085088093</x:v>
+        <x:v>0.6433016241996037</x:v>
       </x:c>
       <x:c r="L21" s="1"/>
       <x:c r="M21" s="1"/>
@@ -2099,7 +2111,7 @@
       </x:c>
       <x:c r="E22" s="7" t="n">
         <x:f>'収益試算'!AF22</x:f>
-        <x:v>120534.04318847656</x:v>
+        <x:v>119791.5388592497</x:v>
       </x:c>
       <x:c r="F22" s="7" t="n">
         <x:f>SUM('収益試算'!AH22:AI22)</x:f>
@@ -2107,23 +2119,23 @@
       </x:c>
       <x:c r="G22" s="7" t="n">
         <x:f>'収益試算'!AJ22</x:f>
-        <x:v>555999.2901448568</x:v>
+        <x:v>556741.7944740837</x:v>
       </x:c>
       <x:c r="H22" s="7" t="n">
         <x:f>'収益試算'!AK22</x:f>
-        <x:v>155999.2901448568</x:v>
+        <x:v>156741.7944740837</x:v>
       </x:c>
       <x:c r="I22" s="7" t="n">
         <x:f>'収益試算'!AL22</x:f>
-        <x:v>505999.2901448568</x:v>
+        <x:v>506741.7944740837</x:v>
       </x:c>
       <x:c r="J22" s="8" t="n">
         <x:f>'収益試算'!AO22</x:f>
-        <x:v>0.694999112681071</x:v>
+        <x:v>0.6959272430926047</x:v>
       </x:c>
       <x:c r="K22" s="8" t="n">
         <x:f>'収益試算'!AP22</x:f>
-        <x:v>0.49499911268107094</x:v>
+        <x:v>0.49592724309260466</x:v>
       </x:c>
       <x:c r="L22" s="1"/>
       <x:c r="M22" s="1"/>
@@ -2187,7 +2199,7 @@
       </x:c>
       <x:c r="E23" s="7" t="n">
         <x:f>'収益試算'!AF23</x:f>
-        <x:v>2541539.0477539063</x:v>
+        <x:v>2535383.825085315</x:v>
       </x:c>
       <x:c r="F23" s="7" t="n">
         <x:f>SUM('収益試算'!AH23:AI23)</x:f>
@@ -2195,23 +2207,23 @@
       </x:c>
       <x:c r="G23" s="7" t="n">
         <x:f>'収益試算'!AJ23</x:f>
-        <x:v>-1945005.7144205729</x:v>
+        <x:v>-1938850.4917519814</x:v>
       </x:c>
       <x:c r="H23" s="7" t="n">
         <x:f>'収益試算'!AK23</x:f>
-        <x:v>-2345005.714420573</x:v>
+        <x:v>-2338850.4917519814</x:v>
       </x:c>
       <x:c r="I23" s="7" t="n">
         <x:f>'収益試算'!AL23</x:f>
-        <x:v>-1995005.7144205729</x:v>
+        <x:v>-1988850.4917519814</x:v>
       </x:c>
       <x:c r="J23" s="8" t="n">
         <x:f>'収益試算'!AO23</x:f>
-        <x:v>-2.431257143025716</x:v>
+        <x:v>-2.4235631146899768</x:v>
       </x:c>
       <x:c r="K23" s="8" t="n">
         <x:f>'収益試算'!AP23</x:f>
-        <x:v>-2.6312571430257163</x:v>
+        <x:v>-2.623563114689977</x:v>
       </x:c>
       <x:c r="L23" s="1"/>
       <x:c r="M23" s="1"/>
@@ -2275,7 +2287,7 @@
       </x:c>
       <x:c r="E24" s="7" t="n">
         <x:f>'収益試算'!AF24</x:f>
-        <x:v>47311.04992980957</x:v>
+        <x:v>46927.168362705</x:v>
       </x:c>
       <x:c r="F24" s="7" t="n">
         <x:f>SUM('収益試算'!AH24:AI24)</x:f>
@@ -2283,23 +2295,23 @@
       </x:c>
       <x:c r="G24" s="7" t="n">
         <x:f>'収益試算'!AJ24</x:f>
-        <x:v>1274022.2834035237</x:v>
+        <x:v>1274406.1649706285</x:v>
       </x:c>
       <x:c r="H24" s="7" t="n">
         <x:f>'収益試算'!AK24</x:f>
-        <x:v>524022.28340352373</x:v>
+        <x:v>524406.1649706285</x:v>
       </x:c>
       <x:c r="I24" s="7" t="n">
         <x:f>'収益試算'!AL24</x:f>
-        <x:v>1024022.2834035237</x:v>
+        <x:v>1024406.1649706285</x:v>
       </x:c>
       <x:c r="J24" s="8" t="n">
         <x:f>'収益試算'!AO24</x:f>
-        <x:v>0.8493481889356825</x:v>
+        <x:v>0.849604109980419</x:v>
       </x:c>
       <x:c r="K24" s="8" t="n">
         <x:f>'収益試算'!AP24</x:f>
-        <x:v>0.6493481889356825</x:v>
+        <x:v>0.6496041099804191</x:v>
       </x:c>
       <x:c r="L24" s="1"/>
       <x:c r="M24" s="1"/>
@@ -2363,7 +2375,7 @@
       </x:c>
       <x:c r="E25" s="7" t="n">
         <x:f>'収益試算'!AF25</x:f>
-        <x:v>89766.62159423828</x:v>
+        <x:v>89210.25413883798</x:v>
       </x:c>
       <x:c r="F25" s="7" t="n">
         <x:f>SUM('収益試算'!AH25:AI25)</x:f>
@@ -2371,23 +2383,23 @@
       </x:c>
       <x:c r="G25" s="7" t="n">
         <x:f>'収益試算'!AJ25</x:f>
-        <x:v>1064900.0450724284</x:v>
+        <x:v>1065456.4125278287</x:v>
       </x:c>
       <x:c r="H25" s="7" t="n">
         <x:f>'収益試算'!AK25</x:f>
-        <x:v>314900.0450724284</x:v>
+        <x:v>315456.4125278287</x:v>
       </x:c>
       <x:c r="I25" s="7" t="n">
         <x:f>'収益試算'!AL25</x:f>
-        <x:v>814900.0450724284</x:v>
+        <x:v>815456.4125278287</x:v>
       </x:c>
       <x:c r="J25" s="8" t="n">
         <x:f>'収益試算'!AO25</x:f>
-        <x:v>0.7099333633816189</x:v>
+        <x:v>0.7103042750185524</x:v>
       </x:c>
       <x:c r="K25" s="8" t="n">
         <x:f>'収益試算'!AP25</x:f>
-        <x:v>0.509933363381619</x:v>
+        <x:v>0.5103042750185525</x:v>
       </x:c>
       <x:c r="L25" s="1"/>
       <x:c r="M25" s="1"/>
@@ -2451,7 +2463,7 @@
       </x:c>
       <x:c r="E26" s="7" t="n">
         <x:f>'収益試算'!AF26</x:f>
-        <x:v>1298519.5238769532</x:v>
+        <x:v>1295441.9125426577</x:v>
       </x:c>
       <x:c r="F26" s="7" t="n">
         <x:f>SUM('収益試算'!AH26:AI26)</x:f>
@@ -2459,23 +2471,23 @@
       </x:c>
       <x:c r="G26" s="7" t="n">
         <x:f>'収益試算'!AJ26</x:f>
-        <x:v>-543852.8572102864</x:v>
+        <x:v>-540775.245875991</x:v>
       </x:c>
       <x:c r="H26" s="7" t="n">
         <x:f>'収益試算'!AK26</x:f>
-        <x:v>-1293852.8572102864</x:v>
+        <x:v>-1290775.245875991</x:v>
       </x:c>
       <x:c r="I26" s="7" t="n">
         <x:f>'収益試算'!AL26</x:f>
-        <x:v>-793852.8572102864</x:v>
+        <x:v>-790775.245875991</x:v>
       </x:c>
       <x:c r="J26" s="8" t="n">
         <x:f>'収益試算'!AO26</x:f>
-        <x:v>-0.3625685714735243</x:v>
+        <x:v>-0.360516830583994</x:v>
       </x:c>
       <x:c r="K26" s="8" t="n">
         <x:f>'収益試算'!AP26</x:f>
-        <x:v>-0.5625685714735242</x:v>
+        <x:v>-0.560516830583994</x:v>
       </x:c>
       <x:c r="L26" s="1"/>
       <x:c r="M26" s="1"/>
@@ -2539,7 +2551,7 @@
       </x:c>
       <x:c r="E27" s="7" t="n">
         <x:f>'収益試算'!AF27</x:f>
-        <x:v>72246.59971923828</x:v>
+        <x:v>71821.76519554132</x:v>
       </x:c>
       <x:c r="F27" s="7" t="n">
         <x:f>SUM('収益試算'!AH27:AI27)</x:f>
@@ -2547,23 +2559,23 @@
       </x:c>
       <x:c r="G27" s="7" t="n">
         <x:f>'収益試算'!AJ27</x:f>
-        <x:v>2163086.733614095</x:v>
+        <x:v>2163511.568137792</x:v>
       </x:c>
       <x:c r="H27" s="7" t="n">
         <x:f>'収益試算'!AK27</x:f>
-        <x:v>913086.733614095</x:v>
+        <x:v>913511.5681377919</x:v>
       </x:c>
       <x:c r="I27" s="7" t="n">
         <x:f>'収益試算'!AL27</x:f>
-        <x:v>1913086.733614095</x:v>
+        <x:v>1913511.568137792</x:v>
       </x:c>
       <x:c r="J27" s="8" t="n">
         <x:f>'収益試算'!AO27</x:f>
-        <x:v>0.865234693445638</x:v>
+        <x:v>0.8654046272551168</x:v>
       </x:c>
       <x:c r="K27" s="8" t="n">
         <x:f>'収益試算'!AP27</x:f>
-        <x:v>0.6652346934456379</x:v>
+        <x:v>0.6654046272551168</x:v>
       </x:c>
       <x:c r="L27" s="1"/>
       <x:c r="M27" s="1"/>
@@ -2627,7 +2639,7 @@
       </x:c>
       <x:c r="E28" s="7" t="n">
         <x:f>'収益試算'!AF28</x:f>
-        <x:v>242068.88637695313</x:v>
+        <x:v>240954.10830007316</x:v>
       </x:c>
       <x:c r="F28" s="7" t="n">
         <x:f>SUM('収益試算'!AH28:AI28)</x:f>
@@ -2635,23 +2647,23 @@
       </x:c>
       <x:c r="G28" s="7" t="n">
         <x:f>'収益試算'!AJ28</x:f>
-        <x:v>1826597.7802897135</x:v>
+        <x:v>1827712.5583665934</x:v>
       </x:c>
       <x:c r="H28" s="7" t="n">
         <x:f>'収益試算'!AK28</x:f>
-        <x:v>576597.7802897135</x:v>
+        <x:v>577712.5583665934</x:v>
       </x:c>
       <x:c r="I28" s="7" t="n">
         <x:f>'収益試算'!AL28</x:f>
-        <x:v>1576597.7802897135</x:v>
+        <x:v>1577712.5583665934</x:v>
       </x:c>
       <x:c r="J28" s="8" t="n">
         <x:f>'収益試算'!AO28</x:f>
-        <x:v>0.7306391121158854</x:v>
+        <x:v>0.7310850233466374</x:v>
       </x:c>
       <x:c r="K28" s="8" t="n">
         <x:f>'収益試算'!AP28</x:f>
-        <x:v>0.5306391121158853</x:v>
+        <x:v>0.5310850233466373</x:v>
       </x:c>
       <x:c r="L28" s="1"/>
       <x:c r="M28" s="1"/>
@@ -2715,7 +2727,7 @@
       </x:c>
       <x:c r="E29" s="7" t="n">
         <x:f>'収益試算'!AF29</x:f>
-        <x:v>5087578.095507813</x:v>
+        <x:v>5075267.650170631</x:v>
       </x:c>
       <x:c r="F29" s="7" t="n">
         <x:f>SUM('収益試算'!AH29:AI29)</x:f>
@@ -2723,23 +2735,23 @@
       </x:c>
       <x:c r="G29" s="7" t="n">
         <x:f>'収益試算'!AJ29</x:f>
-        <x:v>-3418911.4288411457</x:v>
+        <x:v>-3406600.983503964</x:v>
       </x:c>
       <x:c r="H29" s="7" t="n">
         <x:f>'収益試算'!AK29</x:f>
-        <x:v>-4668911.428841146</x:v>
+        <x:v>-4656600.983503964</x:v>
       </x:c>
       <x:c r="I29" s="7" t="n">
         <x:f>'収益試算'!AL29</x:f>
-        <x:v>-3668911.4288411457</x:v>
+        <x:v>-3656600.983503964</x:v>
       </x:c>
       <x:c r="J29" s="8" t="n">
         <x:f>'収益試算'!AO29</x:f>
-        <x:v>-1.3675645715364584</x:v>
+        <x:v>-1.3626403934015856</x:v>
       </x:c>
       <x:c r="K29" s="8" t="n">
         <x:f>'収益試算'!AP29</x:f>
-        <x:v>-1.5675645715364583</x:v>
+        <x:v>-1.5626403934015856</x:v>
       </x:c>
       <x:c r="L29" s="1"/>
       <x:c r="M29" s="1"/>
@@ -2803,7 +2815,7 @@
       </x:c>
       <x:c r="E30" s="7" t="n">
         <x:f>'収益試算'!AF30</x:f>
-        <x:v>122117.6992980957</x:v>
+        <x:v>121610.95886121393</x:v>
       </x:c>
       <x:c r="F30" s="7" t="n">
         <x:f>SUM('収益試算'!AH30:AI30)</x:f>
@@ -2811,23 +2823,23 @@
       </x:c>
       <x:c r="G30" s="7" t="n">
         <x:f>'収益試算'!AJ30</x:f>
-        <x:v>3459215.6340352376</x:v>
+        <x:v>3459722.3744721194</x:v>
       </x:c>
       <x:c r="H30" s="7" t="n">
         <x:f>'収益試算'!AK30</x:f>
-        <x:v>1459215.6340352376</x:v>
+        <x:v>1459722.3744721194</x:v>
       </x:c>
       <x:c r="I30" s="7" t="n">
         <x:f>'収益試算'!AL30</x:f>
-        <x:v>3209215.6340352376</x:v>
+        <x:v>3209722.3744721194</x:v>
       </x:c>
       <x:c r="J30" s="8" t="n">
         <x:f>'収益試算'!AO30</x:f>
-        <x:v>0.8648039085088094</x:v>
+        <x:v>0.8649305936180298</x:v>
       </x:c>
       <x:c r="K30" s="8" t="n">
         <x:f>'収益試算'!AP30</x:f>
-        <x:v>0.6648039085088093</x:v>
+        <x:v>0.6649305936180299</x:v>
       </x:c>
       <x:c r="L30" s="1"/>
       <x:c r="M30" s="1"/>
@@ -2891,7 +2903,7 @@
       </x:c>
       <x:c r="E31" s="7" t="n">
         <x:f>'収益試算'!AF31</x:f>
-        <x:v>546673.4159423828</x:v>
+        <x:v>544441.8166225436</x:v>
       </x:c>
       <x:c r="F31" s="7" t="n">
         <x:f>SUM('収益試算'!AH31:AI31)</x:f>
@@ -2899,23 +2911,23 @@
       </x:c>
       <x:c r="G31" s="7" t="n">
         <x:f>'収益試算'!AJ31</x:f>
-        <x:v>2867993.250724284</x:v>
+        <x:v>2870224.850044123</x:v>
       </x:c>
       <x:c r="H31" s="7" t="n">
         <x:f>'収益試算'!AK31</x:f>
-        <x:v>867993.250724284</x:v>
+        <x:v>870224.8500441229</x:v>
       </x:c>
       <x:c r="I31" s="7" t="n">
         <x:f>'収益試算'!AL31</x:f>
-        <x:v>2617993.250724284</x:v>
+        <x:v>2620224.850044123</x:v>
       </x:c>
       <x:c r="J31" s="8" t="n">
         <x:f>'収益試算'!AO31</x:f>
-        <x:v>0.716998312681071</x:v>
+        <x:v>0.7175562125110307</x:v>
       </x:c>
       <x:c r="K31" s="8" t="n">
         <x:f>'収益試算'!AP31</x:f>
-        <x:v>0.5169983126810709</x:v>
+        <x:v>0.5175562125110307</x:v>
       </x:c>
       <x:c r="L31" s="1"/>
       <x:c r="M31" s="1"/>
@@ -2979,7 +2991,7 @@
       </x:c>
       <x:c r="E32" s="7" t="n">
         <x:f>'収益試算'!AF32</x:f>
-        <x:v>12665695.238769531</x:v>
+        <x:v>12634919.125426577</x:v>
       </x:c>
       <x:c r="F32" s="7" t="n">
         <x:f>SUM('収益試算'!AH32:AI32)</x:f>
@@ -2987,23 +2999,23 @@
       </x:c>
       <x:c r="G32" s="7" t="n">
         <x:f>'収益試算'!AJ32</x:f>
-        <x:v>-9651028.572102865</x:v>
+        <x:v>-9620252.458759911</x:v>
       </x:c>
       <x:c r="H32" s="7" t="n">
         <x:f>'収益試算'!AK32</x:f>
-        <x:v>-11651028.572102865</x:v>
+        <x:v>-11620252.458759911</x:v>
       </x:c>
       <x:c r="I32" s="7" t="n">
         <x:f>'収益試算'!AL32</x:f>
-        <x:v>-9901028.572102865</x:v>
+        <x:v>-9870252.458759911</x:v>
       </x:c>
       <x:c r="J32" s="8" t="n">
         <x:f>'収益試算'!AO32</x:f>
-        <x:v>-2.412757143025716</x:v>
+        <x:v>-2.4050631146899777</x:v>
       </x:c>
       <x:c r="K32" s="8" t="n">
         <x:f>'収益試算'!AP32</x:f>
-        <x:v>-2.6127571430257164</x:v>
+        <x:v>-2.605063114689978</x:v>
       </x:c>
       <x:c r="L32" s="1"/>
       <x:c r="M32" s="1"/>
@@ -3067,7 +3079,7 @@
       </x:c>
       <x:c r="E33" s="7" t="n">
         <x:f>'収益試算'!AF33</x:f>
-        <x:v>80622.89985961914</x:v>
+        <x:v>80225.36730698377</x:v>
       </x:c>
       <x:c r="F33" s="7" t="n">
         <x:f>SUM('収益試算'!AH33:AI33)</x:f>
@@ -3075,23 +3087,23 @@
       </x:c>
       <x:c r="G33" s="7" t="n">
         <x:f>'収益試算'!AJ33</x:f>
-        <x:v>2570043.7668070477</x:v>
+        <x:v>2570441.299359683</x:v>
       </x:c>
       <x:c r="H33" s="7" t="n">
         <x:f>'収益試算'!AK33</x:f>
-        <x:v>1070043.7668070477</x:v>
+        <x:v>1070441.299359683</x:v>
       </x:c>
       <x:c r="I33" s="7" t="n">
         <x:f>'収益試算'!AL33</x:f>
-        <x:v>2070043.7668070477</x:v>
+        <x:v>2070441.299359683</x:v>
       </x:c>
       <x:c r="J33" s="8" t="n">
         <x:f>'収益試算'!AO33</x:f>
-        <x:v>0.8566812556023492</x:v>
+        <x:v>0.8568137664532276</x:v>
       </x:c>
       <x:c r="K33" s="8" t="n">
         <x:f>'収益試算'!AP33</x:f>
-        <x:v>0.6566812556023491</x:v>
+        <x:v>0.6568137664532276</x:v>
       </x:c>
       <x:c r="L33" s="1"/>
       <x:c r="M33" s="1"/>
@@ -3155,7 +3167,7 @@
       </x:c>
       <x:c r="E34" s="7" t="n">
         <x:f>'収益試算'!AF34</x:f>
-        <x:v>165534.0431884766</x:v>
+        <x:v>164791.5388592497</x:v>
       </x:c>
       <x:c r="F34" s="7" t="n">
         <x:f>SUM('収益試算'!AH34:AI34)</x:f>
@@ -3163,23 +3175,23 @@
       </x:c>
       <x:c r="G34" s="7" t="n">
         <x:f>'収益試算'!AJ34</x:f>
-        <x:v>2151799.290144857</x:v>
+        <x:v>2152541.794474084</x:v>
       </x:c>
       <x:c r="H34" s="7" t="n">
         <x:f>'収益試算'!AK34</x:f>
-        <x:v>651799.290144857</x:v>
+        <x:v>652541.7944740839</x:v>
       </x:c>
       <x:c r="I34" s="7" t="n">
         <x:f>'収益試算'!AL34</x:f>
-        <x:v>1651799.290144857</x:v>
+        <x:v>1652541.794474084</x:v>
       </x:c>
       <x:c r="J34" s="8" t="n">
         <x:f>'収益試算'!AO34</x:f>
-        <x:v>0.7172664300482857</x:v>
+        <x:v>0.7175139314913613</x:v>
       </x:c>
       <x:c r="K34" s="8" t="n">
         <x:f>'収益試算'!AP34</x:f>
-        <x:v>0.5172664300482857</x:v>
+        <x:v>0.5175139314913613</x:v>
       </x:c>
       <x:c r="L34" s="1"/>
       <x:c r="M34" s="1"/>
@@ -3243,7 +3255,7 @@
       </x:c>
       <x:c r="E35" s="7" t="n">
         <x:f>'収益試算'!AF35</x:f>
-        <x:v>2586539.0477539063</x:v>
+        <x:v>2580383.825085315</x:v>
       </x:c>
       <x:c r="F35" s="7" t="n">
         <x:f>SUM('収益試算'!AH35:AI35)</x:f>
@@ -3251,23 +3263,23 @@
       </x:c>
       <x:c r="G35" s="7" t="n">
         <x:f>'収益試算'!AJ35</x:f>
-        <x:v>-1069205.7144205729</x:v>
+        <x:v>-1063050.491751982</x:v>
       </x:c>
       <x:c r="H35" s="7" t="n">
         <x:f>'収益試算'!AK35</x:f>
-        <x:v>-2569205.714420573</x:v>
+        <x:v>-2563050.491751982</x:v>
       </x:c>
       <x:c r="I35" s="7" t="n">
         <x:f>'収益試算'!AL35</x:f>
-        <x:v>-1569205.7144205729</x:v>
+        <x:v>-1563050.491751982</x:v>
       </x:c>
       <x:c r="J35" s="8" t="n">
         <x:f>'収益試算'!AO35</x:f>
-        <x:v>-0.35640190480685763</x:v>
+        <x:v>-0.3543501639173273</x:v>
       </x:c>
       <x:c r="K35" s="8" t="n">
         <x:f>'収益試算'!AP35</x:f>
-        <x:v>-0.5564019048068576</x:v>
+        <x:v>-0.5543501639173274</x:v>
       </x:c>
       <x:c r="L35" s="1"/>
       <x:c r="M35" s="1"/>
@@ -3331,7 +3343,7 @@
       </x:c>
       <x:c r="E36" s="7" t="n">
         <x:f>'収益試算'!AF36</x:f>
-        <x:v>130493.99943847656</x:v>
+        <x:v>130014.56097265639</x:v>
       </x:c>
       <x:c r="F36" s="7" t="n">
         <x:f>SUM('収益試算'!AH36:AI36)</x:f>
@@ -3339,23 +3351,23 @@
       </x:c>
       <x:c r="G36" s="7" t="n">
         <x:f>'収益試算'!AJ36</x:f>
-        <x:v>4348172.66722819</x:v>
+        <x:v>4348652.105694011</x:v>
       </x:c>
       <x:c r="H36" s="7" t="n">
         <x:f>'収益試算'!AK36</x:f>
-        <x:v>1848172.6672281902</x:v>
+        <x:v>1848652.1056940109</x:v>
       </x:c>
       <x:c r="I36" s="7" t="n">
         <x:f>'収益試算'!AL36</x:f>
-        <x:v>3848172.66722819</x:v>
+        <x:v>3848652.105694011</x:v>
       </x:c>
       <x:c r="J36" s="8" t="n">
         <x:f>'収益試算'!AO36</x:f>
-        <x:v>0.869634533445638</x:v>
+        <x:v>0.8697304211388022</x:v>
       </x:c>
       <x:c r="K36" s="8" t="n">
         <x:f>'収益試算'!AP36</x:f>
-        <x:v>0.669634533445638</x:v>
+        <x:v>0.6697304211388022</x:v>
       </x:c>
       <x:c r="L36" s="1"/>
       <x:c r="M36" s="1"/>
@@ -3419,7 +3431,7 @@
       </x:c>
       <x:c r="E37" s="7" t="n">
         <x:f>'収益試算'!AF37</x:f>
-        <x:v>470138.57275390625</x:v>
+        <x:v>468279.24718172004</x:v>
       </x:c>
       <x:c r="F37" s="7" t="n">
         <x:f>SUM('収益試算'!AH37:AI37)</x:f>
@@ -3427,23 +3439,23 @@
       </x:c>
       <x:c r="G37" s="7" t="n">
         <x:f>'収益試算'!AJ37</x:f>
-        <x:v>3675194.7605794272</x:v>
+        <x:v>3677054.0861516134</x:v>
       </x:c>
       <x:c r="H37" s="7" t="n">
         <x:f>'収益試算'!AK37</x:f>
-        <x:v>1175194.7605794272</x:v>
+        <x:v>1177054.0861516134</x:v>
       </x:c>
       <x:c r="I37" s="7" t="n">
         <x:f>'収益試算'!AL37</x:f>
-        <x:v>3175194.7605794272</x:v>
+        <x:v>3177054.0861516134</x:v>
       </x:c>
       <x:c r="J37" s="8" t="n">
         <x:f>'収益試算'!AO37</x:f>
-        <x:v>0.7350389521158854</x:v>
+        <x:v>0.7354108172303226</x:v>
       </x:c>
       <x:c r="K37" s="8" t="n">
         <x:f>'収益試算'!AP37</x:f>
-        <x:v>0.5350389521158854</x:v>
+        <x:v>0.5354108172303227</x:v>
       </x:c>
       <x:c r="L37" s="1"/>
       <x:c r="M37" s="1"/>
@@ -3507,7 +3519,7 @@
       </x:c>
       <x:c r="E38" s="7" t="n">
         <x:f>'収益試算'!AF38</x:f>
-        <x:v>10164656.191015624</x:v>
+        <x:v>10140035.300341262</x:v>
       </x:c>
       <x:c r="F38" s="7" t="n">
         <x:f>SUM('収益試算'!AH38:AI38)</x:f>
@@ -3515,23 +3527,23 @@
       </x:c>
       <x:c r="G38" s="7" t="n">
         <x:f>'収益試算'!AJ38</x:f>
-        <x:v>-6819322.85768229</x:v>
+        <x:v>-6794701.967007928</x:v>
       </x:c>
       <x:c r="H38" s="7" t="n">
         <x:f>'収益試算'!AK38</x:f>
-        <x:v>-9319322.85768229</x:v>
+        <x:v>-9294701.967007928</x:v>
       </x:c>
       <x:c r="I38" s="7" t="n">
         <x:f>'収益試算'!AL38</x:f>
-        <x:v>-7319322.85768229</x:v>
+        <x:v>-7294701.967007928</x:v>
       </x:c>
       <x:c r="J38" s="8" t="n">
         <x:f>'収益試算'!AO38</x:f>
-        <x:v>-1.363864571536458</x:v>
+        <x:v>-1.3589403934015856</x:v>
       </x:c>
       <x:c r="K38" s="8" t="n">
         <x:f>'収益試算'!AP38</x:f>
-        <x:v>-1.5638645715364579</x:v>
+        <x:v>-1.5589403934015855</x:v>
       </x:c>
       <x:c r="L38" s="1"/>
       <x:c r="M38" s="1"/>
@@ -3595,7 +3607,7 @@
       </x:c>
       <x:c r="E39" s="7" t="n">
         <x:f>'収益試算'!AF39</x:f>
-        <x:v>230236.19859619142</x:v>
+        <x:v>229592.94830400162</x:v>
       </x:c>
       <x:c r="F39" s="7" t="n">
         <x:f>SUM('収益試算'!AH39:AI39)</x:f>
@@ -3603,23 +3615,23 @@
       </x:c>
       <x:c r="G39" s="7" t="n">
         <x:f>'収益試算'!AJ39</x:f>
-        <x:v>6940430.468070475</x:v>
+        <x:v>6941073.718362665</x:v>
       </x:c>
       <x:c r="H39" s="7" t="n">
         <x:f>'収益試算'!AK39</x:f>
-        <x:v>2940430.4680704754</x:v>
+        <x:v>2941073.718362665</x:v>
       </x:c>
       <x:c r="I39" s="7" t="n">
         <x:f>'収益試算'!AL39</x:f>
-        <x:v>6440430.468070475</x:v>
+        <x:v>6441073.718362665</x:v>
       </x:c>
       <x:c r="J39" s="8" t="n">
         <x:f>'収益試算'!AO39</x:f>
-        <x:v>0.8675538085088095</x:v>
+        <x:v>0.8676342147953331</x:v>
       </x:c>
       <x:c r="K39" s="8" t="n">
         <x:f>'収益試算'!AP39</x:f>
-        <x:v>0.6675538085088095</x:v>
+        <x:v>0.6676342147953331</x:v>
       </x:c>
       <x:c r="L39" s="1"/>
       <x:c r="M39" s="1"/>
@@ -3683,7 +3695,7 @@
       </x:c>
       <x:c r="E40" s="7" t="n">
         <x:f>'収益試算'!AF40</x:f>
-        <x:v>1081248.4318847656</x:v>
+        <x:v>1076954.3509181517</x:v>
       </x:c>
       <x:c r="F40" s="7" t="n">
         <x:f>SUM('収益試算'!AH40:AI40)</x:f>
@@ -3691,23 +3703,23 @@
       </x:c>
       <x:c r="G40" s="7" t="n">
         <x:f>'収益試算'!AJ40</x:f>
-        <x:v>5756084.901448568</x:v>
+        <x:v>5760378.982415182</x:v>
       </x:c>
       <x:c r="H40" s="7" t="n">
         <x:f>'収益試算'!AK40</x:f>
-        <x:v>1756084.9014485683</x:v>
+        <x:v>1760378.9824151816</x:v>
       </x:c>
       <x:c r="I40" s="7" t="n">
         <x:f>'収益試算'!AL40</x:f>
-        <x:v>5256084.901448568</x:v>
+        <x:v>5260378.982415182</x:v>
       </x:c>
       <x:c r="J40" s="8" t="n">
         <x:f>'収益試算'!AO40</x:f>
-        <x:v>0.7195106126810711</x:v>
+        <x:v>0.7200473728018977</x:v>
       </x:c>
       <x:c r="K40" s="8" t="n">
         <x:f>'収益試算'!AP40</x:f>
-        <x:v>0.5195106126810711</x:v>
+        <x:v>0.5200473728018977</x:v>
       </x:c>
       <x:c r="L40" s="1"/>
       <x:c r="M40" s="1"/>
@@ -3771,7 +3783,7 @@
       </x:c>
       <x:c r="E41" s="7" t="n">
         <x:f>'収益試算'!AF41</x:f>
-        <x:v>25320890.477539062</x:v>
+        <x:v>25259338.25085315</x:v>
       </x:c>
       <x:c r="F41" s="7" t="n">
         <x:f>SUM('収益試算'!AH41:AI41)</x:f>
@@ -3779,23 +3791,23 @@
       </x:c>
       <x:c r="G41" s="7" t="n">
         <x:f>'収益試算'!AJ41</x:f>
-        <x:v>-19283557.14420573</x:v>
+        <x:v>-19222004.91751982</x:v>
       </x:c>
       <x:c r="H41" s="7" t="n">
         <x:f>'収益試算'!AK41</x:f>
-        <x:v>-23283557.14420573</x:v>
+        <x:v>-23222004.91751982</x:v>
       </x:c>
       <x:c r="I41" s="7" t="n">
         <x:f>'収益試算'!AL41</x:f>
-        <x:v>-19783557.14420573</x:v>
+        <x:v>-19722004.91751982</x:v>
       </x:c>
       <x:c r="J41" s="8" t="n">
         <x:f>'収益試算'!AO41</x:f>
-        <x:v>-2.4104446430257163</x:v>
+        <x:v>-2.4027506146899773</x:v>
       </x:c>
       <x:c r="K41" s="8" t="n">
         <x:f>'収益試算'!AP41</x:f>
-        <x:v>-2.6104446430257164</x:v>
+        <x:v>-2.6027506146899775</x:v>
       </x:c>
       <x:c r="L41" s="1"/>
       <x:c r="M41" s="1"/>
@@ -7272,7 +7284,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>青字・淡黄色は変更可能。実測費用は未取得。公式参考単価と仮定を区別。</x:v>
+        <x:v>Run概算単価のみ請求CSVで校正。他の利用量・配賦予算は仮定。価格・人数・利用量は変更可能。</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -7582,16 +7594,16 @@
         <x:v>Cloud Run active CPU</x:v>
       </x:c>
       <x:c r="B8" s="6" t="n">
-        <x:v>0.000024</x:v>
+        <x:v>0.000025908257440771683</x:v>
       </x:c>
       <x:c r="C8" s="1" t="str">
         <x:v>USD/vCPU秒</x:v>
       </x:c>
       <x:c r="D8" s="1" t="str">
-        <x:v>公式参考</x:v>
+        <x:v>請求から逆算・概算</x:v>
       </x:c>
       <x:c r="E8" s="1" t="str">
-        <x:v>https://cloud.google.com/run/pricing （取得表はIowa。東京SKU未照合）</x:v>
+        <x:v>7〜9月の正規費用（円丸め）÷表示使用量÷150。将来単価保証なし。地域係数は1へ。</x:v>
       </x:c>
       <x:c r="F8" s="1"/>
       <x:c r="G8" s="1"/>
@@ -7647,16 +7659,16 @@
         <x:v>Cloud Run active memory</x:v>
       </x:c>
       <x:c r="B9" s="6" t="n">
-        <x:v>0.0000025</x:v>
+        <x:v>0.0000026351242296379006</x:v>
       </x:c>
       <x:c r="C9" s="1" t="str">
         <x:v>USD/GiB秒</x:v>
       </x:c>
       <x:c r="D9" s="1" t="str">
-        <x:v>公式参考</x:v>
+        <x:v>請求から逆算・概算</x:v>
       </x:c>
       <x:c r="E9" s="1" t="str">
-        <x:v>https://cloud.google.com/run/pricing</x:v>
+        <x:v>7〜9月の正規費用（円丸め）÷表示使用量÷150。将来単価保証なし。地域係数は1へ。</x:v>
       </x:c>
       <x:c r="F9" s="1"/>
       <x:c r="G9" s="1"/>
@@ -7712,16 +7724,16 @@
         <x:v>Cloud Run idle CPU</x:v>
       </x:c>
       <x:c r="B10" s="6" t="n">
-        <x:v>0.0000025</x:v>
+        <x:v>0.0000026834998308159128</x:v>
       </x:c>
       <x:c r="C10" s="1" t="str">
         <x:v>USD/vCPU秒</x:v>
       </x:c>
       <x:c r="D10" s="1" t="str">
-        <x:v>公式参考</x:v>
+        <x:v>請求から逆算・概算</x:v>
       </x:c>
       <x:c r="E10" s="1" t="str">
-        <x:v>https://cloud.google.com/run/pricing</x:v>
+        <x:v>7〜9月の正規費用（円丸め）÷表示使用量÷150。将来単価保証なし。地域係数は1へ。</x:v>
       </x:c>
       <x:c r="F10" s="1"/>
       <x:c r="G10" s="1"/>
@@ -7777,16 +7789,16 @@
         <x:v>Cloud Run idle memory</x:v>
       </x:c>
       <x:c r="B11" s="6" t="n">
-        <x:v>0.0000025</x:v>
+        <x:v>0.0000026821305095229113</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
         <x:v>USD/GiB秒</x:v>
       </x:c>
       <x:c r="D11" s="1" t="str">
-        <x:v>公式参考</x:v>
+        <x:v>請求から逆算・概算</x:v>
       </x:c>
       <x:c r="E11" s="1" t="str">
-        <x:v>https://cloud.google.com/run/pricing</x:v>
+        <x:v>7〜9月の正規費用（円丸め）÷表示使用量÷150。将来単価保証なし。地域係数は1へ。</x:v>
       </x:c>
       <x:c r="F11" s="1"/>
       <x:c r="G11" s="1"/>
@@ -7842,16 +7854,16 @@
         <x:v>Run地域補正係数</x:v>
       </x:c>
       <x:c r="B12" s="6" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="1" t="str">
         <x:v>倍</x:v>
       </x:c>
       <x:c r="D12" s="1" t="str">
-        <x:v>仮定</x:v>
+        <x:v>概算単価へ更新</x:v>
       </x:c>
       <x:c r="E12" s="1" t="str">
-        <x:v>東京単価ではない。SKU照合後に単価と係数を更新</x:v>
+        <x:v>日本SKU相当を逆算したため地域係数を重ねない。削減・無料枠を将来へ適用しない。</x:v>
       </x:c>
       <x:c r="F12" s="1"/>
       <x:c r="G12" s="1"/>
@@ -7913,10 +7925,10 @@
         <x:v>vCPU</x:v>
       </x:c>
       <x:c r="D13" s="1" t="str">
-        <x:v>仮定</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E13" s="1" t="str">
-        <x:v>現在値未取得</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F13" s="1"/>
       <x:c r="G13" s="1"/>
@@ -7978,10 +7990,10 @@
         <x:v>GiB</x:v>
       </x:c>
       <x:c r="D14" s="1" t="str">
-        <x:v>既存記録</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E14" s="1" t="str">
-        <x:v>d2fdd5b Fit/Gap、今回fresh未確認</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F14" s="1"/>
       <x:c r="G14" s="1"/>
@@ -8043,10 +8055,10 @@
         <x:v>台</x:v>
       </x:c>
       <x:c r="D15" s="1" t="str">
-        <x:v>既存記録</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
-        <x:v>d2fdd5b Fit/Gap、課金方式は未確認</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F15" s="1"/>
       <x:c r="G15" s="1"/>
@@ -9278,10 +9290,10 @@
         <x:v>日</x:v>
       </x:c>
       <x:c r="D34" s="1" t="str">
-        <x:v>既存記録</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E34" s="1" t="str">
-        <x:v>GCS lifecycle記録。リンク期限7/14日とは異なる</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F34" s="1"/>
       <x:c r="G34" s="1"/>
@@ -9343,10 +9355,10 @@
         <x:v>日</x:v>
       </x:c>
       <x:c r="D35" s="1" t="str">
-        <x:v>仮定</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E35" s="1" t="str">
-        <x:v>soft delete設定未確認。実設定が無効なら0へ</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F35" s="1"/>
       <x:c r="G35" s="1"/>
@@ -9863,10 +9875,10 @@
         <x:v>vCPU</x:v>
       </x:c>
       <x:c r="D43" s="1" t="str">
-        <x:v>仮定</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E43" s="1" t="str">
-        <x:v>fresh未確認</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F43" s="1"/>
       <x:c r="G43" s="1"/>
@@ -9928,10 +9940,10 @@
         <x:v>GiB</x:v>
       </x:c>
       <x:c r="D44" s="1" t="str">
-        <x:v>既存記録</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E44" s="1" t="str">
-        <x:v>d2fdd5b Fit/Gap</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F44" s="1"/>
       <x:c r="G44" s="1"/>
@@ -9993,10 +10005,10 @@
         <x:v>vCPU</x:v>
       </x:c>
       <x:c r="D45" s="1" t="str">
-        <x:v>仮定</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E45" s="1" t="str">
-        <x:v>fresh未確認</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F45" s="1"/>
       <x:c r="G45" s="1"/>
@@ -10058,10 +10070,10 @@
         <x:v>GiB</x:v>
       </x:c>
       <x:c r="D46" s="1" t="str">
-        <x:v>既存記録</x:v>
+        <x:v>構成実測</x:v>
       </x:c>
       <x:c r="E46" s="1" t="str">
-        <x:v>d2fdd5b Fit/Gap</x:v>
+        <x:v>2026-10-18読み取り専用構成収集で確認。docs/secure-send-config-evidence-20261018.md</x:v>
       </x:c>
       <x:c r="F46" s="1"/>
       <x:c r="G46" s="1"/>
@@ -11049,7 +11061,7 @@
       </x:c>
       <x:c r="B62" s="1" t="n">
         <x:f>'設定と出典'!$B$7*86400*'設定と出典'!$B$15*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>3499.2</x:v>
+        <x:v>3128.969418426243</x:v>
       </x:c>
       <x:c r="C62" s="1"/>
       <x:c r="D62" s="1"/>
@@ -11109,7 +11121,7 @@
       </x:c>
       <x:c r="B63" s="1" t="n">
         <x:f>SUM(B62,'設定と出典'!$B$22,'設定と出典'!$B$23,'設定と出典'!$B$24,'設定と出典'!$B$25)</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="C63" s="1"/>
       <x:c r="D63" s="1"/>
@@ -13729,15 +13741,15 @@
       </x:c>
       <x:c r="W6" s="7" t="n">
         <x:f>(N6*'設定と出典'!$B$36+S6)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1.477125</x:v>
+        <x:v>1.3272587033350431</x:v>
       </x:c>
       <x:c r="X6" s="7" t="n">
         <x:f>N6*I6*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>0.22724999999999998</x:v>
+        <x:v>0.20419364666692974</x:v>
       </x:c>
       <x:c r="Y6" s="7" t="n">
         <x:f>MAX(0,S6*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S6,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>0.9674999999999999</x:v>
+        <x:v>0.8674029393819658</x:v>
       </x:c>
       <x:c r="Z6" s="7" t="n">
         <x:f>O6*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I6)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -13761,11 +13773,11 @@
       </x:c>
       <x:c r="AE6" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF6" s="7" t="n">
         <x:f>SUM(U6:AE6)</x:f>
-        <x:v>14665.436998596193</x:v>
+        <x:v>14294.933397311817</x:v>
       </x:c>
       <x:c r="AG6" s="7" t="n">
         <x:f>T6*'設定と出典'!$B$28</x:f>
@@ -13781,35 +13793,35 @@
       </x:c>
       <x:c r="AJ6" s="7" t="n">
         <x:f>T6-SUM(AF6:AI6)</x:f>
-        <x:v>3921.229668070475</x:v>
+        <x:v>4291.733269354849</x:v>
       </x:c>
       <x:c r="AK6" s="7" t="n">
         <x:f>AJ6-T6*'設定と出典'!$B$32</x:f>
-        <x:v>-11078.770331929525</x:v>
+        <x:v>-10708.266730645151</x:v>
       </x:c>
       <x:c r="AL6" s="7" t="n">
         <x:f>AJ6-A6*MIN(E6,AV6)*'設定と出典'!$B$32</x:f>
-        <x:v>-1078.7703319295251</x:v>
+        <x:v>-708.2667306451513</x:v>
       </x:c>
       <x:c r="AM6" s="8" t="n">
         <x:f>AJ6/T6</x:f>
-        <x:v>0.13070765560234915</x:v>
+        <x:v>0.14305777564516162</x:v>
       </x:c>
       <x:c r="AN6" s="8" t="n">
         <x:f>AK6/T6</x:f>
-        <x:v>-0.36929234439765085</x:v>
+        <x:v>-0.35694222435483836</x:v>
       </x:c>
       <x:c r="AO6" s="8" t="n">
         <x:f>AJ6/T6</x:f>
-        <x:v>0.13070765560234915</x:v>
+        <x:v>0.14305777564516162</x:v>
       </x:c>
       <x:c r="AP6" s="8" t="n">
         <x:f>AO6-'設定と出典'!$B$33</x:f>
-        <x:v>-0.06929234439765086</x:v>
+        <x:v>-0.056942224354838394</x:v>
       </x:c>
       <x:c r="AQ6" s="9" t="n">
         <x:f>SUM(W6:AD6)/N6</x:f>
-        <x:v>0.2649479943847656</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR6" s="9" t="n">
         <x:f>MAX(0,(E6*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U6+V6+AH6+AI6+AE6)/A6)/AQ6)</x:f>
@@ -13817,7 +13829,7 @@
       </x:c>
       <x:c r="AS6" s="9" t="n">
         <x:f>MAX(0,(E6*(1-'設定と出典'!$B$28 )-(U6+V6+AH6+AI6+AE6)/A6)/AQ6)</x:f>
-        <x:v>1504.9997551126762</x:v>
+        <x:v>1651.5442677432784</x:v>
       </x:c>
       <x:c r="AT6" s="9" t="n">
         <x:f>MAX(0,(E6*(1-'設定と出典'!$B$28)-MIN(E6,AV6)*'設定と出典'!$B$32-(U6+V6+AH6+AI6+AE6)/A6)/AQ6)</x:f>
@@ -13825,7 +13837,7 @@
       </x:c>
       <x:c r="AU6" s="9" t="n">
         <x:f>IF((T6*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF6-AE6)-AH6)&lt;=0,"成立せず",(AE6+AI6)/((T6*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF6-AE6)-AH6)/A6))</x:f>
-        <x:v>20.14499490283063</x:v>
+        <x:v>19.80547409520302</x:v>
       </x:c>
       <x:c r="AV6" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -13930,15 +13942,15 @@
       </x:c>
       <x:c r="W7" s="7" t="n">
         <x:f>(N7*'設定と出典'!$B$36+S7)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>19.543499999999998</x:v>
+        <x:v>17.560653613355957</x:v>
       </x:c>
       <x:c r="X7" s="7" t="n">
         <x:f>N7*I7*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1.3635</x:v>
+        <x:v>1.2251618800015787</x:v>
       </x:c>
       <x:c r="Y7" s="7" t="n">
         <x:f>MAX(0,S7*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S7,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>15.479999999999999</x:v>
+        <x:v>13.878447030111452</x:v>
       </x:c>
       <x:c r="Z7" s="7" t="n">
         <x:f>O7*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I7)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -13962,11 +13974,11 @@
       </x:c>
       <x:c r="AE7" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF7" s="7" t="n">
         <x:f>SUM(U7:AE7)</x:f>
-        <x:v>15514.548431884767</x:v>
+        <x:v>15140.595112834477</x:v>
       </x:c>
       <x:c r="AG7" s="7" t="n">
         <x:f>T7*'設定と出典'!$B$28</x:f>
@@ -13982,35 +13994,35 @@
       </x:c>
       <x:c r="AJ7" s="7" t="n">
         <x:f>T7-SUM(AF7:AI7)</x:f>
-        <x:v>-261.2150985514345</x:v>
+        <x:v>112.73822049885712</x:v>
       </x:c>
       <x:c r="AK7" s="7" t="n">
         <x:f>AJ7-T7*'設定と出典'!$B$32</x:f>
-        <x:v>-15261.215098551434</x:v>
+        <x:v>-14887.261779501143</x:v>
       </x:c>
       <x:c r="AL7" s="7" t="n">
         <x:f>AJ7-A7*MIN(E7,AV7)*'設定と出典'!$B$32</x:f>
-        <x:v>-5261.2150985514345</x:v>
+        <x:v>-4887.261779501143</x:v>
       </x:c>
       <x:c r="AM7" s="8" t="n">
         <x:f>AJ7/T7</x:f>
-        <x:v>-0.008707169951714484</x:v>
+        <x:v>0.003757940683295237</x:v>
       </x:c>
       <x:c r="AN7" s="8" t="n">
         <x:f>AK7/T7</x:f>
-        <x:v>-0.5087071699517145</x:v>
+        <x:v>-0.4962420593167048</x:v>
       </x:c>
       <x:c r="AO7" s="8" t="n">
         <x:f>AJ7/T7</x:f>
-        <x:v>-0.008707169951714484</x:v>
+        <x:v>0.003757940683295237</x:v>
       </x:c>
       <x:c r="AP7" s="8" t="n">
         <x:f>AO7-'設定と出典'!$B$33</x:f>
-        <x:v>-0.20870716995171448</x:v>
+        <x:v>-0.19624205931670477</x:v>
       </x:c>
       <x:c r="AQ7" s="9" t="n">
         <x:f>SUM(W7:AD7)/N7</x:f>
-        <x:v>0.9153484318847657</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR7" s="9" t="n">
         <x:f>MAX(0,(E7*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U7+V7+AH7+AI7+AE7)/A7)/AQ7)</x:f>
@@ -14018,7 +14030,7 @@
       </x:c>
       <x:c r="AS7" s="9" t="n">
         <x:f>MAX(0,(E7*(1-'設定と出典'!$B$28 )-(U7+V7+AH7+AI7+AE7)/A7)/AQ7)</x:f>
-        <x:v>71.46276877171503</x:v>
+        <x:v>112.36672256940246</x:v>
       </x:c>
       <x:c r="AT7" s="9" t="n">
         <x:f>MAX(0,(E7*(1-'設定と出典'!$B$28)-MIN(E7,AV7)*'設定と出典'!$B$32-(U7+V7+AH7+AI7+AE7)/A7)/AQ7)</x:f>
@@ -14026,7 +14038,7 @@
       </x:c>
       <x:c r="AU7" s="9" t="n">
         <x:f>IF((T7*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF7-AE7)-AH7)&lt;=0,"成立せず",(AE7+AI7)/((T7*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF7-AE7)-AH7)/A7))</x:f>
-        <x:v>32.64952403688305</x:v>
+        <x:v>32.08233073404942</x:v>
       </x:c>
       <x:c r="AV7" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -14131,15 +14143,15 @@
       </x:c>
       <x:c r="W8" s="7" t="n">
         <x:f>(N8*'設定と出典'!$B$36+S8)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>278.154</x:v>
+        <x:v>249.933023520322</x:v>
       </x:c>
       <x:c r="X8" s="7" t="n">
         <x:f>N8*I8*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>7.271999999999999</x:v>
+        <x:v>6.534196693341752</x:v>
       </x:c>
       <x:c r="Y8" s="7" t="n">
         <x:f>MAX(0,S8*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S8,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>232.20000000000002</x:v>
+        <x:v>208.17670545167175</x:v>
       </x:c>
       <x:c r="Z8" s="7" t="n">
         <x:f>O8*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I8)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -14163,11 +14175,11 @@
       </x:c>
       <x:c r="AE8" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF8" s="7" t="n">
         <x:f>SUM(U8:AE8)</x:f>
-        <x:v>39678.590477539066</x:v>
+        <x:v>39255.37782163064</x:v>
       </x:c>
       <x:c r="AG8" s="7" t="n">
         <x:f>T8*'設定と出典'!$B$28</x:f>
@@ -14183,35 +14195,35 @@
       </x:c>
       <x:c r="AJ8" s="7" t="n">
         <x:f>T8-SUM(AF8:AI8)</x:f>
-        <x:v>-32425.25714420573</x:v>
+        <x:v>-32002.044488297302</x:v>
       </x:c>
       <x:c r="AK8" s="7" t="n">
         <x:f>AJ8-T8*'設定と出典'!$B$32</x:f>
-        <x:v>-47425.25714420573</x:v>
+        <x:v>-47002.0444882973</x:v>
       </x:c>
       <x:c r="AL8" s="7" t="n">
         <x:f>AJ8-A8*MIN(E8,AV8)*'設定と出典'!$B$32</x:f>
-        <x:v>-37425.25714420573</x:v>
+        <x:v>-37002.0444882973</x:v>
       </x:c>
       <x:c r="AM8" s="8" t="n">
         <x:f>AJ8/T8</x:f>
-        <x:v>-1.0808419048068576</x:v>
+        <x:v>-1.0667348162765768</x:v>
       </x:c>
       <x:c r="AN8" s="8" t="n">
         <x:f>AK8/T8</x:f>
-        <x:v>-1.5808419048068576</x:v>
+        <x:v>-1.5667348162765768</x:v>
       </x:c>
       <x:c r="AO8" s="8" t="n">
         <x:f>AJ8/T8</x:f>
-        <x:v>-1.0808419048068576</x:v>
+        <x:v>-1.0667348162765768</x:v>
       </x:c>
       <x:c r="AP8" s="8" t="n">
         <x:f>AO8-'設定と出典'!$B$33</x:f>
-        <x:v>-1.2808419048068576</x:v>
+        <x:v>-1.2667348162765768</x:v>
       </x:c>
       <x:c r="AQ8" s="9" t="n">
         <x:f>SUM(W8:AD8)/N8</x:f>
-        <x:v>6.269847619384765</x:v>
+        <x:v>6.256602100801099</x:v>
       </x:c>
       <x:c r="AR8" s="9" t="n">
         <x:f>MAX(0,(E8*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U8+V8+AH8+AI8+AE8)/A8)/AQ8)</x:f>
@@ -14332,15 +14344,15 @@
       </x:c>
       <x:c r="W9" s="7" t="n">
         <x:f>(N9*'設定と出典'!$B$36+S9)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>5.9085</x:v>
+        <x:v>5.309034813340173</x:v>
       </x:c>
       <x:c r="X9" s="7" t="n">
         <x:f>N9*I9*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>0.9089999999999999</x:v>
+        <x:v>0.816774586667719</x:v>
       </x:c>
       <x:c r="Y9" s="7" t="n">
         <x:f>MAX(0,S9*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S9,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>3.8699999999999997</x:v>
+        <x:v>3.469611757527863</x:v>
       </x:c>
       <x:c r="Z9" s="7" t="n">
         <x:f>O9*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I9)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -14364,11 +14376,11 @@
       </x:c>
       <x:c r="AE9" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF9" s="7" t="n">
         <x:f>SUM(U9:AE9)</x:f>
-        <x:v>15164.147994384766</x:v>
+        <x:v>14792.825333968543</x:v>
       </x:c>
       <x:c r="AG9" s="7" t="n">
         <x:f>T9*'設定と出典'!$B$28</x:f>
@@ -14384,35 +14396,35 @@
       </x:c>
       <x:c r="AJ9" s="7" t="n">
         <x:f>T9-SUM(AF9:AI9)</x:f>
-        <x:v>21702.5186722819</x:v>
+        <x:v>22073.841332698124</x:v>
       </x:c>
       <x:c r="AK9" s="7" t="n">
         <x:f>AJ9-T9*'設定と出典'!$B$32</x:f>
-        <x:v>-3297.4813277180983</x:v>
+        <x:v>-2926.1586673018755</x:v>
       </x:c>
       <x:c r="AL9" s="7" t="n">
         <x:f>AJ9-A9*MIN(E9,AV9)*'設定と出典'!$B$32</x:f>
-        <x:v>16702.5186722819</x:v>
+        <x:v>17073.841332698124</x:v>
       </x:c>
       <x:c r="AM9" s="8" t="n">
         <x:f>AJ9/T9</x:f>
-        <x:v>0.434050373445638</x:v>
+        <x:v>0.4414768266539625</x:v>
       </x:c>
       <x:c r="AN9" s="8" t="n">
         <x:f>AK9/T9</x:f>
-        <x:v>-0.06594962655436197</x:v>
+        <x:v>-0.05852317334603751</x:v>
       </x:c>
       <x:c r="AO9" s="8" t="n">
         <x:f>AJ9/T9</x:f>
-        <x:v>0.434050373445638</x:v>
+        <x:v>0.4414768266539625</x:v>
       </x:c>
       <x:c r="AP9" s="8" t="n">
         <x:f>AO9-'設定と出典'!$B$33</x:f>
-        <x:v>0.234050373445638</x:v>
+        <x:v>0.24147682665396247</x:v>
       </x:c>
       <x:c r="AQ9" s="9" t="n">
         <x:f>SUM(W9:AD9)/N9</x:f>
-        <x:v>0.2649479943847656</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR9" s="9" t="n">
         <x:f>MAX(0,(E9*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U9+V9+AH9+AI9+AE9)/A9)/AQ9)</x:f>
@@ -14420,15 +14432,15 @@
       </x:c>
       <x:c r="AS9" s="9" t="n">
         <x:f>MAX(0,(E9*(1-'設定と出典'!$B$28 )-(U9+V9+AH9+AI9+AE9)/A9)/AQ9)</x:f>
-        <x:v>8291.237198332909</x:v>
+        <x:v>8465.869412982422</x:v>
       </x:c>
       <x:c r="AT9" s="9" t="n">
         <x:f>MAX(0,(E9*(1-'設定と出典'!$B$28)-MIN(E9,AV9)*'設定と出典'!$B$32-(U9+V9+AH9+AI9+AE9)/A9)/AQ9)</x:f>
-        <x:v>6404.074394322833</x:v>
+        <x:v>6570.895790835831</x:v>
       </x:c>
       <x:c r="AU9" s="9" t="n">
         <x:f>IF((T9*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF9-AE9)-AH9)&lt;=0,"成立せず",(AE9+AI9)/((T9*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF9-AE9)-AH9)/A9))</x:f>
-        <x:v>11.763196947564689</x:v>
+        <x:v>11.56455556666848</x:v>
       </x:c>
       <x:c r="AV9" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -14533,15 +14545,15 @@
       </x:c>
       <x:c r="W10" s="7" t="n">
         <x:f>(N10*'設定と出典'!$B$36+S10)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>78.17399999999999</x:v>
+        <x:v>70.24261445342383</x:v>
       </x:c>
       <x:c r="X10" s="7" t="n">
         <x:f>N10*I10*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>5.454</x:v>
+        <x:v>4.900647520006315</x:v>
       </x:c>
       <x:c r="Y10" s="7" t="n">
         <x:f>MAX(0,S10*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S10,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>61.919999999999995</x:v>
+        <x:v>55.51378812044581</x:v>
       </x:c>
       <x:c r="Z10" s="7" t="n">
         <x:f>O10*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I10)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -14565,11 +14577,11 @@
       </x:c>
       <x:c r="AE10" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF10" s="7" t="n">
         <x:f>SUM(U10:AE10)</x:f>
-        <x:v>18560.593727539064</x:v>
+        <x:v>18175.47219605918</x:v>
       </x:c>
       <x:c r="AG10" s="7" t="n">
         <x:f>T10*'設定と出典'!$B$28</x:f>
@@ -14585,35 +14597,35 @@
       </x:c>
       <x:c r="AJ10" s="7" t="n">
         <x:f>T10-SUM(AF10:AI10)</x:f>
-        <x:v>14972.739605794268</x:v>
+        <x:v>15357.86113727415</x:v>
       </x:c>
       <x:c r="AK10" s="7" t="n">
         <x:f>AJ10-T10*'設定と出典'!$B$32</x:f>
-        <x:v>-10027.260394205732</x:v>
+        <x:v>-9642.13886272585</x:v>
       </x:c>
       <x:c r="AL10" s="7" t="n">
         <x:f>AJ10-A10*MIN(E10,AV10)*'設定と出典'!$B$32</x:f>
-        <x:v>9972.739605794268</x:v>
+        <x:v>10357.86113727415</x:v>
       </x:c>
       <x:c r="AM10" s="8" t="n">
         <x:f>AJ10/T10</x:f>
-        <x:v>0.2994547921158854</x:v>
+        <x:v>0.307157222745483</x:v>
       </x:c>
       <x:c r="AN10" s="8" t="n">
         <x:f>AK10/T10</x:f>
-        <x:v>-0.20054520788411465</x:v>
+        <x:v>-0.19284277725451698</x:v>
       </x:c>
       <x:c r="AO10" s="8" t="n">
         <x:f>AJ10/T10</x:f>
-        <x:v>0.2994547921158854</x:v>
+        <x:v>0.307157222745483</x:v>
       </x:c>
       <x:c r="AP10" s="8" t="n">
         <x:f>AO10-'設定と出典'!$B$33</x:f>
-        <x:v>0.09945479211588537</x:v>
+        <x:v>0.107157222745483</x:v>
       </x:c>
       <x:c r="AQ10" s="9" t="n">
         <x:f>SUM(W10:AD10)/N10</x:f>
-        <x:v>0.9153484318847657</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR10" s="9" t="n">
         <x:f>MAX(0,(E10*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U10+V10+AH10+AI10+AE10)/A10)/AQ10)</x:f>
@@ -14621,15 +14633,15 @@
       </x:c>
       <x:c r="AS10" s="9" t="n">
         <x:f>MAX(0,(E10*(1-'設定と出典'!$B$28 )-(U10+V10+AH10+AI10+AE10)/A10)/AQ10)</x:f>
-        <x:v>2035.742093856474</x:v>
+        <x:v>2084.6674278134988</x:v>
       </x:c>
       <x:c r="AT10" s="9" t="n">
         <x:f>MAX(0,(E10*(1-'設定と出典'!$B$28)-MIN(E10,AV10)*'設定と出典'!$B$32-(U10+V10+AH10+AI10+AE10)/A10)/AQ10)</x:f>
-        <x:v>1489.5020145781762</x:v>
+        <x:v>1536.1967088913361</x:v>
       </x:c>
       <x:c r="AU10" s="9" t="n">
         <x:f>IF((T10*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF10-AE10)-AH10)&lt;=0,"成立せず",(AE10+AI10)/((T10*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF10-AE10)-AH10)/A10))</x:f>
-        <x:v>18.37563563163371</x:v>
+        <x:v>18.043943574509345</x:v>
       </x:c>
       <x:c r="AV10" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -14734,15 +14746,15 @@
       </x:c>
       <x:c r="W11" s="7" t="n">
         <x:f>(N11*'設定と出典'!$B$36+S11)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1112.616</x:v>
+        <x:v>999.732094081288</x:v>
       </x:c>
       <x:c r="X11" s="7" t="n">
         <x:f>N11*I11*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>29.087999999999997</x:v>
+        <x:v>26.136786773367007</x:v>
       </x:c>
       <x:c r="Y11" s="7" t="n">
         <x:f>MAX(0,S11*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S11,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>928.8000000000001</x:v>
+        <x:v>832.706821806687</x:v>
       </x:c>
       <x:c r="Z11" s="7" t="n">
         <x:f>O11*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I11)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -14766,11 +14778,11 @@
       </x:c>
       <x:c r="AE11" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF11" s="7" t="n">
         <x:f>SUM(U11:AE11)</x:f>
-        <x:v>115216.76191015624</x:v>
+        <x:v>114634.60303124384</x:v>
       </x:c>
       <x:c r="AG11" s="7" t="n">
         <x:f>T11*'設定と出典'!$B$28</x:f>
@@ -14786,35 +14798,35 @@
       </x:c>
       <x:c r="AJ11" s="7" t="n">
         <x:f>T11-SUM(AF11:AI11)</x:f>
-        <x:v>-89683.42857682292</x:v>
+        <x:v>-89101.2696979105</x:v>
       </x:c>
       <x:c r="AK11" s="7" t="n">
         <x:f>AJ11-T11*'設定と出典'!$B$32</x:f>
-        <x:v>-114683.42857682292</x:v>
+        <x:v>-114101.2696979105</x:v>
       </x:c>
       <x:c r="AL11" s="7" t="n">
         <x:f>AJ11-A11*MIN(E11,AV11)*'設定と出典'!$B$32</x:f>
-        <x:v>-94683.42857682292</x:v>
+        <x:v>-94101.2696979105</x:v>
       </x:c>
       <x:c r="AM11" s="8" t="n">
         <x:f>AJ11/T11</x:f>
-        <x:v>-1.7936685715364584</x:v>
+        <x:v>-1.7820253939582098</x:v>
       </x:c>
       <x:c r="AN11" s="8" t="n">
         <x:f>AK11/T11</x:f>
-        <x:v>-2.2936685715364584</x:v>
+        <x:v>-2.28202539395821</x:v>
       </x:c>
       <x:c r="AO11" s="8" t="n">
         <x:f>AJ11/T11</x:f>
-        <x:v>-1.7936685715364584</x:v>
+        <x:v>-1.7820253939582098</x:v>
       </x:c>
       <x:c r="AP11" s="8" t="n">
         <x:f>AO11-'設定と出典'!$B$33</x:f>
-        <x:v>-1.9936685715364584</x:v>
+        <x:v>-1.9820253939582098</x:v>
       </x:c>
       <x:c r="AQ11" s="9" t="n">
         <x:f>SUM(W11:AD11)/N11</x:f>
-        <x:v>6.269847619384765</x:v>
+        <x:v>6.256602100801099</x:v>
       </x:c>
       <x:c r="AR11" s="9" t="n">
         <x:f>MAX(0,(E11*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U11+V11+AH11+AI11+AE11)/A11)/AQ11)</x:f>
@@ -14822,11 +14834,11 @@
       </x:c>
       <x:c r="AS11" s="9" t="n">
         <x:f>MAX(0,(E11*(1-'設定と出典'!$B$28 )-(U11+V11+AH11+AI11+AE11)/A11)/AQ11)</x:f>
-        <x:v>169.6075244389562</x:v>
+        <x:v>175.88402998327302</x:v>
       </x:c>
       <x:c r="AT11" s="9" t="n">
         <x:f>MAX(0,(E11*(1-'設定と出典'!$B$28)-MIN(E11,AV11)*'設定と出典'!$B$32-(U11+V11+AH11+AI11+AE11)/A11)/AQ11)</x:f>
-        <x:v>89.8607697564137</x:v>
+        <x:v>95.968447700043</x:v>
       </x:c>
       <x:c r="AU11" s="9" t="str">
         <x:f>IF((T11*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF11-AE11)-AH11)&lt;=0,"成立せず",(AE11+AI11)/((T11*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF11-AE11)-AH11)/A11))</x:f>
@@ -14935,15 +14947,15 @@
       </x:c>
       <x:c r="W12" s="7" t="n">
         <x:f>(N12*'設定と出典'!$B$36+S12)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>14.771249999999998</x:v>
+        <x:v>13.272587033350435</x:v>
       </x:c>
       <x:c r="X12" s="7" t="n">
         <x:f>N12*I12*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2.2725</x:v>
+        <x:v>2.0419364666692976</x:v>
       </x:c>
       <x:c r="Y12" s="7" t="n">
         <x:f>MAX(0,S12*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S12,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>9.674999999999999</x:v>
+        <x:v>8.674029393819657</x:v>
       </x:c>
       <x:c r="Z12" s="7" t="n">
         <x:f>O12*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I12)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -14967,11 +14979,11 @@
       </x:c>
       <x:c r="AE12" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF12" s="7" t="n">
         <x:f>SUM(U12:AE12)</x:f>
-        <x:v>16161.569985961914</x:v>
+        <x:v>15788.609207281996</x:v>
       </x:c>
       <x:c r="AG12" s="7" t="n">
         <x:f>T12*'設定と出典'!$B$28</x:f>
@@ -14987,51 +14999,51 @@
       </x:c>
       <x:c r="AJ12" s="7" t="n">
         <x:f>T12-SUM(AF12:AI12)</x:f>
-        <x:v>47625.09668070475</x:v>
+        <x:v>47998.05745938467</x:v>
       </x:c>
       <x:c r="AK12" s="7" t="n">
         <x:f>AJ12-T12*'設定と出典'!$B$32</x:f>
-        <x:v>7625.096680704752</x:v>
+        <x:v>7998.057459384669</x:v>
       </x:c>
       <x:c r="AL12" s="7" t="n">
         <x:f>AJ12-A12*MIN(E12,AV12)*'設定と出典'!$B$32</x:f>
-        <x:v>42625.09668070475</x:v>
+        <x:v>42998.05745938467</x:v>
       </x:c>
       <x:c r="AM12" s="8" t="n">
         <x:f>AJ12/T12</x:f>
-        <x:v>0.5953137085088094</x:v>
+        <x:v>0.5999757182423083</x:v>
       </x:c>
       <x:c r="AN12" s="8" t="n">
         <x:f>AK12/T12</x:f>
-        <x:v>0.0953137085088094</x:v>
+        <x:v>0.09997571824230836</x:v>
       </x:c>
       <x:c r="AO12" s="8" t="n">
         <x:f>AJ12/T12</x:f>
-        <x:v>0.5953137085088094</x:v>
+        <x:v>0.5999757182423083</x:v>
       </x:c>
       <x:c r="AP12" s="8" t="n">
         <x:f>AO12-'設定と出典'!$B$33</x:f>
-        <x:v>0.39531370850880937</x:v>
+        <x:v>0.3999757182423083</x:v>
       </x:c>
       <x:c r="AQ12" s="9" t="n">
         <x:f>SUM(W12:AD12)/N12</x:f>
-        <x:v>0.2649479943847657</x:v>
+        <x:v>0.2638559155423014</x:v>
       </x:c>
       <x:c r="AR12" s="9" t="n">
         <x:f>MAX(0,(E12*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U12+V12+AH12+AI12+AE12)/A12)/AQ12)</x:f>
-        <x:v>3127.9597665613383</x:v>
+        <x:v>3281.221582789345</x:v>
       </x:c>
       <x:c r="AS12" s="9" t="n">
         <x:f>MAX(0,(E12*(1-'設定と出典'!$B$28 )-(U12+V12+AH12+AI12+AE12)/A12)/AQ12)</x:f>
-        <x:v>18225.26219864194</x:v>
+        <x:v>18441.010559962077</x:v>
       </x:c>
       <x:c r="AT12" s="9" t="n">
         <x:f>MAX(0,(E12*(1-'設定と出典'!$B$28)-MIN(E12,AV12)*'設定と出典'!$B$32-(U12+V12+AH12+AI12+AE12)/A12)/AQ12)</x:f>
-        <x:v>16338.099394631865</x:v>
+        <x:v>16546.036937815483</x:v>
       </x:c>
       <x:c r="AU12" s="9" t="n">
         <x:f>IF((T12*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF12-AE12)-AH12)&lt;=0,"成立せず",(AE12+AI12)/((T12*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF12-AE12)-AH12)/A12))</x:f>
-        <x:v>7.426066595643022</x:v>
+        <x:v>7.300418468457664</x:v>
       </x:c>
       <x:c r="AV12" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -15136,15 +15148,15 @@
       </x:c>
       <x:c r="W13" s="7" t="n">
         <x:f>(N13*'設定と出典'!$B$36+S13)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>195.435</x:v>
+        <x:v>175.60653613355956</x:v>
       </x:c>
       <x:c r="X13" s="7" t="n">
         <x:f>N13*I13*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>13.635</x:v>
+        <x:v>12.251618800015784</x:v>
       </x:c>
       <x:c r="Y13" s="7" t="n">
         <x:f>MAX(0,S13*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S13,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>154.79999999999998</x:v>
+        <x:v>138.7844703011145</x:v>
       </x:c>
       <x:c r="Z13" s="7" t="n">
         <x:f>O13*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I13)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -15168,11 +15180,11 @@
       </x:c>
       <x:c r="AE13" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF13" s="7" t="n">
         <x:f>SUM(U13:AE13)</x:f>
-        <x:v>24652.684318847656</x:v>
+        <x:v>24245.22636250859</x:v>
       </x:c>
       <x:c r="AG13" s="7" t="n">
         <x:f>T13*'設定と出典'!$B$28</x:f>
@@ -15188,51 +15200,51 @@
       </x:c>
       <x:c r="AJ13" s="7" t="n">
         <x:f>T13-SUM(AF13:AI13)</x:f>
-        <x:v>35800.64901448568</x:v>
+        <x:v>36208.106970824745</x:v>
       </x:c>
       <x:c r="AK13" s="7" t="n">
         <x:f>AJ13-T13*'設定と出典'!$B$32</x:f>
-        <x:v>-4199.35098551432</x:v>
+        <x:v>-3791.893029175255</x:v>
       </x:c>
       <x:c r="AL13" s="7" t="n">
         <x:f>AJ13-A13*MIN(E13,AV13)*'設定と出典'!$B$32</x:f>
-        <x:v>30800.64901448568</x:v>
+        <x:v>31208.106970824745</x:v>
       </x:c>
       <x:c r="AM13" s="8" t="n">
         <x:f>AJ13/T13</x:f>
-        <x:v>0.447508112681071</x:v>
+        <x:v>0.4526013371353093</x:v>
       </x:c>
       <x:c r="AN13" s="8" t="n">
         <x:f>AK13/T13</x:f>
-        <x:v>-0.052491887318929</x:v>
+        <x:v>-0.04739866286469069</x:v>
       </x:c>
       <x:c r="AO13" s="8" t="n">
         <x:f>AJ13/T13</x:f>
-        <x:v>0.447508112681071</x:v>
+        <x:v>0.4526013371353093</x:v>
       </x:c>
       <x:c r="AP13" s="8" t="n">
         <x:f>AO13-'設定と出典'!$B$33</x:f>
-        <x:v>0.24750811268107098</x:v>
+        <x:v>0.2526013371353093</x:v>
       </x:c>
       <x:c r="AQ13" s="9" t="n">
         <x:f>SUM(W13:AD13)/N13</x:f>
-        <x:v>0.9153484318847657</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR13" s="9" t="n">
         <x:f>MAX(0,(E13*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U13+V13+AH13+AI13+AE13)/A13)/AQ13)</x:f>
-        <x:v>541.2292369510511</x:v>
+        <x:v>584.0515408424621</x:v>
       </x:c>
       <x:c r="AS13" s="9" t="n">
         <x:f>MAX(0,(E13*(1-'設定と出典'!$B$28 )-(U13+V13+AH13+AI13+AE13)/A13)/AQ13)</x:f>
-        <x:v>4911.149871177435</x:v>
+        <x:v>4971.817292219763</x:v>
       </x:c>
       <x:c r="AT13" s="9" t="n">
         <x:f>MAX(0,(E13*(1-'設定と出典'!$B$28)-MIN(E13,AV13)*'設定と出典'!$B$32-(U13+V13+AH13+AI13+AE13)/A13)/AQ13)</x:f>
-        <x:v>4364.9097918991365</x:v>
+        <x:v>4423.3465732976</x:v>
       </x:c>
       <x:c r="AU13" s="9" t="n">
         <x:f>IF((T13*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF13-AE13)-AH13)&lt;=0,"成立せず",(AE13+AI13)/((T13*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF13-AE13)-AH13)/A13))</x:f>
-        <x:v>12.359205958486982</x:v>
+        <x:v>12.12584896001249</x:v>
       </x:c>
       <x:c r="AV13" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -15337,15 +15349,15 @@
       </x:c>
       <x:c r="W14" s="7" t="n">
         <x:f>(N14*'設定と出典'!$B$36+S14)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2781.5400000000004</x:v>
+        <x:v>2499.3302352032197</x:v>
       </x:c>
       <x:c r="X14" s="7" t="n">
         <x:f>N14*I14*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>72.72</x:v>
+        <x:v>65.34196693341752</x:v>
       </x:c>
       <x:c r="Y14" s="7" t="n">
         <x:f>MAX(0,S14*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S14,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2321.9999999999995</x:v>
+        <x:v>2081.7670545167175</x:v>
       </x:c>
       <x:c r="Z14" s="7" t="n">
         <x:f>O14*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I14)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -15369,11 +15381,11 @@
       </x:c>
       <x:c r="AE14" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF14" s="7" t="n">
         <x:f>SUM(U14:AE14)</x:f>
-        <x:v>266293.10477539065</x:v>
+        <x:v>265393.0534504702</x:v>
       </x:c>
       <x:c r="AG14" s="7" t="n">
         <x:f>T14*'設定と出典'!$B$28</x:f>
@@ -15389,35 +15401,35 @@
       </x:c>
       <x:c r="AJ14" s="7" t="n">
         <x:f>T14-SUM(AF14:AI14)</x:f>
-        <x:v>-213839.77144205733</x:v>
+        <x:v>-212939.7201171369</x:v>
       </x:c>
       <x:c r="AK14" s="7" t="n">
         <x:f>AJ14-T14*'設定と出典'!$B$32</x:f>
-        <x:v>-253839.77144205733</x:v>
+        <x:v>-252939.7201171369</x:v>
       </x:c>
       <x:c r="AL14" s="7" t="n">
         <x:f>AJ14-A14*MIN(E14,AV14)*'設定と出典'!$B$32</x:f>
-        <x:v>-218839.77144205733</x:v>
+        <x:v>-217939.7201171369</x:v>
       </x:c>
       <x:c r="AM14" s="8" t="n">
         <x:f>AJ14/T14</x:f>
-        <x:v>-2.6729971430257167</x:v>
+        <x:v>-2.661746501464211</x:v>
       </x:c>
       <x:c r="AN14" s="8" t="n">
         <x:f>AK14/T14</x:f>
-        <x:v>-3.1729971430257167</x:v>
+        <x:v>-3.161746501464211</x:v>
       </x:c>
       <x:c r="AO14" s="8" t="n">
         <x:f>AJ14/T14</x:f>
-        <x:v>-2.6729971430257167</x:v>
+        <x:v>-2.661746501464211</x:v>
       </x:c>
       <x:c r="AP14" s="8" t="n">
         <x:f>AO14-'設定と出典'!$B$33</x:f>
-        <x:v>-2.872997143025717</x:v>
+        <x:v>-2.861746501464211</x:v>
       </x:c>
       <x:c r="AQ14" s="9" t="n">
         <x:f>SUM(W14:AD14)/N14</x:f>
-        <x:v>6.269847619384766</x:v>
+        <x:v>6.2566021008011</x:v>
       </x:c>
       <x:c r="AR14" s="9" t="n">
         <x:f>MAX(0,(E14*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U14+V14+AH14+AI14+AE14)/A14)/AQ14)</x:f>
@@ -15425,11 +15437,11 @@
       </x:c>
       <x:c r="AS14" s="9" t="n">
         <x:f>MAX(0,(E14*(1-'設定と出典'!$B$28 )-(U14+V14+AH14+AI14+AE14)/A14)/AQ14)</x:f>
-        <x:v>589.3944410878598</x:v>
+        <x:v>596.5596551221956</x:v>
       </x:c>
       <x:c r="AT14" s="9" t="n">
         <x:f>MAX(0,(E14*(1-'設定と出典'!$B$28)-MIN(E14,AV14)*'設定と出典'!$B$32-(U14+V14+AH14+AI14+AE14)/A14)/AQ14)</x:f>
-        <x:v>509.64768640531736</x:v>
+        <x:v>516.6440728389656</x:v>
       </x:c>
       <x:c r="AU14" s="9" t="str">
         <x:f>IF((T14*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF14-AE14)-AH14)&lt;=0,"成立せず",(AE14+AI14)/((T14*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF14-AE14)-AH14)/A14))</x:f>
@@ -15538,15 +15550,15 @@
       </x:c>
       <x:c r="W15" s="7" t="n">
         <x:f>(N15*'設定と出典'!$B$36+S15)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>14.771249999999998</x:v>
+        <x:v>13.272587033350435</x:v>
       </x:c>
       <x:c r="X15" s="7" t="n">
         <x:f>N15*I15*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2.2725</x:v>
+        <x:v>2.0419364666692976</x:v>
       </x:c>
       <x:c r="Y15" s="7" t="n">
         <x:f>MAX(0,S15*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S15,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>9.674999999999999</x:v>
+        <x:v>8.674029393819657</x:v>
       </x:c>
       <x:c r="Z15" s="7" t="n">
         <x:f>O15*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I15)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -15570,11 +15582,11 @@
       </x:c>
       <x:c r="AE15" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF15" s="7" t="n">
         <x:f>SUM(U15:AE15)</x:f>
-        <x:v>20661.569985961913</x:v>
+        <x:v>20288.609207281996</x:v>
       </x:c>
       <x:c r="AG15" s="7" t="n">
         <x:f>T15*'設定と出典'!$B$28</x:f>
@@ -15590,51 +15602,51 @@
       </x:c>
       <x:c r="AJ15" s="7" t="n">
         <x:f>T15-SUM(AF15:AI15)</x:f>
-        <x:v>237205.09668070474</x:v>
+        <x:v>237578.05745938467</x:v>
       </x:c>
       <x:c r="AK15" s="7" t="n">
         <x:f>AJ15-T15*'設定と出典'!$B$32</x:f>
-        <x:v>87205.09668070474</x:v>
+        <x:v>87578.05745938467</x:v>
       </x:c>
       <x:c r="AL15" s="7" t="n">
         <x:f>AJ15-A15*MIN(E15,AV15)*'設定と出典'!$B$32</x:f>
-        <x:v>187205.09668070474</x:v>
+        <x:v>187578.05745938467</x:v>
       </x:c>
       <x:c r="AM15" s="8" t="n">
         <x:f>AJ15/T15</x:f>
-        <x:v>0.7906836556023491</x:v>
+        <x:v>0.791926858197949</x:v>
       </x:c>
       <x:c r="AN15" s="8" t="n">
         <x:f>AK15/T15</x:f>
-        <x:v>0.2906836556023491</x:v>
+        <x:v>0.2919268581979489</x:v>
       </x:c>
       <x:c r="AO15" s="8" t="n">
         <x:f>AJ15/T15</x:f>
-        <x:v>0.7906836556023491</x:v>
+        <x:v>0.791926858197949</x:v>
       </x:c>
       <x:c r="AP15" s="8" t="n">
         <x:f>AO15-'設定と出典'!$B$33</x:f>
-        <x:v>0.5906836556023491</x:v>
+        <x:v>0.5919268581979489</x:v>
       </x:c>
       <x:c r="AQ15" s="9" t="n">
         <x:f>SUM(W15:AD15)/N15</x:f>
-        <x:v>0.2649479943847657</x:v>
+        <x:v>0.2638559155423014</x:v>
       </x:c>
       <x:c r="AR15" s="9" t="n">
         <x:f>MAX(0,(E15*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U15+V15+AH15+AI15+AE15)/A15)/AQ15)</x:f>
-        <x:v>3316.4042955185696</x:v>
+        <x:v>3344.16217528745</x:v>
       </x:c>
       <x:c r="AS15" s="9" t="n">
         <x:f>MAX(0,(E15*(1-'設定と出典'!$B$28 )-(U15+V15+AH15+AI15+AE15)/A15)/AQ15)</x:f>
-        <x:v>8977.892707548794</x:v>
+        <x:v>9029.083041727223</x:v>
       </x:c>
       <x:c r="AT15" s="9" t="n">
         <x:f>MAX(0,(E15*(1-'設定と出典'!$B$28)-MIN(E15,AV15)*'設定と出典'!$B$32-(U15+V15+AH15+AI15+AE15)/A15)/AQ15)</x:f>
-        <x:v>7090.72990353872</x:v>
+        <x:v>7134.109419580632</x:v>
       </x:c>
       <x:c r="AU15" s="9" t="n">
         <x:f>IF((T15*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF15-AE15)-AH15)&lt;=0,"成立せず",(AE15+AI15)/((T15*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF15-AE15)-AH15)/A15))</x:f>
-        <x:v>20.144994902830618</x:v>
+        <x:v>19.805474095203017</x:v>
       </x:c>
       <x:c r="AV15" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -15642,7 +15654,7 @@
       </x:c>
       <x:c r="AW15" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E15,(AK15/A15-E15*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>1030.4960863903314</x:v>
+        <x:v>1044.623388613056</x:v>
       </x:c>
       <x:c r="AX15" s="1"/>
       <x:c r="AY15" s="1"/>
@@ -15739,15 +15751,15 @@
       </x:c>
       <x:c r="W16" s="7" t="n">
         <x:f>(N16*'設定と出典'!$B$36+S16)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>195.435</x:v>
+        <x:v>175.60653613355956</x:v>
       </x:c>
       <x:c r="X16" s="7" t="n">
         <x:f>N16*I16*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>13.635</x:v>
+        <x:v>12.251618800015784</x:v>
       </x:c>
       <x:c r="Y16" s="7" t="n">
         <x:f>MAX(0,S16*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S16,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>154.79999999999998</x:v>
+        <x:v>138.7844703011145</x:v>
       </x:c>
       <x:c r="Z16" s="7" t="n">
         <x:f>O16*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I16)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -15771,11 +15783,11 @@
       </x:c>
       <x:c r="AE16" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF16" s="7" t="n">
         <x:f>SUM(U16:AE16)</x:f>
-        <x:v>29152.684318847656</x:v>
+        <x:v>28745.226362508587</x:v>
       </x:c>
       <x:c r="AG16" s="7" t="n">
         <x:f>T16*'設定と出典'!$B$28</x:f>
@@ -15791,51 +15803,51 @@
       </x:c>
       <x:c r="AJ16" s="7" t="n">
         <x:f>T16-SUM(AF16:AI16)</x:f>
-        <x:v>195380.64901448568</x:v>
+        <x:v>195788.10697082474</x:v>
       </x:c>
       <x:c r="AK16" s="7" t="n">
         <x:f>AJ16-T16*'設定と出典'!$B$32</x:f>
-        <x:v>45380.64901448568</x:v>
+        <x:v>45788.10697082474</x:v>
       </x:c>
       <x:c r="AL16" s="7" t="n">
         <x:f>AJ16-A16*MIN(E16,AV16)*'設定と出典'!$B$32</x:f>
-        <x:v>145380.64901448568</x:v>
+        <x:v>145788.10697082474</x:v>
       </x:c>
       <x:c r="AM16" s="8" t="n">
         <x:f>AJ16/T16</x:f>
-        <x:v>0.6512688300482856</x:v>
+        <x:v>0.6526270232360825</x:v>
       </x:c>
       <x:c r="AN16" s="8" t="n">
         <x:f>AK16/T16</x:f>
-        <x:v>0.1512688300482856</x:v>
+        <x:v>0.15262702323608246</x:v>
       </x:c>
       <x:c r="AO16" s="8" t="n">
         <x:f>AJ16/T16</x:f>
-        <x:v>0.6512688300482856</x:v>
+        <x:v>0.6526270232360825</x:v>
       </x:c>
       <x:c r="AP16" s="8" t="n">
         <x:f>AO16-'設定と出典'!$B$33</x:f>
-        <x:v>0.4512688300482856</x:v>
+        <x:v>0.45262702323608245</x:v>
       </x:c>
       <x:c r="AQ16" s="9" t="n">
         <x:f>SUM(W16:AD16)/N16</x:f>
-        <x:v>0.9153484318847657</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR16" s="9" t="n">
         <x:f>MAX(0,(E16*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U16+V16+AH16+AI16+AE16)/A16)/AQ16)</x:f>
-        <x:v>595.7745863074654</x:v>
+        <x:v>602.2687189674625</x:v>
       </x:c>
       <x:c r="AS16" s="9" t="n">
         <x:f>MAX(0,(E16*(1-'設定と出典'!$B$28 )-(U16+V16+AH16+AI16+AE16)/A16)/AQ16)</x:f>
-        <x:v>2234.4948241423585</x:v>
+        <x:v>2247.68087573395</x:v>
       </x:c>
       <x:c r="AT16" s="9" t="n">
         <x:f>MAX(0,(E16*(1-'設定と出典'!$B$28)-MIN(E16,AV16)*'設定と出典'!$B$32-(U16+V16+AH16+AI16+AE16)/A16)/AQ16)</x:f>
-        <x:v>1688.254744864061</x:v>
+        <x:v>1699.2101568117876</x:v>
       </x:c>
       <x:c r="AU16" s="9" t="n">
         <x:f>IF((T16*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF16-AE16)-AH16)&lt;=0,"成立せず",(AE16+AI16)/((T16*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF16-AE16)-AH16)/A16))</x:f>
-        <x:v>32.64952403688303</x:v>
+        <x:v>32.082330734049414</x:v>
       </x:c>
       <x:c r="AV16" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -15940,15 +15952,15 @@
       </x:c>
       <x:c r="W17" s="7" t="n">
         <x:f>(N17*'設定と出典'!$B$36+S17)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2781.5400000000004</x:v>
+        <x:v>2499.3302352032197</x:v>
       </x:c>
       <x:c r="X17" s="7" t="n">
         <x:f>N17*I17*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>72.72</x:v>
+        <x:v>65.34196693341752</x:v>
       </x:c>
       <x:c r="Y17" s="7" t="n">
         <x:f>MAX(0,S17*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S17,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2321.9999999999995</x:v>
+        <x:v>2081.7670545167175</x:v>
       </x:c>
       <x:c r="Z17" s="7" t="n">
         <x:f>O17*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I17)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -15972,11 +15984,11 @@
       </x:c>
       <x:c r="AE17" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF17" s="7" t="n">
         <x:f>SUM(U17:AE17)</x:f>
-        <x:v>270793.10477539065</x:v>
+        <x:v>269893.0534504702</x:v>
       </x:c>
       <x:c r="AG17" s="7" t="n">
         <x:f>T17*'設定と出典'!$B$28</x:f>
@@ -15992,35 +16004,35 @@
       </x:c>
       <x:c r="AJ17" s="7" t="n">
         <x:f>T17-SUM(AF17:AI17)</x:f>
-        <x:v>-126259.77144205733</x:v>
+        <x:v>-125359.72011713684</x:v>
       </x:c>
       <x:c r="AK17" s="7" t="n">
         <x:f>AJ17-T17*'設定と出典'!$B$32</x:f>
-        <x:v>-276259.77144205733</x:v>
+        <x:v>-275359.72011713684</x:v>
       </x:c>
       <x:c r="AL17" s="7" t="n">
         <x:f>AJ17-A17*MIN(E17,AV17)*'設定と出典'!$B$32</x:f>
-        <x:v>-176259.77144205733</x:v>
+        <x:v>-175359.72011713684</x:v>
       </x:c>
       <x:c r="AM17" s="8" t="n">
         <x:f>AJ17/T17</x:f>
-        <x:v>-0.42086590480685776</x:v>
+        <x:v>-0.41786573372378943</x:v>
       </x:c>
       <x:c r="AN17" s="8" t="n">
         <x:f>AK17/T17</x:f>
-        <x:v>-0.9208659048068578</x:v>
+        <x:v>-0.9178657337237894</x:v>
       </x:c>
       <x:c r="AO17" s="8" t="n">
         <x:f>AJ17/T17</x:f>
-        <x:v>-0.42086590480685776</x:v>
+        <x:v>-0.41786573372378943</x:v>
       </x:c>
       <x:c r="AP17" s="8" t="n">
         <x:f>AO17-'設定と出典'!$B$33</x:f>
-        <x:v>-0.6208659048068578</x:v>
+        <x:v>-0.6178657337237894</x:v>
       </x:c>
       <x:c r="AQ17" s="9" t="n">
         <x:f>SUM(W17:AD17)/N17</x:f>
-        <x:v>6.269847619384766</x:v>
+        <x:v>6.2566021008011</x:v>
       </x:c>
       <x:c r="AR17" s="9" t="n">
         <x:f>MAX(0,(E17*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U17+V17+AH17+AI17+AE17)/A17)/AQ17)</x:f>
@@ -16028,11 +16040,11 @@
       </x:c>
       <x:c r="AS17" s="9" t="n">
         <x:f>MAX(0,(E17*(1-'設定と出典'!$B$28 )-(U17+V17+AH17+AI17+AE17)/A17)/AQ17)</x:f>
-        <x:v>198.6238596107274</x:v>
+        <x:v>199.63609943952525</x:v>
       </x:c>
       <x:c r="AT17" s="9" t="n">
         <x:f>MAX(0,(E17*(1-'設定と出典'!$B$28)-MIN(E17,AV17)*'設定と出典'!$B$32-(U17+V17+AH17+AI17+AE17)/A17)/AQ17)</x:f>
-        <x:v>118.87710492818492</x:v>
+        <x:v>119.72051715629524</x:v>
       </x:c>
       <x:c r="AU17" s="9" t="str">
         <x:f>IF((T17*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF17-AE17)-AH17)&lt;=0,"成立せず",(AE17+AI17)/((T17*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF17-AE17)-AH17)/A17))</x:f>
@@ -16141,15 +16153,15 @@
       </x:c>
       <x:c r="W18" s="7" t="n">
         <x:f>(N18*'設定と出典'!$B$36+S18)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>59.084999999999994</x:v>
+        <x:v>53.09034813340174</x:v>
       </x:c>
       <x:c r="X18" s="7" t="n">
         <x:f>N18*I18*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>9.09</x:v>
+        <x:v>8.16774586667719</x:v>
       </x:c>
       <x:c r="Y18" s="7" t="n">
         <x:f>MAX(0,S18*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S18,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>38.699999999999996</x:v>
+        <x:v>34.69611757527863</x:v>
       </x:c>
       <x:c r="Z18" s="7" t="n">
         <x:f>O18*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I18)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -16173,11 +16185,11 @@
       </x:c>
       <x:c r="AE18" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF18" s="7" t="n">
         <x:f>SUM(U18:AE18)</x:f>
-        <x:v>25648.679943847656</x:v>
+        <x:v>25267.528573849253</x:v>
       </x:c>
       <x:c r="AG18" s="7" t="n">
         <x:f>T18*'設定と出典'!$B$28</x:f>
@@ -16193,51 +16205,51 @@
       </x:c>
       <x:c r="AJ18" s="7" t="n">
         <x:f>T18-SUM(AF18:AI18)</x:f>
-        <x:v>415017.98672281904</x:v>
+        <x:v>415399.1380928174</x:v>
       </x:c>
       <x:c r="AK18" s="7" t="n">
         <x:f>AJ18-T18*'設定と出典'!$B$32</x:f>
-        <x:v>165017.98672281904</x:v>
+        <x:v>165399.1380928174</x:v>
       </x:c>
       <x:c r="AL18" s="7" t="n">
         <x:f>AJ18-A18*MIN(E18,AV18)*'設定と出典'!$B$32</x:f>
-        <x:v>365017.98672281904</x:v>
+        <x:v>365399.1380928174</x:v>
       </x:c>
       <x:c r="AM18" s="8" t="n">
         <x:f>AJ18/T18</x:f>
-        <x:v>0.8300359734456381</x:v>
+        <x:v>0.8307982761856347</x:v>
       </x:c>
       <x:c r="AN18" s="8" t="n">
         <x:f>AK18/T18</x:f>
-        <x:v>0.33003597344563806</x:v>
+        <x:v>0.3307982761856348</x:v>
       </x:c>
       <x:c r="AO18" s="8" t="n">
         <x:f>AJ18/T18</x:f>
-        <x:v>0.8300359734456381</x:v>
+        <x:v>0.8307982761856347</x:v>
       </x:c>
       <x:c r="AP18" s="8" t="n">
         <x:f>AO18-'設定と出典'!$B$33</x:f>
-        <x:v>0.630035973445638</x:v>
+        <x:v>0.6307982761856348</x:v>
       </x:c>
       <x:c r="AQ18" s="9" t="n">
         <x:f>SUM(W18:AD18)/N18</x:f>
-        <x:v>0.2649479943847657</x:v>
+        <x:v>0.2638559155423014</x:v>
       </x:c>
       <x:c r="AR18" s="9" t="n">
         <x:f>MAX(0,(E18*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U18+V18+AH18+AI18+AE18)/A18)/AQ18)</x:f>
-        <x:v>6328.316130718648</x:v>
+        <x:v>6368.540076233409</x:v>
       </x:c>
       <x:c r="AS18" s="9" t="n">
         <x:f>MAX(0,(E18*(1-'設定と出典'!$B$28 )-(U18+V18+AH18+AI18+AE18)/A18)/AQ18)</x:f>
-        <x:v>15764.130150769024</x:v>
+        <x:v>15843.408186966366</x:v>
       </x:c>
       <x:c r="AT18" s="9" t="n">
         <x:f>MAX(0,(E18*(1-'設定と出典'!$B$28)-MIN(E18,AV18)*'設定と出典'!$B$32-(U18+V18+AH18+AI18+AE18)/A18)/AQ18)</x:f>
-        <x:v>13876.96734675895</x:v>
+        <x:v>13948.434564819774</x:v>
       </x:c>
       <x:c r="AU18" s="9" t="n">
         <x:f>IF((T18*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF18-AE18)-AH18)&lt;=0,"成立せず",(AE18+AI18)/((T18*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF18-AE18)-AH18)/A18))</x:f>
-        <x:v>11.76319694756469</x:v>
+        <x:v>11.564555566668485</x:v>
       </x:c>
       <x:c r="AV18" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -16245,7 +16257,7 @@
       </x:c>
       <x:c r="AW18" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E18,(AK18/A18-E18*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>2462.8025273795097</x:v>
+        <x:v>2477.240079273386</x:v>
       </x:c>
       <x:c r="AX18" s="1"/>
       <x:c r="AY18" s="1"/>
@@ -16342,15 +16354,15 @@
       </x:c>
       <x:c r="W19" s="7" t="n">
         <x:f>(N19*'設定と出典'!$B$36+S19)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>781.74</x:v>
+        <x:v>702.4261445342382</x:v>
       </x:c>
       <x:c r="X19" s="7" t="n">
         <x:f>N19*I19*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>54.54</x:v>
+        <x:v>49.006475200063136</x:v>
       </x:c>
       <x:c r="Y19" s="7" t="n">
         <x:f>MAX(0,S19*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S19,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>619.1999999999999</x:v>
+        <x:v>555.137881204458</x:v>
       </x:c>
       <x:c r="Z19" s="7" t="n">
         <x:f>O19*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I19)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -16374,11 +16386,11 @@
       </x:c>
       <x:c r="AE19" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF19" s="7" t="n">
         <x:f>SUM(U19:AE19)</x:f>
-        <x:v>59613.13727539062</x:v>
+        <x:v>59093.997194755626</x:v>
       </x:c>
       <x:c r="AG19" s="7" t="n">
         <x:f>T19*'設定と出典'!$B$28</x:f>
@@ -16394,51 +16406,51 @@
       </x:c>
       <x:c r="AJ19" s="7" t="n">
         <x:f>T19-SUM(AF19:AI19)</x:f>
-        <x:v>347720.1960579427</x:v>
+        <x:v>348239.3361385777</x:v>
       </x:c>
       <x:c r="AK19" s="7" t="n">
         <x:f>AJ19-T19*'設定と出典'!$B$32</x:f>
-        <x:v>97720.1960579427</x:v>
+        <x:v>98239.33613857772</x:v>
       </x:c>
       <x:c r="AL19" s="7" t="n">
         <x:f>AJ19-A19*MIN(E19,AV19)*'設定と出典'!$B$32</x:f>
-        <x:v>297720.1960579427</x:v>
+        <x:v>298239.3361385777</x:v>
       </x:c>
       <x:c r="AM19" s="8" t="n">
         <x:f>AJ19/T19</x:f>
-        <x:v>0.6954403921158854</x:v>
+        <x:v>0.6964786722771554</x:v>
       </x:c>
       <x:c r="AN19" s="8" t="n">
         <x:f>AK19/T19</x:f>
-        <x:v>0.1954403921158854</x:v>
+        <x:v>0.19647867227715546</x:v>
       </x:c>
       <x:c r="AO19" s="8" t="n">
         <x:f>AJ19/T19</x:f>
-        <x:v>0.6954403921158854</x:v>
+        <x:v>0.6964786722771554</x:v>
       </x:c>
       <x:c r="AP19" s="8" t="n">
         <x:f>AO19-'設定と出典'!$B$33</x:f>
-        <x:v>0.49544039211588536</x:v>
+        <x:v>0.4964786722771554</x:v>
       </x:c>
       <x:c r="AQ19" s="9" t="n">
         <x:f>SUM(W19:AD19)/N19</x:f>
-        <x:v>0.9153484318847657</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR19" s="9" t="n">
         <x:f>MAX(0,(E19*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U19+V19+AH19+AI19+AE19)/A19)/AQ19)</x:f>
-        <x:v>1467.5737528356285</x:v>
+        <x:v>1477.6279863672335</x:v>
       </x:c>
       <x:c r="AS19" s="9" t="n">
         <x:f>MAX(0,(E19*(1-'設定と出典'!$B$28 )-(U19+V19+AH19+AI19+AE19)/A19)/AQ19)</x:f>
-        <x:v>4198.774149227118</x:v>
+        <x:v>4219.981580978046</x:v>
       </x:c>
       <x:c r="AT19" s="9" t="n">
         <x:f>MAX(0,(E19*(1-'設定と出典'!$B$28)-MIN(E19,AV19)*'設定と出典'!$B$32-(U19+V19+AH19+AI19+AE19)/A19)/AQ19)</x:f>
-        <x:v>3652.5340699488197</x:v>
+        <x:v>3671.5108620558835</x:v>
       </x:c>
       <x:c r="AU19" s="9" t="n">
         <x:f>IF((T19*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF19-AE19)-AH19)&lt;=0,"成立せず",(AE19+AI19)/((T19*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF19-AE19)-AH19)/A19))</x:f>
-        <x:v>18.375635631633713</x:v>
+        <x:v>18.043943574509353</x:v>
       </x:c>
       <x:c r="AV19" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -16543,15 +16555,15 @@
       </x:c>
       <x:c r="W20" s="7" t="n">
         <x:f>(N20*'設定と出典'!$B$36+S20)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>11126.160000000002</x:v>
+        <x:v>9997.320940812879</x:v>
       </x:c>
       <x:c r="X20" s="7" t="n">
         <x:f>N20*I20*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>290.88</x:v>
+        <x:v>261.3678677336701</x:v>
       </x:c>
       <x:c r="Y20" s="7" t="n">
         <x:f>MAX(0,S20*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S20,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>9287.999999999998</x:v>
+        <x:v>8327.06821806687</x:v>
       </x:c>
       <x:c r="Z20" s="7" t="n">
         <x:f>O20*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I20)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -16575,11 +16587,11 @@
       </x:c>
       <x:c r="AE20" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF20" s="7" t="n">
         <x:f>SUM(U20:AE20)</x:f>
-        <x:v>1026174.8191015625</x:v>
+        <x:v>1023685.3055466022</x:v>
       </x:c>
       <x:c r="AG20" s="7" t="n">
         <x:f>T20*'設定と出典'!$B$28</x:f>
@@ -16595,47 +16607,47 @@
       </x:c>
       <x:c r="AJ20" s="7" t="n">
         <x:f>T20-SUM(AF20:AI20)</x:f>
-        <x:v>-698841.4857682292</x:v>
+        <x:v>-696351.972213269</x:v>
       </x:c>
       <x:c r="AK20" s="7" t="n">
         <x:f>AJ20-T20*'設定と出典'!$B$32</x:f>
-        <x:v>-948841.4857682292</x:v>
+        <x:v>-946351.972213269</x:v>
       </x:c>
       <x:c r="AL20" s="7" t="n">
         <x:f>AJ20-A20*MIN(E20,AV20)*'設定と出典'!$B$32</x:f>
-        <x:v>-748841.4857682292</x:v>
+        <x:v>-746351.972213269</x:v>
       </x:c>
       <x:c r="AM20" s="8" t="n">
         <x:f>AJ20/T20</x:f>
-        <x:v>-1.3976829715364585</x:v>
+        <x:v>-1.3927039444265379</x:v>
       </x:c>
       <x:c r="AN20" s="8" t="n">
         <x:f>AK20/T20</x:f>
-        <x:v>-1.8976829715364585</x:v>
+        <x:v>-1.8927039444265379</x:v>
       </x:c>
       <x:c r="AO20" s="8" t="n">
         <x:f>AJ20/T20</x:f>
-        <x:v>-1.3976829715364585</x:v>
+        <x:v>-1.3927039444265379</x:v>
       </x:c>
       <x:c r="AP20" s="8" t="n">
         <x:f>AO20-'設定と出典'!$B$33</x:f>
-        <x:v>-1.5976829715364584</x:v>
+        <x:v>-1.5927039444265378</x:v>
       </x:c>
       <x:c r="AQ20" s="9" t="n">
         <x:f>SUM(W20:AD20)/N20</x:f>
-        <x:v>6.269847619384766</x:v>
+        <x:v>6.2566021008011</x:v>
       </x:c>
       <x:c r="AR20" s="9" t="n">
         <x:f>MAX(0,(E20*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U20+V20+AH20+AI20+AE20)/A20)/AQ20)</x:f>
-        <x:v>86.65941603643776</x:v>
+        <x:v>87.43462191387032</x:v>
       </x:c>
       <x:c r="AS20" s="9" t="n">
         <x:f>MAX(0,(E20*(1-'設定と出典'!$B$28 )-(U20+V20+AH20+AI20+AE20)/A20)/AQ20)</x:f>
-        <x:v>485.3931894491502</x:v>
+        <x:v>487.0125333300204</x:v>
       </x:c>
       <x:c r="AT20" s="9" t="n">
         <x:f>MAX(0,(E20*(1-'設定と出典'!$B$28)-MIN(E20,AV20)*'設定と出典'!$B$32-(U20+V20+AH20+AI20+AE20)/A20)/AQ20)</x:f>
-        <x:v>405.64643476660774</x:v>
+        <x:v>407.09695104679037</x:v>
       </x:c>
       <x:c r="AU20" s="9" t="str">
         <x:f>IF((T20*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF20-AE20)-AH20)&lt;=0,"成立せず",(AE20+AI20)/((T20*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF20-AE20)-AH20)/A20))</x:f>
@@ -16744,15 +16756,15 @@
       </x:c>
       <x:c r="W21" s="7" t="n">
         <x:f>(N21*'設定と出典'!$B$36+S21)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>147.7125</x:v>
+        <x:v>132.72587033350433</x:v>
       </x:c>
       <x:c r="X21" s="7" t="n">
         <x:f>N21*I21*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>22.724999999999998</x:v>
+        <x:v>20.41936466669297</x:v>
       </x:c>
       <x:c r="Y21" s="7" t="n">
         <x:f>MAX(0,S21*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S21,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>96.74999999999999</x:v>
+        <x:v>86.74029393819656</x:v>
       </x:c>
       <x:c r="Z21" s="7" t="n">
         <x:f>O21*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I21)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -16776,11 +16788,11 @@
       </x:c>
       <x:c r="AE21" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF21" s="7" t="n">
         <x:f>SUM(U21:AE21)</x:f>
-        <x:v>35622.89985961914</x:v>
+        <x:v>35225.367306983775</x:v>
       </x:c>
       <x:c r="AG21" s="7" t="n">
         <x:f>T21*'設定と出典'!$B$28</x:f>
@@ -16796,51 +16808,51 @@
       </x:c>
       <x:c r="AJ21" s="7" t="n">
         <x:f>T21-SUM(AF21:AI21)</x:f>
-        <x:v>674243.7668070475</x:v>
+        <x:v>674641.299359683</x:v>
       </x:c>
       <x:c r="AK21" s="7" t="n">
         <x:f>AJ21-T21*'設定と出典'!$B$32</x:f>
-        <x:v>274243.76680704753</x:v>
+        <x:v>274641.29935968295</x:v>
       </x:c>
       <x:c r="AL21" s="7" t="n">
         <x:f>AJ21-A21*MIN(E21,AV21)*'設定と出典'!$B$32</x:f>
-        <x:v>624243.7668070475</x:v>
+        <x:v>624641.299359683</x:v>
       </x:c>
       <x:c r="AM21" s="8" t="n">
         <x:f>AJ21/T21</x:f>
-        <x:v>0.8428047085088094</x:v>
+        <x:v>0.8433016241996036</x:v>
       </x:c>
       <x:c r="AN21" s="8" t="n">
         <x:f>AK21/T21</x:f>
-        <x:v>0.3428047085088094</x:v>
+        <x:v>0.3433016241996037</x:v>
       </x:c>
       <x:c r="AO21" s="8" t="n">
         <x:f>AJ21/T21</x:f>
-        <x:v>0.8428047085088094</x:v>
+        <x:v>0.8433016241996036</x:v>
       </x:c>
       <x:c r="AP21" s="8" t="n">
         <x:f>AO21-'設定と出典'!$B$33</x:f>
-        <x:v>0.6428047085088093</x:v>
+        <x:v>0.6433016241996037</x:v>
       </x:c>
       <x:c r="AQ21" s="9" t="n">
         <x:f>SUM(W21:AD21)/N21</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR21" s="9" t="n">
         <x:f>MAX(0,(E21*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U21+V21+AH21+AI21+AE21)/A21)/AQ21)</x:f>
-        <x:v>10600.852718997457</x:v>
+        <x:v>10658.760356773291</x:v>
       </x:c>
       <x:c r="AS21" s="9" t="n">
         <x:f>MAX(0,(E21*(1-'設定と出典'!$B$28 )-(U21+V21+AH21+AI21+AE21)/A21)/AQ21)</x:f>
-        <x:v>25698.155151078063</x:v>
+        <x:v>25818.549333946026</x:v>
       </x:c>
       <x:c r="AT21" s="9" t="n">
         <x:f>MAX(0,(E21*(1-'設定と出典'!$B$28)-MIN(E21,AV21)*'設定と出典'!$B$32-(U21+V21+AH21+AI21+AE21)/A21)/AQ21)</x:f>
-        <x:v>23810.99234706799</x:v>
+        <x:v>23923.575711799436</x:v>
       </x:c>
       <x:c r="AU21" s="9" t="n">
         <x:f>IF((T21*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF21-AE21)-AH21)&lt;=0,"成立せず",(AE21+AI21)/((T21*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF21-AE21)-AH21)/A21))</x:f>
-        <x:v>7.426066595643021</x:v>
+        <x:v>7.300418468457663</x:v>
       </x:c>
       <x:c r="AV21" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -16848,7 +16860,7 @@
       </x:c>
       <x:c r="AW21" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E21,(AK21/A21-E21*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>4327.415409357862</x:v>
+        <x:v>4342.473460594051</x:v>
       </x:c>
       <x:c r="AX21" s="1"/>
       <x:c r="AY21" s="1"/>
@@ -16945,15 +16957,15 @@
       </x:c>
       <x:c r="W22" s="7" t="n">
         <x:f>(N22*'設定と出典'!$B$36+S22)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1954.35</x:v>
+        <x:v>1756.065361335596</x:v>
       </x:c>
       <x:c r="X22" s="7" t="n">
         <x:f>N22*I22*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>136.35</x:v>
+        <x:v>122.51618800015784</x:v>
       </x:c>
       <x:c r="Y22" s="7" t="n">
         <x:f>MAX(0,S22*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S22,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1547.9999999999998</x:v>
+        <x:v>1387.844703011145</x:v>
       </x:c>
       <x:c r="Z22" s="7" t="n">
         <x:f>O22*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I22)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -16977,11 +16989,11 @@
       </x:c>
       <x:c r="AE22" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF22" s="7" t="n">
         <x:f>SUM(U22:AE22)</x:f>
-        <x:v>120534.04318847656</x:v>
+        <x:v>119791.5388592497</x:v>
       </x:c>
       <x:c r="AG22" s="7" t="n">
         <x:f>T22*'設定と出典'!$B$28</x:f>
@@ -16997,51 +17009,51 @@
       </x:c>
       <x:c r="AJ22" s="7" t="n">
         <x:f>T22-SUM(AF22:AI22)</x:f>
-        <x:v>555999.2901448568</x:v>
+        <x:v>556741.7944740837</x:v>
       </x:c>
       <x:c r="AK22" s="7" t="n">
         <x:f>AJ22-T22*'設定と出典'!$B$32</x:f>
-        <x:v>155999.2901448568</x:v>
+        <x:v>156741.7944740837</x:v>
       </x:c>
       <x:c r="AL22" s="7" t="n">
         <x:f>AJ22-A22*MIN(E22,AV22)*'設定と出典'!$B$32</x:f>
-        <x:v>505999.2901448568</x:v>
+        <x:v>506741.7944740837</x:v>
       </x:c>
       <x:c r="AM22" s="8" t="n">
         <x:f>AJ22/T22</x:f>
-        <x:v>0.694999112681071</x:v>
+        <x:v>0.6959272430926047</x:v>
       </x:c>
       <x:c r="AN22" s="8" t="n">
         <x:f>AK22/T22</x:f>
-        <x:v>0.19499911268107098</x:v>
+        <x:v>0.19592724309260462</x:v>
       </x:c>
       <x:c r="AO22" s="8" t="n">
         <x:f>AJ22/T22</x:f>
-        <x:v>0.694999112681071</x:v>
+        <x:v>0.6959272430926047</x:v>
       </x:c>
       <x:c r="AP22" s="8" t="n">
         <x:f>AO22-'設定と出典'!$B$33</x:f>
-        <x:v>0.49499911268107094</x:v>
+        <x:v>0.49592724309260466</x:v>
       </x:c>
       <x:c r="AQ22" s="9" t="n">
         <x:f>SUM(W22:AD22)/N22</x:f>
-        <x:v>0.9153484318847658</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR22" s="9" t="n">
         <x:f>MAX(0,(E22*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U22+V22+AH22+AI22+AE22)/A22)/AQ22)</x:f>
-        <x:v>2704.261292321694</x:v>
+        <x:v>2719.3656940070086</x:v>
       </x:c>
       <x:c r="AS22" s="9" t="n">
         <x:f>MAX(0,(E22*(1-'設定と出典'!$B$28 )-(U22+V22+AH22+AI22+AE22)/A22)/AQ22)</x:f>
-        <x:v>7074.181926548077</x:v>
+        <x:v>7107.13144538431</x:v>
       </x:c>
       <x:c r="AT22" s="9" t="n">
         <x:f>MAX(0,(E22*(1-'設定と出典'!$B$28)-MIN(E22,AV22)*'設定と出典'!$B$32-(U22+V22+AH22+AI22+AE22)/A22)/AQ22)</x:f>
-        <x:v>6527.94184726978</x:v>
+        <x:v>6558.660726462147</x:v>
       </x:c>
       <x:c r="AU22" s="9" t="n">
         <x:f>IF((T22*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF22-AE22)-AH22)&lt;=0,"成立せず",(AE22+AI22)/((T22*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF22-AE22)-AH22)/A22))</x:f>
-        <x:v>12.359205958486983</x:v>
+        <x:v>12.12584896001249</x:v>
       </x:c>
       <x:c r="AV22" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -17146,15 +17158,15 @@
       </x:c>
       <x:c r="W23" s="7" t="n">
         <x:f>(N23*'設定と出典'!$B$36+S23)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>27815.4</x:v>
+        <x:v>24993.302352032202</x:v>
       </x:c>
       <x:c r="X23" s="7" t="n">
         <x:f>N23*I23*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>727.1999999999999</x:v>
+        <x:v>653.4196693341751</x:v>
       </x:c>
       <x:c r="Y23" s="7" t="n">
         <x:f>MAX(0,S23*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S23,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>27820.800000000003</x:v>
+        <x:v>24931.685891616493</x:v>
       </x:c>
       <x:c r="Z23" s="7" t="n">
         <x:f>O23*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I23)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -17178,11 +17190,11 @@
       </x:c>
       <x:c r="AE23" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF23" s="7" t="n">
         <x:f>SUM(U23:AE23)</x:f>
-        <x:v>2541539.0477539063</x:v>
+        <x:v>2535383.825085315</x:v>
       </x:c>
       <x:c r="AG23" s="7" t="n">
         <x:f>T23*'設定と出典'!$B$28</x:f>
@@ -17198,47 +17210,47 @@
       </x:c>
       <x:c r="AJ23" s="7" t="n">
         <x:f>T23-SUM(AF23:AI23)</x:f>
-        <x:v>-1945005.7144205729</x:v>
+        <x:v>-1938850.4917519814</x:v>
       </x:c>
       <x:c r="AK23" s="7" t="n">
         <x:f>AJ23-T23*'設定と出典'!$B$32</x:f>
-        <x:v>-2345005.714420573</x:v>
+        <x:v>-2338850.4917519814</x:v>
       </x:c>
       <x:c r="AL23" s="7" t="n">
         <x:f>AJ23-A23*MIN(E23,AV23)*'設定と出典'!$B$32</x:f>
-        <x:v>-1995005.7144205729</x:v>
+        <x:v>-1988850.4917519814</x:v>
       </x:c>
       <x:c r="AM23" s="8" t="n">
         <x:f>AJ23/T23</x:f>
-        <x:v>-2.431257143025716</x:v>
+        <x:v>-2.4235631146899768</x:v>
       </x:c>
       <x:c r="AN23" s="8" t="n">
         <x:f>AK23/T23</x:f>
-        <x:v>-2.931257143025716</x:v>
+        <x:v>-2.9235631146899768</x:v>
       </x:c>
       <x:c r="AO23" s="8" t="n">
         <x:f>AJ23/T23</x:f>
-        <x:v>-2.431257143025716</x:v>
+        <x:v>-2.4235631146899768</x:v>
       </x:c>
       <x:c r="AP23" s="8" t="n">
         <x:f>AO23-'設定と出典'!$B$33</x:f>
-        <x:v>-2.6312571430257163</x:v>
+        <x:v>-2.623563114689977</x:v>
       </x:c>
       <x:c r="AQ23" s="9" t="n">
         <x:f>SUM(W23:AD23)/N23</x:f>
-        <x:v>6.281349619384765</x:v>
+        <x:v>6.266887139167222</x:v>
       </x:c>
       <x:c r="AR23" s="9" t="n">
         <x:f>MAX(0,(E23*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U23+V23+AH23+AI23+AE23)/A23)/AQ23)</x:f>
-        <x:v>266.7167782164347</x:v>
+        <x:v>267.9230695978659</x:v>
       </x:c>
       <x:c r="AS23" s="9" t="n">
         <x:f>MAX(0,(E23*(1-'設定と出典'!$B$28 )-(U23+V23+AH23+AI23+AE23)/A23)/AQ23)</x:f>
-        <x:v>903.5225989998646</x:v>
+        <x:v>906.1984862717239</x:v>
       </x:c>
       <x:c r="AT23" s="9" t="n">
         <x:f>MAX(0,(E23*(1-'設定と出典'!$B$28)-MIN(E23,AV23)*'設定と出典'!$B$32-(U23+V23+AH23+AI23+AE23)/A23)/AQ23)</x:f>
-        <x:v>823.921871401936</x:v>
+        <x:v>826.4140591874917</x:v>
       </x:c>
       <x:c r="AU23" s="9" t="str">
         <x:f>IF((T23*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF23-AE23)-AH23)&lt;=0,"成立せず",(AE23+AI23)/((T23*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF23-AE23)-AH23)/A23))</x:f>
@@ -17347,15 +17359,15 @@
       </x:c>
       <x:c r="W24" s="7" t="n">
         <x:f>(N24*'設定と出典'!$B$36+S24)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>73.85625</x:v>
+        <x:v>66.36293516675217</x:v>
       </x:c>
       <x:c r="X24" s="7" t="n">
         <x:f>N24*I24*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>11.362499999999999</x:v>
+        <x:v>10.209682333346485</x:v>
       </x:c>
       <x:c r="Y24" s="7" t="n">
         <x:f>MAX(0,S24*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S24,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>48.37499999999999</x:v>
+        <x:v>43.37014696909828</x:v>
       </x:c>
       <x:c r="Z24" s="7" t="n">
         <x:f>O24*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I24)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -17379,11 +17391,11 @@
       </x:c>
       <x:c r="AE24" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF24" s="7" t="n">
         <x:f>SUM(U24:AE24)</x:f>
-        <x:v>47311.04992980957</x:v>
+        <x:v>46927.168362705</x:v>
       </x:c>
       <x:c r="AG24" s="7" t="n">
         <x:f>T24*'設定と出典'!$B$28</x:f>
@@ -17399,51 +17411,51 @@
       </x:c>
       <x:c r="AJ24" s="7" t="n">
         <x:f>T24-SUM(AF24:AI24)</x:f>
-        <x:v>1274022.2834035237</x:v>
+        <x:v>1274406.1649706285</x:v>
       </x:c>
       <x:c r="AK24" s="7" t="n">
         <x:f>AJ24-T24*'設定と出典'!$B$32</x:f>
-        <x:v>524022.28340352373</x:v>
+        <x:v>524406.1649706285</x:v>
       </x:c>
       <x:c r="AL24" s="7" t="n">
         <x:f>AJ24-A24*MIN(E24,AV24)*'設定と出典'!$B$32</x:f>
-        <x:v>1024022.2834035237</x:v>
+        <x:v>1024406.1649706285</x:v>
       </x:c>
       <x:c r="AM24" s="8" t="n">
         <x:f>AJ24/T24</x:f>
-        <x:v>0.8493481889356825</x:v>
+        <x:v>0.849604109980419</x:v>
       </x:c>
       <x:c r="AN24" s="8" t="n">
         <x:f>AK24/T24</x:f>
-        <x:v>0.3493481889356825</x:v>
+        <x:v>0.34960410998041896</x:v>
       </x:c>
       <x:c r="AO24" s="8" t="n">
         <x:f>AJ24/T24</x:f>
-        <x:v>0.8493481889356825</x:v>
+        <x:v>0.849604109980419</x:v>
       </x:c>
       <x:c r="AP24" s="8" t="n">
         <x:f>AO24-'設定と出典'!$B$33</x:f>
-        <x:v>0.6493481889356825</x:v>
+        <x:v>0.6496041099804191</x:v>
       </x:c>
       <x:c r="AQ24" s="9" t="n">
         <x:f>SUM(W24:AD24)/N24</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR24" s="9" t="n">
         <x:f>MAX(0,(E24*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U24+V24+AH24+AI24+AE24)/A24)/AQ24)</x:f>
-        <x:v>3980.661446846225</x:v>
+        <x:v>3999.9433996415783</x:v>
       </x:c>
       <x:c r="AS24" s="9" t="n">
         <x:f>MAX(0,(E24*(1-'設定と出典'!$B$28 )-(U24+V24+AH24+AI24+AE24)/A24)/AQ24)</x:f>
-        <x:v>9642.149858876452</x:v>
+        <x:v>9684.864266081355</x:v>
       </x:c>
       <x:c r="AT24" s="9" t="n">
         <x:f>MAX(0,(E24*(1-'設定と出典'!$B$28)-MIN(E24,AV24)*'設定と出典'!$B$32-(U24+V24+AH24+AI24+AE24)/A24)/AQ24)</x:f>
-        <x:v>7754.987054866376</x:v>
+        <x:v>7789.890643934763</x:v>
       </x:c>
       <x:c r="AU24" s="9" t="n">
         <x:f>IF((T24*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF24-AE24)-AH24)&lt;=0,"成立せず",(AE24+AI24)/((T24*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF24-AE24)-AH24)/A24))</x:f>
-        <x:v>20.144994902830618</x:v>
+        <x:v>19.805474095203017</x:v>
       </x:c>
       <x:c r="AV24" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -17451,7 +17463,7 @@
       </x:c>
       <x:c r="AW24" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E24,(AK24/A24-E24*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>1697.1385106327557</x:v>
+        <x:v>1700.0467043229428</x:v>
       </x:c>
       <x:c r="AX24" s="1"/>
       <x:c r="AY24" s="1"/>
@@ -17548,15 +17560,15 @@
       </x:c>
       <x:c r="W25" s="7" t="n">
         <x:f>(N25*'設定と出典'!$B$36+S25)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>977.175</x:v>
+        <x:v>878.032680667798</x:v>
       </x:c>
       <x:c r="X25" s="7" t="n">
         <x:f>N25*I25*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>68.175</x:v>
+        <x:v>61.25809400007892</x:v>
       </x:c>
       <x:c r="Y25" s="7" t="n">
         <x:f>MAX(0,S25*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S25,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>773.9999999999999</x:v>
+        <x:v>693.9223515055725</x:v>
       </x:c>
       <x:c r="Z25" s="7" t="n">
         <x:f>O25*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I25)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -17580,11 +17592,11 @@
       </x:c>
       <x:c r="AE25" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF25" s="7" t="n">
         <x:f>SUM(U25:AE25)</x:f>
-        <x:v>89766.62159423828</x:v>
+        <x:v>89210.25413883798</x:v>
       </x:c>
       <x:c r="AG25" s="7" t="n">
         <x:f>T25*'設定と出典'!$B$28</x:f>
@@ -17600,51 +17612,51 @@
       </x:c>
       <x:c r="AJ25" s="7" t="n">
         <x:f>T25-SUM(AF25:AI25)</x:f>
-        <x:v>1064900.0450724284</x:v>
+        <x:v>1065456.4125278287</x:v>
       </x:c>
       <x:c r="AK25" s="7" t="n">
         <x:f>AJ25-T25*'設定と出典'!$B$32</x:f>
-        <x:v>314900.0450724284</x:v>
+        <x:v>315456.4125278287</x:v>
       </x:c>
       <x:c r="AL25" s="7" t="n">
         <x:f>AJ25-A25*MIN(E25,AV25)*'設定と出典'!$B$32</x:f>
-        <x:v>814900.0450724284</x:v>
+        <x:v>815456.4125278287</x:v>
       </x:c>
       <x:c r="AM25" s="8" t="n">
         <x:f>AJ25/T25</x:f>
-        <x:v>0.7099333633816189</x:v>
+        <x:v>0.7103042750185524</x:v>
       </x:c>
       <x:c r="AN25" s="8" t="n">
         <x:f>AK25/T25</x:f>
-        <x:v>0.20993336338161894</x:v>
+        <x:v>0.21030427501855248</x:v>
       </x:c>
       <x:c r="AO25" s="8" t="n">
         <x:f>AJ25/T25</x:f>
-        <x:v>0.7099333633816189</x:v>
+        <x:v>0.7103042750185524</x:v>
       </x:c>
       <x:c r="AP25" s="8" t="n">
         <x:f>AO25-'設定と出典'!$B$33</x:f>
-        <x:v>0.509933363381619</x:v>
+        <x:v>0.5103042750185525</x:v>
       </x:c>
       <x:c r="AQ25" s="9" t="n">
         <x:f>SUM(W25:AD25)/N25</x:f>
-        <x:v>0.9153484318847658</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR25" s="9" t="n">
         <x:f>MAX(0,(E25*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U25+V25+AH25+AI25+AE25)/A25)/AQ25)</x:f>
-        <x:v>788.0441023404112</x:v>
+        <x:v>792.074421470978</x:v>
       </x:c>
       <x:c r="AS25" s="9" t="n">
         <x:f>MAX(0,(E25*(1-'設定と出典'!$B$28 )-(U25+V25+AH25+AI25+AE25)/A25)/AQ25)</x:f>
-        <x:v>2426.764340175305</x:v>
+        <x:v>2437.486578237465</x:v>
       </x:c>
       <x:c r="AT25" s="9" t="n">
         <x:f>MAX(0,(E25*(1-'設定と出典'!$B$28)-MIN(E25,AV25)*'設定と出典'!$B$32-(U25+V25+AH25+AI25+AE25)/A25)/AQ25)</x:f>
-        <x:v>1880.5242608970068</x:v>
+        <x:v>1889.0158593153028</x:v>
       </x:c>
       <x:c r="AU25" s="9" t="n">
         <x:f>IF((T25*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF25-AE25)-AH25)&lt;=0,"成立せず",(AE25+AI25)/((T25*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF25-AE25)-AH25)/A25))</x:f>
-        <x:v>32.64952403688304</x:v>
+        <x:v>32.082330734049414</x:v>
       </x:c>
       <x:c r="AV25" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -17652,7 +17664,7 @@
       </x:c>
       <x:c r="AW25" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E25,(AK25/A25-E25*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>112.87912933657911</x:v>
+        <x:v>117.09403430173273</x:v>
       </x:c>
       <x:c r="AX25" s="1"/>
       <x:c r="AY25" s="1"/>
@@ -17749,15 +17761,15 @@
       </x:c>
       <x:c r="W26" s="7" t="n">
         <x:f>(N26*'設定と出典'!$B$36+S26)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>13907.7</x:v>
+        <x:v>12496.651176016101</x:v>
       </x:c>
       <x:c r="X26" s="7" t="n">
         <x:f>N26*I26*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>363.59999999999997</x:v>
+        <x:v>326.70983466708753</x:v>
       </x:c>
       <x:c r="Y26" s="7" t="n">
         <x:f>MAX(0,S26*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S26,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>12160.800000000001</x:v>
+        <x:v>10901.358236595128</x:v>
       </x:c>
       <x:c r="Z26" s="7" t="n">
         <x:f>O26*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I26)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -17781,11 +17793,11 @@
       </x:c>
       <x:c r="AE26" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF26" s="7" t="n">
         <x:f>SUM(U26:AE26)</x:f>
-        <x:v>1298519.5238769532</x:v>
+        <x:v>1295441.9125426577</x:v>
       </x:c>
       <x:c r="AG26" s="7" t="n">
         <x:f>T26*'設定と出典'!$B$28</x:f>
@@ -17801,35 +17813,35 @@
       </x:c>
       <x:c r="AJ26" s="7" t="n">
         <x:f>T26-SUM(AF26:AI26)</x:f>
-        <x:v>-543852.8572102864</x:v>
+        <x:v>-540775.245875991</x:v>
       </x:c>
       <x:c r="AK26" s="7" t="n">
         <x:f>AJ26-T26*'設定と出典'!$B$32</x:f>
-        <x:v>-1293852.8572102864</x:v>
+        <x:v>-1290775.245875991</x:v>
       </x:c>
       <x:c r="AL26" s="7" t="n">
         <x:f>AJ26-A26*MIN(E26,AV26)*'設定と出典'!$B$32</x:f>
-        <x:v>-793852.8572102864</x:v>
+        <x:v>-790775.245875991</x:v>
       </x:c>
       <x:c r="AM26" s="8" t="n">
         <x:f>AJ26/T26</x:f>
-        <x:v>-0.3625685714735243</x:v>
+        <x:v>-0.360516830583994</x:v>
       </x:c>
       <x:c r="AN26" s="8" t="n">
         <x:f>AK26/T26</x:f>
-        <x:v>-0.8625685714735243</x:v>
+        <x:v>-0.860516830583994</x:v>
       </x:c>
       <x:c r="AO26" s="8" t="n">
         <x:f>AJ26/T26</x:f>
-        <x:v>-0.3625685714735243</x:v>
+        <x:v>-0.360516830583994</x:v>
       </x:c>
       <x:c r="AP26" s="8" t="n">
         <x:f>AO26-'設定と出典'!$B$33</x:f>
-        <x:v>-0.5625685714735242</x:v>
+        <x:v>-0.560516830583994</x:v>
       </x:c>
       <x:c r="AQ26" s="9" t="n">
         <x:f>SUM(W26:AD26)/N26</x:f>
-        <x:v>6.2726016193847665</x:v>
+        <x:v>6.259064715621157</x:v>
       </x:c>
       <x:c r="AR26" s="9" t="n">
         <x:f>MAX(0,(E26*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U26+V26+AH26+AI26+AE26)/A26)/AQ26)</x:f>
@@ -17837,11 +17849,11 @@
       </x:c>
       <x:c r="AS26" s="9" t="n">
         <x:f>MAX(0,(E26*(1-'設定と出典'!$B$28 )-(U26+V26+AH26+AI26+AE26)/A26)/AQ26)</x:f>
-        <x:v>226.594166117749</x:v>
+        <x:v>227.20253889487898</x:v>
       </x:c>
       <x:c r="AT26" s="9" t="n">
         <x:f>MAX(0,(E26*(1-'設定と出典'!$B$28)-MIN(E26,AV26)*'設定と出典'!$B$32-(U26+V26+AH26+AI26+AE26)/A26)/AQ26)</x:f>
-        <x:v>146.8824244291319</x:v>
+        <x:v>147.31839921629134</x:v>
       </x:c>
       <x:c r="AU26" s="9" t="str">
         <x:f>IF((T26*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF26-AE26)-AH26)&lt;=0,"成立せず",(AE26+AI26)/((T26*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF26-AE26)-AH26)/A26))</x:f>
@@ -17950,15 +17962,15 @@
       </x:c>
       <x:c r="W27" s="7" t="n">
         <x:f>(N27*'設定と出典'!$B$36+S27)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>295.425</x:v>
+        <x:v>265.45174066700866</x:v>
       </x:c>
       <x:c r="X27" s="7" t="n">
         <x:f>N27*I27*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>45.449999999999996</x:v>
+        <x:v>40.83872933338594</x:v>
       </x:c>
       <x:c r="Y27" s="7" t="n">
         <x:f>MAX(0,S27*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S27,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>193.49999999999997</x:v>
+        <x:v>173.48058787639312</x:v>
       </x:c>
       <x:c r="Z27" s="7" t="n">
         <x:f>O27*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I27)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -17982,11 +17994,11 @@
       </x:c>
       <x:c r="AE27" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF27" s="7" t="n">
         <x:f>SUM(U27:AE27)</x:f>
-        <x:v>72246.59971923828</x:v>
+        <x:v>71821.76519554132</x:v>
       </x:c>
       <x:c r="AG27" s="7" t="n">
         <x:f>T27*'設定と出典'!$B$28</x:f>
@@ -18002,51 +18014,51 @@
       </x:c>
       <x:c r="AJ27" s="7" t="n">
         <x:f>T27-SUM(AF27:AI27)</x:f>
-        <x:v>2163086.733614095</x:v>
+        <x:v>2163511.568137792</x:v>
       </x:c>
       <x:c r="AK27" s="7" t="n">
         <x:f>AJ27-T27*'設定と出典'!$B$32</x:f>
-        <x:v>913086.733614095</x:v>
+        <x:v>913511.5681377919</x:v>
       </x:c>
       <x:c r="AL27" s="7" t="n">
         <x:f>AJ27-A27*MIN(E27,AV27)*'設定と出典'!$B$32</x:f>
-        <x:v>1913086.733614095</x:v>
+        <x:v>1913511.568137792</x:v>
       </x:c>
       <x:c r="AM27" s="8" t="n">
         <x:f>AJ27/T27</x:f>
-        <x:v>0.865234693445638</x:v>
+        <x:v>0.8654046272551168</x:v>
       </x:c>
       <x:c r="AN27" s="8" t="n">
         <x:f>AK27/T27</x:f>
-        <x:v>0.365234693445638</x:v>
+        <x:v>0.3654046272551168</x:v>
       </x:c>
       <x:c r="AO27" s="8" t="n">
         <x:f>AJ27/T27</x:f>
-        <x:v>0.865234693445638</x:v>
+        <x:v>0.8654046272551168</x:v>
       </x:c>
       <x:c r="AP27" s="8" t="n">
         <x:f>AO27-'設定と出典'!$B$33</x:f>
-        <x:v>0.6652346934456379</x:v>
+        <x:v>0.6654046272551168</x:v>
       </x:c>
       <x:c r="AQ27" s="9" t="n">
         <x:f>SUM(W27:AD27)/N27</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR27" s="9" t="n">
         <x:f>MAX(0,(E27*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U27+V27+AH27+AI27+AE27)/A27)/AQ27)</x:f>
-        <x:v>6992.573282046305</x:v>
+        <x:v>7024.32130058754</x:v>
       </x:c>
       <x:c r="AS27" s="9" t="n">
         <x:f>MAX(0,(E27*(1-'設定と出典'!$B$28 )-(U27+V27+AH27+AI27+AE27)/A27)/AQ27)</x:f>
-        <x:v>16428.387302096682</x:v>
+        <x:v>16499.189411320498</x:v>
       </x:c>
       <x:c r="AT27" s="9" t="n">
         <x:f>MAX(0,(E27*(1-'設定と出典'!$B$28)-MIN(E27,AV27)*'設定と出典'!$B$32-(U27+V27+AH27+AI27+AE27)/A27)/AQ27)</x:f>
-        <x:v>14541.224498086607</x:v>
+        <x:v>14604.215789173906</x:v>
       </x:c>
       <x:c r="AU27" s="9" t="n">
         <x:f>IF((T27*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF27-AE27)-AH27)&lt;=0,"成立せず",(AE27+AI27)/((T27*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF27-AE27)-AH27)/A27))</x:f>
-        <x:v>11.763196947564689</x:v>
+        <x:v>11.564555566668481</x:v>
       </x:c>
       <x:c r="AV27" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -18054,7 +18066,7 @@
       </x:c>
       <x:c r="AW27" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E27,(AK27/A27-E27*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>3129.4449516219324</x:v>
+        <x:v>3132.663394983273</x:v>
       </x:c>
       <x:c r="AX27" s="1"/>
       <x:c r="AY27" s="1"/>
@@ -18151,15 +18163,15 @@
       </x:c>
       <x:c r="W28" s="7" t="n">
         <x:f>(N28*'設定と出典'!$B$36+S28)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>3908.7</x:v>
+        <x:v>3512.130722671192</x:v>
       </x:c>
       <x:c r="X28" s="7" t="n">
         <x:f>N28*I28*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>272.7</x:v>
+        <x:v>245.03237600031568</x:v>
       </x:c>
       <x:c r="Y28" s="7" t="n">
         <x:f>MAX(0,S28*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S28,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>3095.9999999999995</x:v>
+        <x:v>2775.68940602229</x:v>
       </x:c>
       <x:c r="Z28" s="7" t="n">
         <x:f>O28*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I28)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -18183,11 +18195,11 @@
       </x:c>
       <x:c r="AE28" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF28" s="7" t="n">
         <x:f>SUM(U28:AE28)</x:f>
-        <x:v>242068.88637695313</x:v>
+        <x:v>240954.10830007316</x:v>
       </x:c>
       <x:c r="AG28" s="7" t="n">
         <x:f>T28*'設定と出典'!$B$28</x:f>
@@ -18203,51 +18215,51 @@
       </x:c>
       <x:c r="AJ28" s="7" t="n">
         <x:f>T28-SUM(AF28:AI28)</x:f>
-        <x:v>1826597.7802897135</x:v>
+        <x:v>1827712.5583665934</x:v>
       </x:c>
       <x:c r="AK28" s="7" t="n">
         <x:f>AJ28-T28*'設定と出典'!$B$32</x:f>
-        <x:v>576597.7802897135</x:v>
+        <x:v>577712.5583665934</x:v>
       </x:c>
       <x:c r="AL28" s="7" t="n">
         <x:f>AJ28-A28*MIN(E28,AV28)*'設定と出典'!$B$32</x:f>
-        <x:v>1576597.7802897135</x:v>
+        <x:v>1577712.5583665934</x:v>
       </x:c>
       <x:c r="AM28" s="8" t="n">
         <x:f>AJ28/T28</x:f>
-        <x:v>0.7306391121158854</x:v>
+        <x:v>0.7310850233466374</x:v>
       </x:c>
       <x:c r="AN28" s="8" t="n">
         <x:f>AK28/T28</x:f>
-        <x:v>0.23063911211588542</x:v>
+        <x:v>0.23108502334663739</x:v>
       </x:c>
       <x:c r="AO28" s="8" t="n">
         <x:f>AJ28/T28</x:f>
-        <x:v>0.7306391121158854</x:v>
+        <x:v>0.7310850233466374</x:v>
       </x:c>
       <x:c r="AP28" s="8" t="n">
         <x:f>AO28-'設定と出典'!$B$33</x:f>
-        <x:v>0.5306391121158853</x:v>
+        <x:v>0.5310850233466373</x:v>
       </x:c>
       <x:c r="AQ28" s="9" t="n">
         <x:f>SUM(W28:AD28)/N28</x:f>
-        <x:v>0.9153484318847658</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR28" s="9" t="n">
         <x:f>MAX(0,(E28*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U28+V28+AH28+AI28+AE28)/A28)/AQ28)</x:f>
-        <x:v>1659.8432688685746</x:v>
+        <x:v>1667.4336888707492</x:v>
       </x:c>
       <x:c r="AS28" s="9" t="n">
         <x:f>MAX(0,(E28*(1-'設定と出典'!$B$28 )-(U28+V28+AH28+AI28+AE28)/A28)/AQ28)</x:f>
-        <x:v>4391.043665260064</x:v>
+        <x:v>4409.787283481562</x:v>
       </x:c>
       <x:c r="AT28" s="9" t="n">
         <x:f>MAX(0,(E28*(1-'設定と出典'!$B$28)-MIN(E28,AV28)*'設定と出典'!$B$32-(U28+V28+AH28+AI28+AE28)/A28)/AQ28)</x:f>
-        <x:v>3844.803585981766</x:v>
+        <x:v>3861.316564559399</x:v>
       </x:c>
       <x:c r="AU28" s="9" t="n">
         <x:f>IF((T28*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF28-AE28)-AH28)&lt;=0,"成立せず",(AE28+AI28)/((T28*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF28-AE28)-AH28)/A28))</x:f>
-        <x:v>18.37563563163371</x:v>
+        <x:v>18.043943574509345</x:v>
       </x:c>
       <x:c r="AV28" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -18255,7 +18267,7 @@
       </x:c>
       <x:c r="AW28" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E28,(AK28/A28-E28*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>580.286214316012</x:v>
+        <x:v>588.7315027772227</x:v>
       </x:c>
       <x:c r="AX28" s="1"/>
       <x:c r="AY28" s="1"/>
@@ -18352,15 +18364,15 @@
       </x:c>
       <x:c r="W29" s="7" t="n">
         <x:f>(N29*'設定と出典'!$B$36+S29)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>55630.8</x:v>
+        <x:v>49986.604704064404</x:v>
       </x:c>
       <x:c r="X29" s="7" t="n">
         <x:f>N29*I29*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1454.3999999999999</x:v>
+        <x:v>1306.8393386683501</x:v>
       </x:c>
       <x:c r="Y29" s="7" t="n">
         <x:f>MAX(0,S29*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S29,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>59140.799999999996</x:v>
+        <x:v>52992.34120165924</x:v>
       </x:c>
       <x:c r="Z29" s="7" t="n">
         <x:f>O29*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I29)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -18384,11 +18396,11 @@
       </x:c>
       <x:c r="AE29" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF29" s="7" t="n">
         <x:f>SUM(U29:AE29)</x:f>
-        <x:v>5087578.095507813</x:v>
+        <x:v>5075267.650170631</x:v>
       </x:c>
       <x:c r="AG29" s="7" t="n">
         <x:f>T29*'設定と出典'!$B$28</x:f>
@@ -18404,47 +18416,47 @@
       </x:c>
       <x:c r="AJ29" s="7" t="n">
         <x:f>T29-SUM(AF29:AI29)</x:f>
-        <x:v>-3418911.4288411457</x:v>
+        <x:v>-3406600.983503964</x:v>
       </x:c>
       <x:c r="AK29" s="7" t="n">
         <x:f>AJ29-T29*'設定と出典'!$B$32</x:f>
-        <x:v>-4668911.428841146</x:v>
+        <x:v>-4656600.983503964</x:v>
       </x:c>
       <x:c r="AL29" s="7" t="n">
         <x:f>AJ29-A29*MIN(E29,AV29)*'設定と出典'!$B$32</x:f>
-        <x:v>-3668911.4288411457</x:v>
+        <x:v>-3656600.983503964</x:v>
       </x:c>
       <x:c r="AM29" s="8" t="n">
         <x:f>AJ29/T29</x:f>
-        <x:v>-1.3675645715364584</x:v>
+        <x:v>-1.3626403934015856</x:v>
       </x:c>
       <x:c r="AN29" s="8" t="n">
         <x:f>AK29/T29</x:f>
-        <x:v>-1.8675645715364584</x:v>
+        <x:v>-1.8626403934015856</x:v>
       </x:c>
       <x:c r="AO29" s="8" t="n">
         <x:f>AJ29/T29</x:f>
-        <x:v>-1.3675645715364584</x:v>
+        <x:v>-1.3626403934015856</x:v>
       </x:c>
       <x:c r="AP29" s="8" t="n">
         <x:f>AO29-'設定と出典'!$B$33</x:f>
-        <x:v>-1.5675645715364583</x:v>
+        <x:v>-1.5626403934015856</x:v>
       </x:c>
       <x:c r="AQ29" s="9" t="n">
         <x:f>SUM(W29:AD29)/N29</x:f>
-        <x:v>6.285723619384766</x:v>
+        <x:v>6.270798350940256</x:v>
       </x:c>
       <x:c r="AR29" s="9" t="n">
         <x:f>MAX(0,(E29*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U29+V29+AH29+AI29+AE29)/A29)/AQ29)</x:f>
-        <x:v>114.43947855342395</x:v>
+        <x:v>114.82993937901242</x:v>
       </x:c>
       <x:c r="AS29" s="9" t="n">
         <x:f>MAX(0,(E29*(1-'設定と出典'!$B$28 )-(U29+V29+AH29+AI29+AE29)/A29)/AQ29)</x:f>
-        <x:v>512.1661606955025</x:v>
+        <x:v>513.5032597585691</x:v>
       </x:c>
       <x:c r="AT29" s="9" t="n">
         <x:f>MAX(0,(E29*(1-'設定と出典'!$B$28)-MIN(E29,AV29)*'設定と出典'!$B$32-(U29+V29+AH29+AI29+AE29)/A29)/AQ29)</x:f>
-        <x:v>432.6208242670868</x:v>
+        <x:v>433.76859568265775</x:v>
       </x:c>
       <x:c r="AU29" s="9" t="str">
         <x:f>IF((T29*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF29-AE29)-AH29)&lt;=0,"成立せず",(AE29+AI29)/((T29*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF29-AE29)-AH29)/A29))</x:f>
@@ -18553,15 +18565,15 @@
       </x:c>
       <x:c r="W30" s="7" t="n">
         <x:f>(N30*'設定と出典'!$B$36+S30)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>738.5625</x:v>
+        <x:v>663.6293516675216</x:v>
       </x:c>
       <x:c r="X30" s="7" t="n">
         <x:f>N30*I30*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>113.62499999999999</x:v>
+        <x:v>102.09682333346487</x:v>
       </x:c>
       <x:c r="Y30" s="7" t="n">
         <x:f>MAX(0,S30*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S30,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>483.75</x:v>
+        <x:v>433.70146969098283</x:v>
       </x:c>
       <x:c r="Z30" s="7" t="n">
         <x:f>O30*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I30)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -18585,11 +18597,11 @@
       </x:c>
       <x:c r="AE30" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF30" s="7" t="n">
         <x:f>SUM(U30:AE30)</x:f>
-        <x:v>122117.6992980957</x:v>
+        <x:v>121610.95886121393</x:v>
       </x:c>
       <x:c r="AG30" s="7" t="n">
         <x:f>T30*'設定と出典'!$B$28</x:f>
@@ -18605,51 +18617,51 @@
       </x:c>
       <x:c r="AJ30" s="7" t="n">
         <x:f>T30-SUM(AF30:AI30)</x:f>
-        <x:v>3459215.6340352376</x:v>
+        <x:v>3459722.3744721194</x:v>
       </x:c>
       <x:c r="AK30" s="7" t="n">
         <x:f>AJ30-T30*'設定と出典'!$B$32</x:f>
-        <x:v>1459215.6340352376</x:v>
+        <x:v>1459722.3744721194</x:v>
       </x:c>
       <x:c r="AL30" s="7" t="n">
         <x:f>AJ30-A30*MIN(E30,AV30)*'設定と出典'!$B$32</x:f>
-        <x:v>3209215.6340352376</x:v>
+        <x:v>3209722.3744721194</x:v>
       </x:c>
       <x:c r="AM30" s="8" t="n">
         <x:f>AJ30/T30</x:f>
-        <x:v>0.8648039085088094</x:v>
+        <x:v>0.8649305936180298</x:v>
       </x:c>
       <x:c r="AN30" s="8" t="n">
         <x:f>AK30/T30</x:f>
-        <x:v>0.3648039085088094</x:v>
+        <x:v>0.3649305936180298</x:v>
       </x:c>
       <x:c r="AO30" s="8" t="n">
         <x:f>AJ30/T30</x:f>
-        <x:v>0.8648039085088094</x:v>
+        <x:v>0.8649305936180298</x:v>
       </x:c>
       <x:c r="AP30" s="8" t="n">
         <x:f>AO30-'設定と出典'!$B$33</x:f>
-        <x:v>0.6648039085088093</x:v>
+        <x:v>0.6649305936180299</x:v>
       </x:c>
       <x:c r="AQ30" s="9" t="n">
         <x:f>SUM(W30:AD30)/N30</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR30" s="9" t="n">
         <x:f>MAX(0,(E30*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U30+V30+AH30+AI30+AE30)/A30)/AQ30)</x:f>
-        <x:v>11265.109870325114</x:v>
+        <x:v>11314.541581127422</x:v>
       </x:c>
       <x:c r="AS30" s="9" t="n">
         <x:f>MAX(0,(E30*(1-'設定と出典'!$B$28 )-(U30+V30+AH30+AI30+AE30)/A30)/AQ30)</x:f>
-        <x:v>26362.41230240572</x:v>
+        <x:v>26474.330558300157</x:v>
       </x:c>
       <x:c r="AT30" s="9" t="n">
         <x:f>MAX(0,(E30*(1-'設定と出典'!$B$28)-MIN(E30,AV30)*'設定と出典'!$B$32-(U30+V30+AH30+AI30+AE30)/A30)/AQ30)</x:f>
-        <x:v>24475.249498395642</x:v>
+        <x:v>24579.356936153563</x:v>
       </x:c>
       <x:c r="AU30" s="9" t="n">
         <x:f>IF((T30*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF30-AE30)-AH30)&lt;=0,"成立せず",(AE30+AI30)/((T30*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF30-AE30)-AH30)/A30))</x:f>
-        <x:v>7.426066595643023</x:v>
+        <x:v>7.300418468457666</x:v>
       </x:c>
       <x:c r="AV30" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -18657,7 +18669,7 @@
       </x:c>
       <x:c r="AW30" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E30,(AK30/A30-E30*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>4994.057833600285</x:v>
+        <x:v>4997.896776303935</x:v>
       </x:c>
       <x:c r="AX30" s="1"/>
       <x:c r="AY30" s="1"/>
@@ -18754,15 +18766,15 @@
       </x:c>
       <x:c r="W31" s="7" t="n">
         <x:f>(N31*'設定と出典'!$B$36+S31)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>9771.75</x:v>
+        <x:v>8780.32680667798</x:v>
       </x:c>
       <x:c r="X31" s="7" t="n">
         <x:f>N31*I31*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>681.75</x:v>
+        <x:v>612.5809400007893</x:v>
       </x:c>
       <x:c r="Y31" s="7" t="n">
         <x:f>MAX(0,S31*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S31,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>7740</x:v>
+        <x:v>6939.223515055725</x:v>
       </x:c>
       <x:c r="Z31" s="7" t="n">
         <x:f>O31*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I31)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -18786,11 +18798,11 @@
       </x:c>
       <x:c r="AE31" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF31" s="7" t="n">
         <x:f>SUM(U31:AE31)</x:f>
-        <x:v>546673.4159423828</x:v>
+        <x:v>544441.8166225436</x:v>
       </x:c>
       <x:c r="AG31" s="7" t="n">
         <x:f>T31*'設定と出典'!$B$28</x:f>
@@ -18806,51 +18818,51 @@
       </x:c>
       <x:c r="AJ31" s="7" t="n">
         <x:f>T31-SUM(AF31:AI31)</x:f>
-        <x:v>2867993.250724284</x:v>
+        <x:v>2870224.850044123</x:v>
       </x:c>
       <x:c r="AK31" s="7" t="n">
         <x:f>AJ31-T31*'設定と出典'!$B$32</x:f>
-        <x:v>867993.250724284</x:v>
+        <x:v>870224.8500441229</x:v>
       </x:c>
       <x:c r="AL31" s="7" t="n">
         <x:f>AJ31-A31*MIN(E31,AV31)*'設定と出典'!$B$32</x:f>
-        <x:v>2617993.250724284</x:v>
+        <x:v>2620224.850044123</x:v>
       </x:c>
       <x:c r="AM31" s="8" t="n">
         <x:f>AJ31/T31</x:f>
-        <x:v>0.716998312681071</x:v>
+        <x:v>0.7175562125110307</x:v>
       </x:c>
       <x:c r="AN31" s="8" t="n">
         <x:f>AK31/T31</x:f>
-        <x:v>0.216998312681071</x:v>
+        <x:v>0.21755621251103072</x:v>
       </x:c>
       <x:c r="AO31" s="8" t="n">
         <x:f>AJ31/T31</x:f>
-        <x:v>0.716998312681071</x:v>
+        <x:v>0.7175562125110307</x:v>
       </x:c>
       <x:c r="AP31" s="8" t="n">
         <x:f>AO31-'設定と出典'!$B$33</x:f>
-        <x:v>0.5169983126810709</x:v>
+        <x:v>0.5175562125110307</x:v>
       </x:c>
       <x:c r="AQ31" s="9" t="n">
         <x:f>SUM(W31:AD31)/N31</x:f>
-        <x:v>0.9153484318847657</x:v>
+        <x:v>0.9116256944082347</x:v>
       </x:c>
       <x:c r="AR31" s="9" t="n">
         <x:f>MAX(0,(E31*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U31+V31+AH31+AI31+AE31)/A31)/AQ31)</x:f>
-        <x:v>2896.53080835464</x:v>
+        <x:v>2909.171396510524</x:v>
       </x:c>
       <x:c r="AS31" s="9" t="n">
         <x:f>MAX(0,(E31*(1-'設定と出典'!$B$28 )-(U31+V31+AH31+AI31+AE31)/A31)/AQ31)</x:f>
-        <x:v>7266.451442581024</x:v>
+        <x:v>7296.937147887824</x:v>
       </x:c>
       <x:c r="AT31" s="9" t="n">
         <x:f>MAX(0,(E31*(1-'設定と出典'!$B$28)-MIN(E31,AV31)*'設定と出典'!$B$32-(U31+V31+AH31+AI31+AE31)/A31)/AQ31)</x:f>
-        <x:v>6720.211363302726</x:v>
+        <x:v>6748.466428965661</x:v>
       </x:c>
       <x:c r="AU31" s="9" t="n">
         <x:f>IF((T31*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF31-AE31)-AH31)&lt;=0,"成立せず",(AE31+AI31)/((T31*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF31-AE31)-AH31)/A31))</x:f>
-        <x:v>12.359205958486983</x:v>
+        <x:v>12.125848960012492</x:v>
       </x:c>
       <x:c r="AV31" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -18858,7 +18870,7 @@
       </x:c>
       <x:c r="AW31" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E31,(AK31/A31-E31*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>515.1003842748784</x:v>
+        <x:v>532.0064397282042</x:v>
       </x:c>
       <x:c r="AX31" s="1"/>
       <x:c r="AY31" s="1"/>
@@ -18955,15 +18967,15 @@
       </x:c>
       <x:c r="W32" s="7" t="n">
         <x:f>(N32*'設定と出典'!$B$36+S32)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>139077</x:v>
+        <x:v>124966.511760161</x:v>
       </x:c>
       <x:c r="X32" s="7" t="n">
         <x:f>N32*I32*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>3635.9999999999995</x:v>
+        <x:v>3267.098346670876</x:v>
       </x:c>
       <x:c r="Y32" s="7" t="n">
         <x:f>MAX(0,S32*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S32,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>153100.8</x:v>
+        <x:v>137174.30713178744</x:v>
       </x:c>
       <x:c r="Z32" s="7" t="n">
         <x:f>O32*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I32)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -18987,11 +18999,11 @@
       </x:c>
       <x:c r="AE32" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF32" s="7" t="n">
         <x:f>SUM(U32:AE32)</x:f>
-        <x:v>12665695.238769531</x:v>
+        <x:v>12634919.125426577</x:v>
       </x:c>
       <x:c r="AG32" s="7" t="n">
         <x:f>T32*'設定と出典'!$B$28</x:f>
@@ -19007,47 +19019,47 @@
       </x:c>
       <x:c r="AJ32" s="7" t="n">
         <x:f>T32-SUM(AF32:AI32)</x:f>
-        <x:v>-9651028.572102865</x:v>
+        <x:v>-9620252.458759911</x:v>
       </x:c>
       <x:c r="AK32" s="7" t="n">
         <x:f>AJ32-T32*'設定と出典'!$B$32</x:f>
-        <x:v>-11651028.572102865</x:v>
+        <x:v>-11620252.458759911</x:v>
       </x:c>
       <x:c r="AL32" s="7" t="n">
         <x:f>AJ32-A32*MIN(E32,AV32)*'設定と出典'!$B$32</x:f>
-        <x:v>-9901028.572102865</x:v>
+        <x:v>-9870252.458759911</x:v>
       </x:c>
       <x:c r="AM32" s="8" t="n">
         <x:f>AJ32/T32</x:f>
-        <x:v>-2.412757143025716</x:v>
+        <x:v>-2.4050631146899777</x:v>
       </x:c>
       <x:c r="AN32" s="8" t="n">
         <x:f>AK32/T32</x:f>
-        <x:v>-2.912757143025716</x:v>
+        <x:v>-2.9050631146899777</x:v>
       </x:c>
       <x:c r="AO32" s="8" t="n">
         <x:f>AJ32/T32</x:f>
-        <x:v>-2.412757143025716</x:v>
+        <x:v>-2.4050631146899777</x:v>
       </x:c>
       <x:c r="AP32" s="8" t="n">
         <x:f>AO32-'設定と出典'!$B$33</x:f>
-        <x:v>-2.6127571430257164</x:v>
+        <x:v>-2.605063114689978</x:v>
       </x:c>
       <x:c r="AQ32" s="9" t="n">
         <x:f>SUM(W32:AD32)/N32</x:f>
-        <x:v>6.288348019384766</x:v>
+        <x:v>6.273145078004076</x:v>
       </x:c>
       <x:c r="AR32" s="9" t="n">
         <x:f>MAX(0,(E32*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U32+V32+AH32+AI32+AE32)/A32)/AQ32)</x:f>
-        <x:v>294.407200051002</x:v>
+        <x:v>295.2387313646753</x:v>
       </x:c>
       <x:c r="AS32" s="9" t="n">
         <x:f>MAX(0,(E32*(1-'設定と出典'!$B$28 )-(U32+V32+AH32+AI32+AE32)/A32)/AQ32)</x:f>
-        <x:v>930.5043097639834</x:v>
+        <x:v>932.8774198154578</x:v>
       </x:c>
       <x:c r="AT32" s="9" t="n">
         <x:f>MAX(0,(E32*(1-'設定と出典'!$B$28)-MIN(E32,AV32)*'設定と出典'!$B$32-(U32+V32+AH32+AI32+AE32)/A32)/AQ32)</x:f>
-        <x:v>850.9921710498608</x:v>
+        <x:v>853.17258375911</x:v>
       </x:c>
       <x:c r="AU32" s="9" t="str">
         <x:f>IF((T32*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF32-AE32)-AH32)&lt;=0,"成立せず",(AE32+AI32)/((T32*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF32-AE32)-AH32)/A32))</x:f>
@@ -19156,15 +19168,15 @@
       </x:c>
       <x:c r="W33" s="7" t="n">
         <x:f>(N33*'設定と出典'!$B$36+S33)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>147.7125</x:v>
+        <x:v>132.72587033350433</x:v>
       </x:c>
       <x:c r="X33" s="7" t="n">
         <x:f>N33*I33*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>22.724999999999998</x:v>
+        <x:v>20.41936466669297</x:v>
       </x:c>
       <x:c r="Y33" s="7" t="n">
         <x:f>MAX(0,S33*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S33,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>96.74999999999999</x:v>
+        <x:v>86.74029393819656</x:v>
       </x:c>
       <x:c r="Z33" s="7" t="n">
         <x:f>O33*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I33)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -19188,11 +19200,11 @@
       </x:c>
       <x:c r="AE33" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF33" s="7" t="n">
         <x:f>SUM(U33:AE33)</x:f>
-        <x:v>80622.89985961914</x:v>
+        <x:v>80225.36730698377</x:v>
       </x:c>
       <x:c r="AG33" s="7" t="n">
         <x:f>T33*'設定と出典'!$B$28</x:f>
@@ -19208,51 +19220,51 @@
       </x:c>
       <x:c r="AJ33" s="7" t="n">
         <x:f>T33-SUM(AF33:AI33)</x:f>
-        <x:v>2570043.7668070477</x:v>
+        <x:v>2570441.299359683</x:v>
       </x:c>
       <x:c r="AK33" s="7" t="n">
         <x:f>AJ33-T33*'設定と出典'!$B$32</x:f>
-        <x:v>1070043.7668070477</x:v>
+        <x:v>1070441.299359683</x:v>
       </x:c>
       <x:c r="AL33" s="7" t="n">
         <x:f>AJ33-A33*MIN(E33,AV33)*'設定と出典'!$B$32</x:f>
-        <x:v>2070043.7668070477</x:v>
+        <x:v>2070441.299359683</x:v>
       </x:c>
       <x:c r="AM33" s="8" t="n">
         <x:f>AJ33/T33</x:f>
-        <x:v>0.8566812556023492</x:v>
+        <x:v>0.8568137664532276</x:v>
       </x:c>
       <x:c r="AN33" s="8" t="n">
         <x:f>AK33/T33</x:f>
-        <x:v>0.3566812556023492</x:v>
+        <x:v>0.35681376645322765</x:v>
       </x:c>
       <x:c r="AO33" s="8" t="n">
         <x:f>AJ33/T33</x:f>
-        <x:v>0.8566812556023492</x:v>
+        <x:v>0.8568137664532276</x:v>
       </x:c>
       <x:c r="AP33" s="8" t="n">
         <x:f>AO33-'設定と出典'!$B$33</x:f>
-        <x:v>0.6566812556023491</x:v>
+        <x:v>0.6568137664532276</x:v>
       </x:c>
       <x:c r="AQ33" s="9" t="n">
         <x:f>SUM(W33:AD33)/N33</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR33" s="9" t="n">
         <x:f>MAX(0,(E33*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U33+V33+AH33+AI33+AE33)/A33)/AQ33)</x:f>
-        <x:v>4063.6935907621814</x:v>
+        <x:v>4081.9160526858445</x:v>
       </x:c>
       <x:c r="AS33" s="9" t="n">
         <x:f>MAX(0,(E33*(1-'設定と出典'!$B$28 )-(U33+V33+AH33+AI33+AE33)/A33)/AQ33)</x:f>
-        <x:v>9725.182002792408</x:v>
+        <x:v>9766.83691912562</x:v>
       </x:c>
       <x:c r="AT33" s="9" t="n">
         <x:f>MAX(0,(E33*(1-'設定と出典'!$B$28)-MIN(E33,AV33)*'設定と出典'!$B$32-(U33+V33+AH33+AI33+AE33)/A33)/AQ33)</x:f>
-        <x:v>7838.019198782333</x:v>
+        <x:v>7871.863296979028</x:v>
       </x:c>
       <x:c r="AU33" s="9" t="n">
         <x:f>IF((T33*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF33-AE33)-AH33)&lt;=0,"成立せず",(AE33+AI33)/((T33*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF33-AE33)-AH33)/A33))</x:f>
-        <x:v>20.144994902830618</x:v>
+        <x:v>19.805474095203017</x:v>
       </x:c>
       <x:c r="AV33" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -19260,7 +19272,7 @@
       </x:c>
       <x:c r="AW33" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E33,(AK33/A33-E33*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>1780.4688136630596</x:v>
+        <x:v>1781.974618786678</x:v>
       </x:c>
       <x:c r="AX33" s="1"/>
       <x:c r="AY33" s="1"/>
@@ -19357,15 +19369,15 @@
       </x:c>
       <x:c r="W34" s="7" t="n">
         <x:f>(N34*'設定と出典'!$B$36+S34)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1954.35</x:v>
+        <x:v>1756.065361335596</x:v>
       </x:c>
       <x:c r="X34" s="7" t="n">
         <x:f>N34*I34*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>136.35</x:v>
+        <x:v>122.51618800015784</x:v>
       </x:c>
       <x:c r="Y34" s="7" t="n">
         <x:f>MAX(0,S34*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S34,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1547.9999999999998</x:v>
+        <x:v>1387.844703011145</x:v>
       </x:c>
       <x:c r="Z34" s="7" t="n">
         <x:f>O34*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I34)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -19389,11 +19401,11 @@
       </x:c>
       <x:c r="AE34" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF34" s="7" t="n">
         <x:f>SUM(U34:AE34)</x:f>
-        <x:v>165534.0431884766</x:v>
+        <x:v>164791.5388592497</x:v>
       </x:c>
       <x:c r="AG34" s="7" t="n">
         <x:f>T34*'設定と出典'!$B$28</x:f>
@@ -19409,51 +19421,51 @@
       </x:c>
       <x:c r="AJ34" s="7" t="n">
         <x:f>T34-SUM(AF34:AI34)</x:f>
-        <x:v>2151799.290144857</x:v>
+        <x:v>2152541.794474084</x:v>
       </x:c>
       <x:c r="AK34" s="7" t="n">
         <x:f>AJ34-T34*'設定と出典'!$B$32</x:f>
-        <x:v>651799.290144857</x:v>
+        <x:v>652541.7944740839</x:v>
       </x:c>
       <x:c r="AL34" s="7" t="n">
         <x:f>AJ34-A34*MIN(E34,AV34)*'設定と出典'!$B$32</x:f>
-        <x:v>1651799.290144857</x:v>
+        <x:v>1652541.794474084</x:v>
       </x:c>
       <x:c r="AM34" s="8" t="n">
         <x:f>AJ34/T34</x:f>
-        <x:v>0.7172664300482857</x:v>
+        <x:v>0.7175139314913613</x:v>
       </x:c>
       <x:c r="AN34" s="8" t="n">
         <x:f>AK34/T34</x:f>
-        <x:v>0.21726643004828566</x:v>
+        <x:v>0.2175139314913613</x:v>
       </x:c>
       <x:c r="AO34" s="8" t="n">
         <x:f>AJ34/T34</x:f>
-        <x:v>0.7172664300482857</x:v>
+        <x:v>0.7175139314913613</x:v>
       </x:c>
       <x:c r="AP34" s="8" t="n">
         <x:f>AO34-'設定と出典'!$B$33</x:f>
-        <x:v>0.5172664300482857</x:v>
+        <x:v>0.5175139314913613</x:v>
       </x:c>
       <x:c r="AQ34" s="9" t="n">
         <x:f>SUM(W34:AD34)/N34</x:f>
-        <x:v>0.9153484318847658</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR34" s="9" t="n">
         <x:f>MAX(0,(E34*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U34+V34+AH34+AI34+AE34)/A34)/AQ34)</x:f>
-        <x:v>812.0777918445295</x:v>
+        <x:v>815.8001342839171</x:v>
       </x:c>
       <x:c r="AS34" s="9" t="n">
         <x:f>MAX(0,(E34*(1-'設定と出典'!$B$28 )-(U34+V34+AH34+AI34+AE34)/A34)/AQ34)</x:f>
-        <x:v>2450.7980296794226</x:v>
+        <x:v>2461.2122910504045</x:v>
       </x:c>
       <x:c r="AT34" s="9" t="n">
         <x:f>MAX(0,(E34*(1-'設定と出典'!$B$28)-MIN(E34,AV34)*'設定と出典'!$B$32-(U34+V34+AH34+AI34+AE34)/A34)/AQ34)</x:f>
-        <x:v>1904.557950401125</x:v>
+        <x:v>1912.741572128242</x:v>
       </x:c>
       <x:c r="AU34" s="9" t="n">
         <x:f>IF((T34*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF34-AE34)-AH34)&lt;=0,"成立せず",(AE34+AI34)/((T34*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF34-AE34)-AH34)/A34))</x:f>
-        <x:v>32.64952403688304</x:v>
+        <x:v>32.082330734049414</x:v>
       </x:c>
       <x:c r="AV34" s="9" t="n">
         <x:f>'設定と出典'!D51</x:f>
@@ -19461,7 +19473,7 @@
       </x:c>
       <x:c r="AW34" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E34,(AK34/A34-E34*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>196.20943236688248</x:v>
+        <x:v>199.0219487654697</x:v>
       </x:c>
       <x:c r="AX34" s="1"/>
       <x:c r="AY34" s="1"/>
@@ -19558,15 +19570,15 @@
       </x:c>
       <x:c r="W35" s="7" t="n">
         <x:f>(N35*'設定と出典'!$B$36+S35)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>27815.4</x:v>
+        <x:v>24993.302352032202</x:v>
       </x:c>
       <x:c r="X35" s="7" t="n">
         <x:f>N35*I35*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>727.1999999999999</x:v>
+        <x:v>653.4196693341751</x:v>
       </x:c>
       <x:c r="Y35" s="7" t="n">
         <x:f>MAX(0,S35*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S35,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>27820.800000000003</x:v>
+        <x:v>24931.685891616493</x:v>
       </x:c>
       <x:c r="Z35" s="7" t="n">
         <x:f>O35*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I35)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -19590,11 +19602,11 @@
       </x:c>
       <x:c r="AE35" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF35" s="7" t="n">
         <x:f>SUM(U35:AE35)</x:f>
-        <x:v>2586539.0477539063</x:v>
+        <x:v>2580383.825085315</x:v>
       </x:c>
       <x:c r="AG35" s="7" t="n">
         <x:f>T35*'設定と出典'!$B$28</x:f>
@@ -19610,35 +19622,35 @@
       </x:c>
       <x:c r="AJ35" s="7" t="n">
         <x:f>T35-SUM(AF35:AI35)</x:f>
-        <x:v>-1069205.7144205729</x:v>
+        <x:v>-1063050.491751982</x:v>
       </x:c>
       <x:c r="AK35" s="7" t="n">
         <x:f>AJ35-T35*'設定と出典'!$B$32</x:f>
-        <x:v>-2569205.714420573</x:v>
+        <x:v>-2563050.491751982</x:v>
       </x:c>
       <x:c r="AL35" s="7" t="n">
         <x:f>AJ35-A35*MIN(E35,AV35)*'設定と出典'!$B$32</x:f>
-        <x:v>-1569205.7144205729</x:v>
+        <x:v>-1563050.491751982</x:v>
       </x:c>
       <x:c r="AM35" s="8" t="n">
         <x:f>AJ35/T35</x:f>
-        <x:v>-0.35640190480685763</x:v>
+        <x:v>-0.3543501639173273</x:v>
       </x:c>
       <x:c r="AN35" s="8" t="n">
         <x:f>AK35/T35</x:f>
-        <x:v>-0.8564019048068576</x:v>
+        <x:v>-0.8543501639173273</x:v>
       </x:c>
       <x:c r="AO35" s="8" t="n">
         <x:f>AJ35/T35</x:f>
-        <x:v>-0.35640190480685763</x:v>
+        <x:v>-0.3543501639173273</x:v>
       </x:c>
       <x:c r="AP35" s="8" t="n">
         <x:f>AO35-'設定と出典'!$B$33</x:f>
-        <x:v>-0.5564019048068576</x:v>
+        <x:v>-0.5543501639173274</x:v>
       </x:c>
       <x:c r="AQ35" s="9" t="n">
         <x:f>SUM(W35:AD35)/N35</x:f>
-        <x:v>6.281349619384765</x:v>
+        <x:v>6.266887139167222</x:v>
       </x:c>
       <x:c r="AR35" s="9" t="n">
         <x:f>MAX(0,(E35*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U35+V35+AH35+AI35+AE35)/A35)/AQ35)</x:f>
@@ -19646,11 +19658,11 @@
       </x:c>
       <x:c r="AS35" s="9" t="n">
         <x:f>MAX(0,(E35*(1-'設定と出典'!$B$28 )-(U35+V35+AH35+AI35+AE35)/A35)/AQ35)</x:f>
-        <x:v>229.7808943605184</x:v>
+        <x:v>230.37025110791353</x:v>
       </x:c>
       <x:c r="AT35" s="9" t="n">
         <x:f>MAX(0,(E35*(1-'設定と出典'!$B$28)-MIN(E35,AV35)*'設定と出典'!$B$32-(U35+V35+AH35+AI35+AE35)/A35)/AQ35)</x:f>
-        <x:v>150.1801667625897</x:v>
+        <x:v>150.5858240236813</x:v>
       </x:c>
       <x:c r="AU35" s="9" t="str">
         <x:f>IF((T35*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF35-AE35)-AH35)&lt;=0,"成立せず",(AE35+AI35)/((T35*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF35-AE35)-AH35)/A35))</x:f>
@@ -19759,15 +19771,15 @@
       </x:c>
       <x:c r="W36" s="7" t="n">
         <x:f>(N36*'設定と出典'!$B$36+S36)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>590.85</x:v>
+        <x:v>530.9034813340173</x:v>
       </x:c>
       <x:c r="X36" s="7" t="n">
         <x:f>N36*I36*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>90.89999999999999</x:v>
+        <x:v>81.67745866677188</x:v>
       </x:c>
       <x:c r="Y36" s="7" t="n">
         <x:f>MAX(0,S36*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S36,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>386.99999999999994</x:v>
+        <x:v>346.96117575278623</x:v>
       </x:c>
       <x:c r="Z36" s="7" t="n">
         <x:f>O36*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I36)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -19791,11 +19803,11 @@
       </x:c>
       <x:c r="AE36" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF36" s="7" t="n">
         <x:f>SUM(U36:AE36)</x:f>
-        <x:v>130493.99943847656</x:v>
+        <x:v>130014.56097265639</x:v>
       </x:c>
       <x:c r="AG36" s="7" t="n">
         <x:f>T36*'設定と出典'!$B$28</x:f>
@@ -19811,51 +19823,51 @@
       </x:c>
       <x:c r="AJ36" s="7" t="n">
         <x:f>T36-SUM(AF36:AI36)</x:f>
-        <x:v>4348172.66722819</x:v>
+        <x:v>4348652.105694011</x:v>
       </x:c>
       <x:c r="AK36" s="7" t="n">
         <x:f>AJ36-T36*'設定と出典'!$B$32</x:f>
-        <x:v>1848172.6672281902</x:v>
+        <x:v>1848652.1056940109</x:v>
       </x:c>
       <x:c r="AL36" s="7" t="n">
         <x:f>AJ36-A36*MIN(E36,AV36)*'設定と出典'!$B$32</x:f>
-        <x:v>3848172.66722819</x:v>
+        <x:v>3848652.105694011</x:v>
       </x:c>
       <x:c r="AM36" s="8" t="n">
         <x:f>AJ36/T36</x:f>
-        <x:v>0.869634533445638</x:v>
+        <x:v>0.8697304211388022</x:v>
       </x:c>
       <x:c r="AN36" s="8" t="n">
         <x:f>AK36/T36</x:f>
-        <x:v>0.36963453344563807</x:v>
+        <x:v>0.36973042113880217</x:v>
       </x:c>
       <x:c r="AO36" s="8" t="n">
         <x:f>AJ36/T36</x:f>
-        <x:v>0.869634533445638</x:v>
+        <x:v>0.8697304211388022</x:v>
       </x:c>
       <x:c r="AP36" s="8" t="n">
         <x:f>AO36-'設定と出典'!$B$33</x:f>
-        <x:v>0.669634533445638</x:v>
+        <x:v>0.6697304211388022</x:v>
       </x:c>
       <x:c r="AQ36" s="9" t="n">
         <x:f>SUM(W36:AD36)/N36</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR36" s="9" t="n">
         <x:f>MAX(0,(E36*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U36+V36+AH36+AI36+AE36)/A36)/AQ36)</x:f>
-        <x:v>7075.605425962262</x:v>
+        <x:v>7106.293953631805</x:v>
       </x:c>
       <x:c r="AS36" s="9" t="n">
         <x:f>MAX(0,(E36*(1-'設定と出典'!$B$28 )-(U36+V36+AH36+AI36+AE36)/A36)/AQ36)</x:f>
-        <x:v>16511.41944601264</x:v>
+        <x:v>16581.162064364766</x:v>
       </x:c>
       <x:c r="AT36" s="9" t="n">
         <x:f>MAX(0,(E36*(1-'設定と出典'!$B$28)-MIN(E36,AV36)*'設定と出典'!$B$32-(U36+V36+AH36+AI36+AE36)/A36)/AQ36)</x:f>
-        <x:v>14624.256642002563</x:v>
+        <x:v>14686.188442218172</x:v>
       </x:c>
       <x:c r="AU36" s="9" t="n">
         <x:f>IF((T36*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF36-AE36)-AH36)&lt;=0,"成立せず",(AE36+AI36)/((T36*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF36-AE36)-AH36)/A36))</x:f>
-        <x:v>11.763196947564689</x:v>
+        <x:v>11.564555566668481</x:v>
       </x:c>
       <x:c r="AV36" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -19863,7 +19875,7 @@
       </x:c>
       <x:c r="AW36" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E36,(AK36/A36-E36*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>3212.775254652236</x:v>
+        <x:v>3214.591309447011</x:v>
       </x:c>
       <x:c r="AX36" s="1"/>
       <x:c r="AY36" s="1"/>
@@ -19960,15 +19972,15 @@
       </x:c>
       <x:c r="W37" s="7" t="n">
         <x:f>(N37*'設定と出典'!$B$36+S37)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>7817.4</x:v>
+        <x:v>7024.261445342384</x:v>
       </x:c>
       <x:c r="X37" s="7" t="n">
         <x:f>N37*I37*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>545.4</x:v>
+        <x:v>490.06475200063136</x:v>
       </x:c>
       <x:c r="Y37" s="7" t="n">
         <x:f>MAX(0,S37*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S37,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>6191.999999999999</x:v>
+        <x:v>5551.37881204458</x:v>
       </x:c>
       <x:c r="Z37" s="7" t="n">
         <x:f>O37*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I37)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -19992,11 +20004,11 @@
       </x:c>
       <x:c r="AE37" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF37" s="7" t="n">
         <x:f>SUM(U37:AE37)</x:f>
-        <x:v>470138.57275390625</x:v>
+        <x:v>468279.24718172004</x:v>
       </x:c>
       <x:c r="AG37" s="7" t="n">
         <x:f>T37*'設定と出典'!$B$28</x:f>
@@ -20012,51 +20024,51 @@
       </x:c>
       <x:c r="AJ37" s="7" t="n">
         <x:f>T37-SUM(AF37:AI37)</x:f>
-        <x:v>3675194.7605794272</x:v>
+        <x:v>3677054.0861516134</x:v>
       </x:c>
       <x:c r="AK37" s="7" t="n">
         <x:f>AJ37-T37*'設定と出典'!$B$32</x:f>
-        <x:v>1175194.7605794272</x:v>
+        <x:v>1177054.0861516134</x:v>
       </x:c>
       <x:c r="AL37" s="7" t="n">
         <x:f>AJ37-A37*MIN(E37,AV37)*'設定と出典'!$B$32</x:f>
-        <x:v>3175194.7605794272</x:v>
+        <x:v>3177054.0861516134</x:v>
       </x:c>
       <x:c r="AM37" s="8" t="n">
         <x:f>AJ37/T37</x:f>
-        <x:v>0.7350389521158854</x:v>
+        <x:v>0.7354108172303226</x:v>
       </x:c>
       <x:c r="AN37" s="8" t="n">
         <x:f>AK37/T37</x:f>
-        <x:v>0.23503895211588544</x:v>
+        <x:v>0.23541081723032267</x:v>
       </x:c>
       <x:c r="AO37" s="8" t="n">
         <x:f>AJ37/T37</x:f>
-        <x:v>0.7350389521158854</x:v>
+        <x:v>0.7354108172303226</x:v>
       </x:c>
       <x:c r="AP37" s="8" t="n">
         <x:f>AO37-'設定と出典'!$B$33</x:f>
-        <x:v>0.5350389521158854</x:v>
+        <x:v>0.5354108172303227</x:v>
       </x:c>
       <x:c r="AQ37" s="9" t="n">
         <x:f>SUM(W37:AD37)/N37</x:f>
-        <x:v>0.9153484318847658</x:v>
+        <x:v>0.9116256944082346</x:v>
       </x:c>
       <x:c r="AR37" s="9" t="n">
         <x:f>MAX(0,(E37*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U37+V37+AH37+AI37+AE37)/A37)/AQ37)</x:f>
-        <x:v>1683.8769583726928</x:v>
+        <x:v>1691.1594016836884</x:v>
       </x:c>
       <x:c r="AS37" s="9" t="n">
         <x:f>MAX(0,(E37*(1-'設定と出典'!$B$28 )-(U37+V37+AH37+AI37+AE37)/A37)/AQ37)</x:f>
-        <x:v>4415.077354764181</x:v>
+        <x:v>4433.5129962945</x:v>
       </x:c>
       <x:c r="AT37" s="9" t="n">
         <x:f>MAX(0,(E37*(1-'設定と出典'!$B$28)-MIN(E37,AV37)*'設定と出典'!$B$32-(U37+V37+AH37+AI37+AE37)/A37)/AQ37)</x:f>
-        <x:v>3868.8372754858838</x:v>
+        <x:v>3885.042277372338</x:v>
       </x:c>
       <x:c r="AU37" s="9" t="n">
         <x:f>IF((T37*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF37-AE37)-AH37)&lt;=0,"成立せず",(AE37+AI37)/((T37*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF37-AE37)-AH37)/A37))</x:f>
-        <x:v>18.37563563163371</x:v>
+        <x:v>18.043943574509345</x:v>
       </x:c>
       <x:c r="AV37" s="9" t="n">
         <x:f>'設定と出典'!D52</x:f>
@@ -20064,7 +20076,7 @@
       </x:c>
       <x:c r="AW37" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E37,(AK37/A37-E37*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>663.6165173463157</x:v>
+        <x:v>670.6594172409597</x:v>
       </x:c>
       <x:c r="AX37" s="1"/>
       <x:c r="AY37" s="1"/>
@@ -20161,15 +20173,15 @@
       </x:c>
       <x:c r="W38" s="7" t="n">
         <x:f>(N38*'設定と出典'!$B$36+S38)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>111261.6</x:v>
+        <x:v>99973.20940812881</x:v>
       </x:c>
       <x:c r="X38" s="7" t="n">
         <x:f>N38*I38*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>2908.7999999999997</x:v>
+        <x:v>2613.6786773367003</x:v>
       </x:c>
       <x:c r="Y38" s="7" t="n">
         <x:f>MAX(0,S38*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S38,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>121780.79999999999</x:v>
+        <x:v>109113.6518217447</x:v>
       </x:c>
       <x:c r="Z38" s="7" t="n">
         <x:f>O38*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I38)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -20193,11 +20205,11 @@
       </x:c>
       <x:c r="AE38" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF38" s="7" t="n">
         <x:f>SUM(U38:AE38)</x:f>
-        <x:v>10164656.191015624</x:v>
+        <x:v>10140035.300341262</x:v>
       </x:c>
       <x:c r="AG38" s="7" t="n">
         <x:f>T38*'設定と出典'!$B$28</x:f>
@@ -20213,47 +20225,47 @@
       </x:c>
       <x:c r="AJ38" s="7" t="n">
         <x:f>T38-SUM(AF38:AI38)</x:f>
-        <x:v>-6819322.85768229</x:v>
+        <x:v>-6794701.967007928</x:v>
       </x:c>
       <x:c r="AK38" s="7" t="n">
         <x:f>AJ38-T38*'設定と出典'!$B$32</x:f>
-        <x:v>-9319322.85768229</x:v>
+        <x:v>-9294701.967007928</x:v>
       </x:c>
       <x:c r="AL38" s="7" t="n">
         <x:f>AJ38-A38*MIN(E38,AV38)*'設定と出典'!$B$32</x:f>
-        <x:v>-7319322.85768229</x:v>
+        <x:v>-7294701.967007928</x:v>
       </x:c>
       <x:c r="AM38" s="8" t="n">
         <x:f>AJ38/T38</x:f>
-        <x:v>-1.363864571536458</x:v>
+        <x:v>-1.3589403934015856</x:v>
       </x:c>
       <x:c r="AN38" s="8" t="n">
         <x:f>AK38/T38</x:f>
-        <x:v>-1.863864571536458</x:v>
+        <x:v>-1.8589403934015856</x:v>
       </x:c>
       <x:c r="AO38" s="8" t="n">
         <x:f>AJ38/T38</x:f>
-        <x:v>-1.363864571536458</x:v>
+        <x:v>-1.3589403934015856</x:v>
       </x:c>
       <x:c r="AP38" s="8" t="n">
         <x:f>AO38-'設定と出典'!$B$33</x:f>
-        <x:v>-1.5638645715364579</x:v>
+        <x:v>-1.5589403934015855</x:v>
       </x:c>
       <x:c r="AQ38" s="9" t="n">
         <x:f>SUM(W38:AD38)/N38</x:f>
-        <x:v>6.287910619384765</x:v>
+        <x:v>6.272753956826771</x:v>
       </x:c>
       <x:c r="AR38" s="9" t="n">
         <x:f>MAX(0,(E38*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U38+V38+AH38+AI38+AE38)/A38)/AQ38)</x:f>
-        <x:v>117.8983255658727</x:v>
+        <x:v>118.24222168122732</x:v>
       </x:c>
       <x:c r="AS38" s="9" t="n">
         <x:f>MAX(0,(E38*(1-'設定と出典'!$B$28 )-(U38+V38+AH38+AI38+AE38)/A38)/AQ38)</x:f>
-        <x:v>515.4866742763081</x:v>
+        <x:v>516.7912508965685</x:v>
       </x:c>
       <x:c r="AT38" s="9" t="n">
         <x:f>MAX(0,(E38*(1-'設定と出典'!$B$28)-MIN(E38,AV38)*'設定と出典'!$B$32-(U38+V38+AH38+AI38+AE38)/A38)/AQ38)</x:f>
-        <x:v>435.969004534221</x:v>
+        <x:v>437.08144505350026</x:v>
       </x:c>
       <x:c r="AU38" s="9" t="str">
         <x:f>IF((T38*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF38-AE38)-AH38)&lt;=0,"成立せず",(AE38+AI38)/((T38*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF38-AE38)-AH38)/A38))</x:f>
@@ -20362,15 +20374,15 @@
       </x:c>
       <x:c r="W39" s="7" t="n">
         <x:f>(N39*'設定と出典'!$B$36+S39)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1477.125</x:v>
+        <x:v>1327.2587033350433</x:v>
       </x:c>
       <x:c r="X39" s="7" t="n">
         <x:f>N39*I39*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>227.24999999999997</x:v>
+        <x:v>204.19364666692974</x:v>
       </x:c>
       <x:c r="Y39" s="7" t="n">
         <x:f>MAX(0,S39*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S39,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>967.5</x:v>
+        <x:v>867.4029393819657</x:v>
       </x:c>
       <x:c r="Z39" s="7" t="n">
         <x:f>O39*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I39)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -20394,11 +20406,11 @@
       </x:c>
       <x:c r="AE39" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF39" s="7" t="n">
         <x:f>SUM(U39:AE39)</x:f>
-        <x:v>230236.19859619142</x:v>
+        <x:v>229592.94830400162</x:v>
       </x:c>
       <x:c r="AG39" s="7" t="n">
         <x:f>T39*'設定と出典'!$B$28</x:f>
@@ -20414,51 +20426,51 @@
       </x:c>
       <x:c r="AJ39" s="7" t="n">
         <x:f>T39-SUM(AF39:AI39)</x:f>
-        <x:v>6940430.468070475</x:v>
+        <x:v>6941073.718362665</x:v>
       </x:c>
       <x:c r="AK39" s="7" t="n">
         <x:f>AJ39-T39*'設定と出典'!$B$32</x:f>
-        <x:v>2940430.4680704754</x:v>
+        <x:v>2941073.718362665</x:v>
       </x:c>
       <x:c r="AL39" s="7" t="n">
         <x:f>AJ39-A39*MIN(E39,AV39)*'設定と出典'!$B$32</x:f>
-        <x:v>6440430.468070475</x:v>
+        <x:v>6441073.718362665</x:v>
       </x:c>
       <x:c r="AM39" s="8" t="n">
         <x:f>AJ39/T39</x:f>
-        <x:v>0.8675538085088095</x:v>
+        <x:v>0.8676342147953331</x:v>
       </x:c>
       <x:c r="AN39" s="8" t="n">
         <x:f>AK39/T39</x:f>
-        <x:v>0.3675538085088094</x:v>
+        <x:v>0.3676342147953331</x:v>
       </x:c>
       <x:c r="AO39" s="8" t="n">
         <x:f>AJ39/T39</x:f>
-        <x:v>0.8675538085088095</x:v>
+        <x:v>0.8676342147953331</x:v>
       </x:c>
       <x:c r="AP39" s="8" t="n">
         <x:f>AO39-'設定と出典'!$B$33</x:f>
-        <x:v>0.6675538085088095</x:v>
+        <x:v>0.6676342147953331</x:v>
       </x:c>
       <x:c r="AQ39" s="9" t="n">
         <x:f>SUM(W39:AD39)/N39</x:f>
-        <x:v>0.26494799438476563</x:v>
+        <x:v>0.26385591554230137</x:v>
       </x:c>
       <x:c r="AR39" s="9" t="n">
         <x:f>MAX(0,(E39*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U39+V39+AH39+AI39+AE39)/A39)/AQ39)</x:f>
-        <x:v>11348.142014241072</x:v>
+        <x:v>11396.514234171687</x:v>
       </x:c>
       <x:c r="AS39" s="9" t="n">
         <x:f>MAX(0,(E39*(1-'設定と出典'!$B$28 )-(U39+V39+AH39+AI39+AE39)/A39)/AQ39)</x:f>
-        <x:v>26445.444446321675</x:v>
+        <x:v>26556.30321134442</x:v>
       </x:c>
       <x:c r="AT39" s="9" t="n">
         <x:f>MAX(0,(E39*(1-'設定と出典'!$B$28)-MIN(E39,AV39)*'設定と出典'!$B$32-(U39+V39+AH39+AI39+AE39)/A39)/AQ39)</x:f>
-        <x:v>24558.281642311602</x:v>
+        <x:v>24661.32958919783</x:v>
       </x:c>
       <x:c r="AU39" s="9" t="n">
         <x:f>IF((T39*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF39-AE39)-AH39)&lt;=0,"成立せず",(AE39+AI39)/((T39*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF39-AE39)-AH39)/A39))</x:f>
-        <x:v>7.426066595643023</x:v>
+        <x:v>7.300418468457666</x:v>
       </x:c>
       <x:c r="AV39" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -20466,7 +20478,7 @@
       </x:c>
       <x:c r="AW39" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E39,(AK39/A39-E39*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>5077.3881366305895</x:v>
+        <x:v>5079.82469076767</x:v>
       </x:c>
       <x:c r="AX39" s="1"/>
       <x:c r="AY39" s="1"/>
@@ -20563,15 +20575,15 @@
       </x:c>
       <x:c r="W40" s="7" t="n">
         <x:f>(N40*'設定と出典'!$B$36+S40)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>19543.5</x:v>
+        <x:v>17560.65361335596</x:v>
       </x:c>
       <x:c r="X40" s="7" t="n">
         <x:f>N40*I40*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>1363.5</x:v>
+        <x:v>1225.1618800015785</x:v>
       </x:c>
       <x:c r="Y40" s="7" t="n">
         <x:f>MAX(0,S40*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S40,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>17380.8</x:v>
+        <x:v>15578.13412160225</x:v>
       </x:c>
       <x:c r="Z40" s="7" t="n">
         <x:f>O40*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I40)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -20595,11 +20607,11 @@
       </x:c>
       <x:c r="AE40" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF40" s="7" t="n">
         <x:f>SUM(U40:AE40)</x:f>
-        <x:v>1081248.4318847656</x:v>
+        <x:v>1076954.3509181517</x:v>
       </x:c>
       <x:c r="AG40" s="7" t="n">
         <x:f>T40*'設定と出典'!$B$28</x:f>
@@ -20615,51 +20627,51 @@
       </x:c>
       <x:c r="AJ40" s="7" t="n">
         <x:f>T40-SUM(AF40:AI40)</x:f>
-        <x:v>5756084.901448568</x:v>
+        <x:v>5760378.982415182</x:v>
       </x:c>
       <x:c r="AK40" s="7" t="n">
         <x:f>AJ40-T40*'設定と出典'!$B$32</x:f>
-        <x:v>1756084.9014485683</x:v>
+        <x:v>1760378.9824151816</x:v>
       </x:c>
       <x:c r="AL40" s="7" t="n">
         <x:f>AJ40-A40*MIN(E40,AV40)*'設定と出典'!$B$32</x:f>
-        <x:v>5256084.901448568</x:v>
+        <x:v>5260378.982415182</x:v>
       </x:c>
       <x:c r="AM40" s="8" t="n">
         <x:f>AJ40/T40</x:f>
-        <x:v>0.7195106126810711</x:v>
+        <x:v>0.7200473728018977</x:v>
       </x:c>
       <x:c r="AN40" s="8" t="n">
         <x:f>AK40/T40</x:f>
-        <x:v>0.21951061268107105</x:v>
+        <x:v>0.2200473728018977</x:v>
       </x:c>
       <x:c r="AO40" s="8" t="n">
         <x:f>AJ40/T40</x:f>
-        <x:v>0.7195106126810711</x:v>
+        <x:v>0.7200473728018977</x:v>
       </x:c>
       <x:c r="AP40" s="8" t="n">
         <x:f>AO40-'設定と出典'!$B$33</x:f>
-        <x:v>0.5195106126810711</x:v>
+        <x:v>0.5200473728018977</x:v>
       </x:c>
       <x:c r="AQ40" s="9" t="n">
         <x:f>SUM(W40:AD40)/N40</x:f>
-        <x:v>0.9172492318847657</x:v>
+        <x:v>0.9133253814997254</x:v>
       </x:c>
       <x:c r="AR40" s="9" t="n">
         <x:f>MAX(0,(E40*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U40+V40+AH40+AI40+AE40)/A40)/AQ40)</x:f>
-        <x:v>2914.512261667595</x:v>
+        <x:v>2927.4390245506506</x:v>
       </x:c>
       <x:c r="AS40" s="9" t="n">
         <x:f>MAX(0,(E40*(1-'設定と出典'!$B$28 )-(U40+V40+AH40+AI40+AE40)/A40)/AQ40)</x:f>
-        <x:v>7275.37718360467</x:v>
+        <x:v>7307.039198841003</x:v>
       </x:c>
       <x:c r="AT40" s="9" t="n">
         <x:f>MAX(0,(E40*(1-'設定と出典'!$B$28)-MIN(E40,AV40)*'設定と出典'!$B$32-(U40+V40+AH40+AI40+AE40)/A40)/AQ40)</x:f>
-        <x:v>6730.269068362536</x:v>
+        <x:v>6759.589177054709</x:v>
       </x:c>
       <x:c r="AU40" s="9" t="n">
         <x:f>IF((T40*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF40-AE40)-AH40)&lt;=0,"成立せず",(AE40+AI40)/((T40*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF40-AE40)-AH40)/A40))</x:f>
-        <x:v>12.372418144944731</x:v>
+        <x:v>12.13741464855473</x:v>
       </x:c>
       <x:c r="AV40" s="9" t="n">
         <x:f>'設定と出典'!D53</x:f>
@@ -20667,7 +20679,7 @@
       </x:c>
       <x:c r="AW40" s="9" t="n">
         <x:f>IF(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33&lt;=0,0,MAX(0,MIN(E40,(AK40/A40-E40*'設定と出典'!$B$33)/(1-'設定と出典'!$B$28-'設定と出典'!$B$32-'設定と出典'!$B$33))))</x:f>
-        <x:v>591.2306873051834</x:v>
+        <x:v>607.4961455120514</x:v>
       </x:c>
       <x:c r="AX40" s="1"/>
       <x:c r="AY40" s="1"/>
@@ -20764,15 +20776,15 @@
       </x:c>
       <x:c r="W41" s="7" t="n">
         <x:f>(N41*'設定と出典'!$B$36+S41)*('設定と出典'!$B$43*'設定と出典'!$B$8+'設定と出典'!$B$44*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>278154</x:v>
+        <x:v>249933.023520322</x:v>
       </x:c>
       <x:c r="X41" s="7" t="n">
         <x:f>N41*I41*'設定と出典'!$B$37*('設定と出典'!$B$45*'設定と出典'!$B$8+'設定と出典'!$B$46*'設定と出典'!$B$9)*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>7271.999999999999</x:v>
+        <x:v>6534.196693341752</x:v>
       </x:c>
       <x:c r="Y41" s="7" t="n">
         <x:f>MAX(0,S41*('設定と出典'!$B$13*'設定と出典'!$B$8+'設定と出典'!$B$14*'設定と出典'!$B$9)-MIN(S41,'設定と出典'!$B$7*86400*'設定と出典'!$B$15)*('設定と出典'!$B$13*'設定と出典'!$B$10+'設定と出典'!$B$14*'設定と出典'!$B$11))*'設定と出典'!$B$12*'設定と出典'!$B$6</x:f>
-        <x:v>309700.8</x:v>
+        <x:v>277477.5836820011</x:v>
       </x:c>
       <x:c r="Z41" s="7" t="n">
         <x:f>O41*('設定と出典'!$B$41*'設定と出典'!$B$18+('設定と出典'!$B$42+I41)*'設定と出典'!$B$19)/1000*'設定と出典'!$B$6</x:f>
@@ -20796,11 +20808,11 @@
       </x:c>
       <x:c r="AE41" s="7" t="n">
         <x:f>'設定と出典'!B63</x:f>
-        <x:v>13999.2</x:v>
+        <x:v>13628.969418426243</x:v>
       </x:c>
       <x:c r="AF41" s="7" t="n">
         <x:f>SUM(U41:AE41)</x:f>
-        <x:v>25320890.477539062</x:v>
+        <x:v>25259338.25085315</x:v>
       </x:c>
       <x:c r="AG41" s="7" t="n">
         <x:f>T41*'設定と出典'!$B$28</x:f>
@@ -20816,47 +20828,47 @@
       </x:c>
       <x:c r="AJ41" s="7" t="n">
         <x:f>T41-SUM(AF41:AI41)</x:f>
-        <x:v>-19283557.14420573</x:v>
+        <x:v>-19222004.91751982</x:v>
       </x:c>
       <x:c r="AK41" s="7" t="n">
         <x:f>AJ41-T41*'設定と出典'!$B$32</x:f>
-        <x:v>-23283557.14420573</x:v>
+        <x:v>-23222004.91751982</x:v>
       </x:c>
       <x:c r="AL41" s="7" t="n">
         <x:f>AJ41-A41*MIN(E41,AV41)*'設定と出典'!$B$32</x:f>
-        <x:v>-19783557.14420573</x:v>
+        <x:v>-19722004.91751982</x:v>
       </x:c>
       <x:c r="AM41" s="8" t="n">
         <x:f>AJ41/T41</x:f>
-        <x:v>-2.4104446430257163</x:v>
+        <x:v>-2.4027506146899773</x:v>
       </x:c>
       <x:c r="AN41" s="8" t="n">
         <x:f>AK41/T41</x:f>
-        <x:v>-2.9104446430257163</x:v>
+        <x:v>-2.9027506146899773</x:v>
       </x:c>
       <x:c r="AO41" s="8" t="n">
         <x:f>AJ41/T41</x:f>
-        <x:v>-2.4104446430257163</x:v>
+        <x:v>-2.4027506146899773</x:v>
       </x:c>
       <x:c r="AP41" s="8" t="n">
         <x:f>AO41-'設定と出典'!$B$33</x:f>
-        <x:v>-2.6104446430257164</x:v>
+        <x:v>-2.6027506146899775</x:v>
       </x:c>
       <x:c r="AQ41" s="9" t="n">
         <x:f>SUM(W41:AD41)/N41</x:f>
-        <x:v>6.289222819384766</x:v>
+        <x:v>6.273927320358681</x:v>
       </x:c>
       <x:c r="AR41" s="9" t="n">
         <x:f>MAX(0,(E41*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(U41+V41+AH41+AI41+AE41)/A41)/AQ41)</x:f>
-        <x:v>297.8641697284608</x:v>
+        <x:v>298.64935760967444</x:v>
       </x:c>
       <x:c r="AS41" s="9" t="n">
         <x:f>MAX(0,(E41*(1-'設定と出典'!$B$28 )-(U41+V41+AH41+AI41+AE41)/A41)/AQ41)</x:f>
-        <x:v>933.8728014581433</x:v>
+        <x:v>936.2085443442954</x:v>
       </x:c>
       <x:c r="AT41" s="9" t="n">
         <x:f>MAX(0,(E41*(1-'設定と出典'!$B$28)-MIN(E41,AV41)*'設定と出典'!$B$32-(U41+V41+AH41+AI41+AE41)/A41)/AQ41)</x:f>
-        <x:v>854.371722491933</x:v>
+        <x:v>856.5136460024678</x:v>
       </x:c>
       <x:c r="AU41" s="9" t="str">
         <x:f>IF((T41*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF41-AE41)-AH41)&lt;=0,"成立せず",(AE41+AI41)/((T41*(1-'設定と出典'!$B$28-'設定と出典'!$B$32)-(AF41-AE41)-AH41)/A41))</x:f>
@@ -24134,10 +24146,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="33" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
@@ -24246,7 +24258,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="10" t="str">
-        <x:v>実績取得状況 2026-10-17</x:v>
+        <x:v>実績取得状況 2026-10-18</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -24303,7 +24315,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>対象: 2026年7〜9月の完了月、10月は部分月。未取得を0円・0件に置換しない。</x:v>
+        <x:v>7〜9月は四半期合計のみ取得。月別へ分割しない。10月は請求反映時点不明の途中値。</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -24492,7 +24504,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E6" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F6" s="1"/>
       <x:c r="G6" s="1"/>
@@ -24557,7 +24569,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E7" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F7" s="1"/>
       <x:c r="G7" s="1"/>
@@ -24622,7 +24634,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E8" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F8" s="1"/>
       <x:c r="G8" s="1"/>
@@ -24687,7 +24699,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E9" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F9" s="1"/>
       <x:c r="G9" s="1"/>
@@ -24752,7 +24764,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E10" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F10" s="1"/>
       <x:c r="G10" s="1"/>
@@ -24817,7 +24829,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E11" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F11" s="1"/>
       <x:c r="G11" s="1"/>
@@ -24882,7 +24894,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E12" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F12" s="1"/>
       <x:c r="G12" s="1"/>
@@ -24947,7 +24959,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E13" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>メール費は未取得。Google Cloud CSVに外部SMTP料金は含まれない。</x:v>
       </x:c>
       <x:c r="F13" s="1"/>
       <x:c r="G13" s="1"/>
@@ -25012,7 +25024,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E14" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F14" s="1"/>
       <x:c r="G14" s="1"/>
@@ -25077,7 +25089,7 @@
         <x:v>未取得</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
-        <x:v>請求export/構成/メトリクス未取得</x:v>
+        <x:v>共有請求取得済・サービス別帰属未確定。四半期合計は下表。</x:v>
       </x:c>
       <x:c r="F15" s="1"/>
       <x:c r="G15" s="1"/>
@@ -25890,7 +25902,7 @@
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="1" t="str">
-        <x:v>gcloud: credentials.dbアクセス拒否。ブラウザ参照: 起動失敗。顧客内容・宛先・OTP・ファイル名は未取得。</x:v>
+        <x:v>Monitoring取得済: upload/download/scan、GCS、共有SQL。業務SQL集計は未取得。</x:v>
       </x:c>
       <x:c r="B28" s="1"/>
       <x:c r="C28" s="1"/>
@@ -26055,12 +26067,22 @@
       <x:c r="AZ30" s="1"/>
       <x:c r="BA30" s="1"/>
     </x:row>
-    <x:row r="31" ht="22" customHeight="1">
-      <x:c r="A31" s="1"/>
-      <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
+    <x:row r="31" ht="30" customHeight="1">
+      <x:c r="A31" s="12" t="str">
+        <x:v>共有請求・円</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>7〜9月削減前</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="str">
+        <x:v>7〜9月削減後</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="str">
+        <x:v>10月途中削減後</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>区分・出典</x:v>
+      </x:c>
       <x:c r="F31" s="1"/>
       <x:c r="G31" s="1"/>
       <x:c r="H31" s="1"/>
@@ -26110,12 +26132,22 @@
       <x:c r="AZ31" s="1"/>
       <x:c r="BA31" s="1"/>
     </x:row>
-    <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="1"/>
-      <x:c r="B32" s="1"/>
-      <x:c r="C32" s="1"/>
-      <x:c r="D32" s="1"/>
-      <x:c r="E32" s="1"/>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" s="1" t="str">
+        <x:v>Compute Engine</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="n">
+        <x:v>50602</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="n">
+        <x:v>24432.66044800001</x:v>
+      </x:c>
+      <x:c r="D32" s="13" t="n">
+        <x:v>12688.418686</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F32" s="1"/>
       <x:c r="G32" s="1"/>
       <x:c r="H32" s="1"/>
@@ -26165,12 +26197,22 @@
       <x:c r="AZ32" s="1"/>
       <x:c r="BA32" s="1"/>
     </x:row>
-    <x:row r="33" ht="22" customHeight="1">
-      <x:c r="A33" s="1"/>
-      <x:c r="B33" s="1"/>
-      <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
+    <x:row r="33" ht="36" customHeight="1">
+      <x:c r="A33" s="1" t="str">
+        <x:v>Cloud Monitoring</x:v>
+      </x:c>
+      <x:c r="B33" s="13" t="n">
+        <x:v>8125</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="n">
+        <x:v>5080.545401</x:v>
+      </x:c>
+      <x:c r="D33" s="13" t="str">
+        <x:v>未掲載</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F33" s="1"/>
       <x:c r="G33" s="1"/>
       <x:c r="H33" s="1"/>
@@ -26220,12 +26262,22 @@
       <x:c r="AZ33" s="1"/>
       <x:c r="BA33" s="1"/>
     </x:row>
-    <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="1"/>
-      <x:c r="B34" s="1"/>
-      <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
+    <x:row r="34" ht="36" customHeight="1">
+      <x:c r="A34" s="1" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="B34" s="13" t="n">
+        <x:v>18041</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="n">
+        <x:v>3857.1839500000006</x:v>
+      </x:c>
+      <x:c r="D34" s="13" t="n">
+        <x:v>1521.672566</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F34" s="1"/>
       <x:c r="G34" s="1"/>
       <x:c r="H34" s="1"/>
@@ -26275,12 +26327,22 @@
       <x:c r="AZ34" s="1"/>
       <x:c r="BA34" s="1"/>
     </x:row>
-    <x:row r="35" ht="22" customHeight="1">
-      <x:c r="A35" s="1"/>
-      <x:c r="B35" s="1"/>
-      <x:c r="C35" s="1"/>
-      <x:c r="D35" s="1"/>
-      <x:c r="E35" s="1"/>
+    <x:row r="35" ht="36" customHeight="1">
+      <x:c r="A35" s="1" t="str">
+        <x:v>Cloud Run</x:v>
+      </x:c>
+      <x:c r="B35" s="13" t="n">
+        <x:v>8360</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="n">
+        <x:v>5388.879989</x:v>
+      </x:c>
+      <x:c r="D35" s="13" t="n">
+        <x:v>1989.350788</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F35" s="1"/>
       <x:c r="G35" s="1"/>
       <x:c r="H35" s="1"/>
@@ -26330,12 +26392,22 @@
       <x:c r="AZ35" s="1"/>
       <x:c r="BA35" s="1"/>
     </x:row>
-    <x:row r="36" ht="22" customHeight="1">
-      <x:c r="A36" s="1"/>
-      <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
+    <x:row r="36" ht="36" customHeight="1">
+      <x:c r="A36" s="1" t="str">
+        <x:v>Cloud SQL</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="n">
+        <x:v>6607</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="n">
+        <x:v>3113.53266</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="n">
+        <x:v>2082.418572</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F36" s="1"/>
       <x:c r="G36" s="1"/>
       <x:c r="H36" s="1"/>
@@ -26385,12 +26457,22 @@
       <x:c r="AZ36" s="1"/>
       <x:c r="BA36" s="1"/>
     </x:row>
-    <x:row r="37" ht="22" customHeight="1">
-      <x:c r="A37" s="1"/>
-      <x:c r="B37" s="1"/>
-      <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-      <x:c r="E37" s="1"/>
+    <x:row r="37" ht="36" customHeight="1">
+      <x:c r="A37" s="1" t="str">
+        <x:v>Secret Manager</x:v>
+      </x:c>
+      <x:c r="B37" s="13" t="n">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="n">
+        <x:v>554.297455</x:v>
+      </x:c>
+      <x:c r="D37" s="13" t="n">
+        <x:v>244.160239</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F37" s="1"/>
       <x:c r="G37" s="1"/>
       <x:c r="H37" s="1"/>
@@ -26440,12 +26522,22 @@
       <x:c r="AZ37" s="1"/>
       <x:c r="BA37" s="1"/>
     </x:row>
-    <x:row r="38" ht="22" customHeight="1">
-      <x:c r="A38" s="1"/>
-      <x:c r="B38" s="1"/>
-      <x:c r="C38" s="1"/>
-      <x:c r="D38" s="1"/>
-      <x:c r="E38" s="1"/>
+    <x:row r="38" ht="36" customHeight="1">
+      <x:c r="A38" s="1" t="str">
+        <x:v>Artifact Registry</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="n">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="n">
+        <x:v>385.632419</x:v>
+      </x:c>
+      <x:c r="D38" s="13" t="n">
+        <x:v>221.630676</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F38" s="1"/>
       <x:c r="G38" s="1"/>
       <x:c r="H38" s="1"/>
@@ -26495,12 +26587,22 @@
       <x:c r="AZ38" s="1"/>
       <x:c r="BA38" s="1"/>
     </x:row>
-    <x:row r="39" ht="22" customHeight="1">
-      <x:c r="A39" s="1"/>
-      <x:c r="B39" s="1"/>
-      <x:c r="C39" s="1"/>
-      <x:c r="D39" s="1"/>
-      <x:c r="E39" s="1"/>
+    <x:row r="39" ht="36" customHeight="1">
+      <x:c r="A39" s="1" t="str">
+        <x:v>Cloud Storage</x:v>
+      </x:c>
+      <x:c r="B39" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C39" s="13" t="n">
+        <x:v>5.433957</x:v>
+      </x:c>
+      <x:c r="D39" s="13" t="n">
+        <x:v>2.260783</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F39" s="1"/>
       <x:c r="G39" s="1"/>
       <x:c r="H39" s="1"/>
@@ -26550,12 +26652,22 @@
       <x:c r="AZ39" s="1"/>
       <x:c r="BA39" s="1"/>
     </x:row>
-    <x:row r="40" ht="22" customHeight="1">
-      <x:c r="A40" s="1"/>
-      <x:c r="B40" s="1"/>
-      <x:c r="C40" s="1"/>
-      <x:c r="D40" s="1"/>
-      <x:c r="E40" s="1"/>
+    <x:row r="40" ht="36" customHeight="1">
+      <x:c r="A40" s="1" t="str">
+        <x:v>Cloud Build</x:v>
+      </x:c>
+      <x:c r="B40" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="13" t="n">
+        <x:v>0.021338</x:v>
+      </x:c>
+      <x:c r="D40" s="13" t="n">
+        <x:v>11.300221</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F40" s="1"/>
       <x:c r="G40" s="1"/>
       <x:c r="H40" s="1"/>
@@ -26605,12 +26717,22 @@
       <x:c r="AZ40" s="1"/>
       <x:c r="BA40" s="1"/>
     </x:row>
-    <x:row r="41" ht="22" customHeight="1">
-      <x:c r="A41" s="1"/>
-      <x:c r="B41" s="1"/>
-      <x:c r="C41" s="1"/>
-      <x:c r="D41" s="1"/>
-      <x:c r="E41" s="1"/>
+    <x:row r="41" ht="36" customHeight="1">
+      <x:c r="A41" s="1" t="str">
+        <x:v>Cloud Logging</x:v>
+      </x:c>
+      <x:c r="B41" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="13" t="str">
+        <x:v>未掲載</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F41" s="1"/>
       <x:c r="G41" s="1"/>
       <x:c r="H41" s="1"/>
@@ -26660,12 +26782,22 @@
       <x:c r="AZ41" s="1"/>
       <x:c r="BA41" s="1"/>
     </x:row>
-    <x:row r="42" ht="22" customHeight="1">
-      <x:c r="A42" s="1"/>
-      <x:c r="B42" s="1"/>
-      <x:c r="C42" s="1"/>
-      <x:c r="D42" s="1"/>
-      <x:c r="E42" s="1"/>
+    <x:row r="42" ht="36" customHeight="1">
+      <x:c r="A42" s="1" t="str">
+        <x:v>VM Manager</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="n">
+        <x:v>3073</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F42" s="1"/>
       <x:c r="G42" s="1"/>
       <x:c r="H42" s="1"/>
@@ -26715,12 +26847,22 @@
       <x:c r="AZ42" s="1"/>
       <x:c r="BA42" s="1"/>
     </x:row>
-    <x:row r="43" ht="22" customHeight="1">
-      <x:c r="A43" s="1"/>
-      <x:c r="B43" s="1"/>
-      <x:c r="C43" s="1"/>
-      <x:c r="D43" s="1"/>
-      <x:c r="E43" s="1"/>
+    <x:row r="43" ht="36" customHeight="1">
+      <x:c r="A43" s="1" t="str">
+        <x:v>Cloud DNS</x:v>
+      </x:c>
+      <x:c r="B43" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="13" t="str">
+        <x:v>未掲載</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F43" s="1"/>
       <x:c r="G43" s="1"/>
       <x:c r="H43" s="1"/>
@@ -26770,12 +26912,22 @@
       <x:c r="AZ43" s="1"/>
       <x:c r="BA43" s="1"/>
     </x:row>
-    <x:row r="44" ht="22" customHeight="1">
-      <x:c r="A44" s="1"/>
-      <x:c r="B44" s="1"/>
-      <x:c r="C44" s="1"/>
-      <x:c r="D44" s="1"/>
-      <x:c r="E44" s="1"/>
+    <x:row r="44" ht="36" customHeight="1">
+      <x:c r="A44" s="1" t="str">
+        <x:v>Cloud Scheduler</x:v>
+      </x:c>
+      <x:c r="B44" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C44" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="13" t="str">
+        <x:v>未掲載</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="str">
+        <x:v>共有実績・Secure Send配賦前</x:v>
+      </x:c>
       <x:c r="F44" s="1"/>
       <x:c r="G44" s="1"/>
       <x:c r="H44" s="1"/>
@@ -26825,12 +26977,12 @@
       <x:c r="AZ44" s="1"/>
       <x:c r="BA44" s="1"/>
     </x:row>
-    <x:row r="45" ht="22" customHeight="1">
+    <x:row r="45" ht="36" customHeight="1">
       <x:c r="A45" s="1"/>
-      <x:c r="B45" s="1"/>
-      <x:c r="C45" s="1"/>
-      <x:c r="D45" s="1"/>
-      <x:c r="E45" s="1"/>
+      <x:c r="B45" s="13"/>
+      <x:c r="C45" s="13"/>
+      <x:c r="D45" s="13"/>
+      <x:c r="E45" s="14"/>
       <x:c r="F45" s="1"/>
       <x:c r="G45" s="1"/>
       <x:c r="H45" s="1"/>
@@ -26880,12 +27032,22 @@
       <x:c r="AZ45" s="1"/>
       <x:c r="BA45" s="1"/>
     </x:row>
-    <x:row r="46" ht="22" customHeight="1">
-      <x:c r="A46" s="1"/>
-      <x:c r="B46" s="1"/>
-      <x:c r="C46" s="1"/>
-      <x:c r="D46" s="1"/>
-      <x:c r="E46" s="1"/>
+    <x:row r="46" ht="36" customHeight="1">
+      <x:c r="A46" s="1" t="str">
+        <x:v>最小CPU＋メモリ</x:v>
+      </x:c>
+      <x:c r="B46" s="13" t="n">
+        <x:v>8187</x:v>
+      </x:c>
+      <x:c r="C46" s="13" t="n">
+        <x:v>5315.570996</x:v>
+      </x:c>
+      <x:c r="D46" s="13" t="str">
+        <x:v>SKUなし</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="str">
+        <x:v>7〜9月共有Cloud Run。scan全額帰属不可</x:v>
+      </x:c>
       <x:c r="F46" s="1"/>
       <x:c r="G46" s="1"/>
       <x:c r="H46" s="1"/>
@@ -26935,12 +27097,12 @@
       <x:c r="AZ46" s="1"/>
       <x:c r="BA46" s="1"/>
     </x:row>
-    <x:row r="47" ht="22" customHeight="1">
+    <x:row r="47" ht="36" customHeight="1">
       <x:c r="A47" s="1"/>
-      <x:c r="B47" s="1"/>
-      <x:c r="C47" s="1"/>
-      <x:c r="D47" s="1"/>
-      <x:c r="E47" s="1"/>
+      <x:c r="B47" s="13"/>
+      <x:c r="C47" s="13"/>
+      <x:c r="D47" s="13"/>
+      <x:c r="E47" s="14"/>
       <x:c r="F47" s="1"/>
       <x:c r="G47" s="1"/>
       <x:c r="H47" s="1"/>
@@ -26990,12 +27152,22 @@
       <x:c r="AZ47" s="1"/>
       <x:c r="BA47" s="1"/>
     </x:row>
-    <x:row r="48" ht="22" customHeight="1">
-      <x:c r="A48" s="1"/>
-      <x:c r="B48" s="1"/>
-      <x:c r="C48" s="1"/>
-      <x:c r="D48" s="1"/>
-      <x:c r="E48" s="1"/>
+    <x:row r="48" ht="36" customHeight="1">
+      <x:c r="A48" s="1" t="str">
+        <x:v>scan9月待機推計</x:v>
+      </x:c>
+      <x:c r="B48" s="13" t="n">
+        <x:v>3126.962664939129</x:v>
+      </x:c>
+      <x:c r="C48" s="13" t="n">
+        <x:v>2077.5687592208883</x:v>
+      </x:c>
+      <x:c r="D48" s="13" t="str">
+        <x:v>期間不一致</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="str">
+        <x:v>実請求ではない。CPU割当でidleを近似・四半期削減率を仮配賦</x:v>
+      </x:c>
       <x:c r="F48" s="1"/>
       <x:c r="G48" s="1"/>
       <x:c r="H48" s="1"/>
@@ -27045,12 +27217,12 @@
       <x:c r="AZ48" s="1"/>
       <x:c r="BA48" s="1"/>
     </x:row>
-    <x:row r="49" ht="22" customHeight="1">
+    <x:row r="49" ht="36" customHeight="1">
       <x:c r="A49" s="1"/>
       <x:c r="B49" s="1"/>
       <x:c r="C49" s="1"/>
       <x:c r="D49" s="1"/>
-      <x:c r="E49" s="1"/>
+      <x:c r="E49" s="14"/>
       <x:c r="F49" s="1"/>
       <x:c r="G49" s="1"/>
       <x:c r="H49" s="1"/>
@@ -27100,12 +27272,18 @@
       <x:c r="AZ49" s="1"/>
       <x:c r="BA49" s="1"/>
     </x:row>
-    <x:row r="50" ht="22" customHeight="1">
-      <x:c r="A50" s="1"/>
-      <x:c r="B50" s="1"/>
+    <x:row r="50" ht="36" customHeight="1">
+      <x:c r="A50" s="1" t="str">
+        <x:v>出典: 7〜9月 SKU CSV</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="str">
+        <x:v>libfile_ceae161333f88191b3ec86f70899a900</x:v>
+      </x:c>
       <x:c r="C50" s="1"/>
       <x:c r="D50" s="1"/>
-      <x:c r="E50" s="1"/>
+      <x:c r="E50" s="14" t="str">
+        <x:v>添付(1)版と内容一致確認。月別・リソース名・プロジェクト列なし</x:v>
+      </x:c>
       <x:c r="F50" s="1"/>
       <x:c r="G50" s="1"/>
       <x:c r="H50" s="1"/>
@@ -27155,12 +27333,18 @@
       <x:c r="AZ50" s="1"/>
       <x:c r="BA50" s="1"/>
     </x:row>
-    <x:row r="51" ht="22" customHeight="1">
-      <x:c r="A51" s="1"/>
-      <x:c r="B51" s="1"/>
+    <x:row r="51" ht="36" customHeight="1">
+      <x:c r="A51" s="1" t="str">
+        <x:v>出典: 10月 service CSV</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="str">
+        <x:v>libfile_0178b7b688d081919ef3d8ea32579b4b</x:v>
+      </x:c>
       <x:c r="C51" s="1"/>
       <x:c r="D51" s="1"/>
-      <x:c r="E51" s="1"/>
+      <x:c r="E51" s="14" t="str">
+        <x:v>10月途中、SKUなし。Monitoringと同一終了時刻とは限らない</x:v>
+      </x:c>
       <x:c r="F51" s="1"/>
       <x:c r="G51" s="1"/>
       <x:c r="H51" s="1"/>
@@ -27210,12 +27394,20 @@
       <x:c r="AZ51" s="1"/>
       <x:c r="BA51" s="1"/>
     </x:row>
-    <x:row r="52" ht="22" customHeight="1">
-      <x:c r="A52" s="1"/>
+    <x:row r="52" ht="36" customHeight="1">
+      <x:c r="A52" s="1" t="str">
+        <x:v>共有小計</x:v>
+      </x:c>
       <x:c r="B52" s="1"/>
-      <x:c r="C52" s="1"/>
-      <x:c r="D52" s="1"/>
-      <x:c r="E52" s="1"/>
+      <x:c r="C52" s="1" t="n">
+        <x:v>42818.187617</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="n">
+        <x:v>18761.212531</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>Q3合計行との差0.106628円は未解明。円丸め後は一致</x:v>
+      </x:c>
       <x:c r="F52" s="1"/>
       <x:c r="G52" s="1"/>
       <x:c r="H52" s="1"/>
